--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122307900</v>
+        <v>122309488</v>
       </c>
       <c r="B2" t="n">
-        <v>77582</v>
+        <v>79176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>1350</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444357</v>
+        <v>444267</v>
       </c>
       <c r="R2" t="n">
-        <v>7029819</v>
+        <v>7029861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (19 cm dbh ca 150 år gammal) i gammal granskog</t>
+          <t>På grenar på gammal levande gran (45 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122310810</v>
+        <v>122314255</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>79176</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1350</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444508</v>
+        <v>444393</v>
       </c>
       <c r="R3" t="n">
-        <v>7029853</v>
+        <v>7029650</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal grov gran vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,17 +902,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122307914</v>
+        <v>122311221</v>
       </c>
       <c r="B4" t="n">
-        <v>74747</v>
+        <v>77582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444357</v>
+        <v>444500</v>
       </c>
       <c r="R4" t="n">
-        <v>7029819</v>
+        <v>7029730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122310674</v>
+        <v>122309331</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>78838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,31 +1038,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>230552</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444517</v>
+        <v>444251</v>
       </c>
       <c r="R5" t="n">
-        <v>7029877</v>
+        <v>7029853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran, ganska färska</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122311206</v>
+        <v>122308391</v>
       </c>
       <c r="B6" t="n">
-        <v>74747</v>
+        <v>79176</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,38 +1164,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1350</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444516</v>
+        <v>444326</v>
       </c>
       <c r="R6" t="n">
-        <v>7029733</v>
+        <v>7029781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1251,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På tunna döda grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,17 +1276,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122311676</v>
+        <v>122310810</v>
       </c>
       <c r="B7" t="n">
-        <v>79176</v>
+        <v>78645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,47 +1295,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1350</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444472</v>
+        <v>444508</v>
       </c>
       <c r="R7" t="n">
-        <v>7029703</v>
+        <v>7029853</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,12 +1368,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På död gren på gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122311003</v>
+        <v>122311468</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>77582</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,48 +1416,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444511</v>
+        <v>444476</v>
       </c>
       <c r="R8" t="n">
-        <v>7029847</v>
+        <v>7029720</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,12 +1485,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökte på död björk och sedan död gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,17 +1510,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122311084</v>
+        <v>122311754</v>
       </c>
       <c r="B9" t="n">
-        <v>77582</v>
+        <v>90797</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,21 +1533,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1562,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444545</v>
+        <v>444435</v>
       </c>
       <c r="R9" t="n">
-        <v>7029748</v>
+        <v>7029665</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,12 +1602,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,17 +1627,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122310115</v>
+        <v>122310674</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,34 +1650,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444400</v>
+        <v>444517</v>
       </c>
       <c r="R10" t="n">
-        <v>7029944</v>
+        <v>7029877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig på död gammal gran i gammal granskog</t>
+          <t>Ringhack på gran, ganska färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,10 +1756,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122309488</v>
+        <v>122307900</v>
       </c>
       <c r="B11" t="n">
-        <v>79176</v>
+        <v>77582</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,25 +1768,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1350</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444267</v>
+        <v>444357</v>
       </c>
       <c r="R11" t="n">
-        <v>7029861</v>
+        <v>7029819</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran (45 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (19 cm dbh ca 150 år gammal) i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122309383</v>
+        <v>122314218</v>
       </c>
       <c r="B12" t="n">
-        <v>74670</v>
+        <v>79183</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,41 +1885,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1460</v>
+        <v>1353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444261</v>
+        <v>444393</v>
       </c>
       <c r="R12" t="n">
-        <v>7029847</v>
+        <v>7029650</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal grov gran vid bäck</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,17 +1983,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122309331</v>
+        <v>122307921</v>
       </c>
       <c r="B13" t="n">
-        <v>78838</v>
+        <v>78645</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,47 +2002,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230552</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444251</v>
+        <v>444357</v>
       </c>
       <c r="R13" t="n">
-        <v>7029853</v>
+        <v>7029819</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2074,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2084,12 +2075,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,10 +2107,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122311468</v>
+        <v>122311602</v>
       </c>
       <c r="B14" t="n">
-        <v>77582</v>
+        <v>90797</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2132,21 +2123,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2156,10 +2147,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444476</v>
+        <v>444478</v>
       </c>
       <c r="R14" t="n">
-        <v>7029720</v>
+        <v>7029647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2191,7 +2182,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2201,12 +2192,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grov gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2233,10 +2224,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122314218</v>
+        <v>122310115</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>78645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2245,41 +2236,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444393</v>
+        <v>444400</v>
       </c>
       <c r="R15" t="n">
-        <v>7029650</v>
+        <v>7029944</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2308,7 +2299,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2318,12 +2309,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på gammal grov gran vid bäck</t>
+          <t>Riklig på död gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,17 +2334,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122307921</v>
+        <v>122307914</v>
       </c>
       <c r="B16" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,21 +2357,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2467,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122311413</v>
+        <v>122311676</v>
       </c>
       <c r="B17" t="n">
-        <v>90797</v>
+        <v>79176</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2479,38 +2470,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444476</v>
+        <v>444472</v>
       </c>
       <c r="R17" t="n">
-        <v>7029720</v>
+        <v>7029703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gren på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2584,7 +2584,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122311602</v>
+        <v>122310954</v>
       </c>
       <c r="B18" t="n">
         <v>90797</v>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444478</v>
+        <v>444511</v>
       </c>
       <c r="R18" t="n">
-        <v>7029647</v>
+        <v>7029847</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På grov gammal gran i gammal granskog</t>
+          <t>På död gran under asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2694,17 +2694,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122311221</v>
+        <v>122310342</v>
       </c>
       <c r="B19" t="n">
-        <v>77582</v>
+        <v>78645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,34 +2717,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444500</v>
+        <v>444461</v>
       </c>
       <c r="R19" t="n">
-        <v>7029730</v>
+        <v>7029933</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Längsta bål 50 cm lång, på gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2811,17 +2811,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122310954</v>
+        <v>122308365</v>
       </c>
       <c r="B20" t="n">
-        <v>90797</v>
+        <v>57527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2834,34 +2834,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444511</v>
+        <v>444341</v>
       </c>
       <c r="R20" t="n">
-        <v>7029847</v>
+        <v>7029799</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2893,7 +2902,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2903,12 +2912,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På död gran under asp</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2928,17 +2937,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122314255</v>
+        <v>122309383</v>
       </c>
       <c r="B21" t="n">
-        <v>79176</v>
+        <v>74670</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2947,41 +2956,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1350</v>
+        <v>1460</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444393</v>
+        <v>444261</v>
       </c>
       <c r="R21" t="n">
-        <v>7029650</v>
+        <v>7029847</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3010,7 +3019,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3020,12 +3029,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på gammal grov gran vid bäck, bäckravin</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,17 +3054,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122308391</v>
+        <v>122311413</v>
       </c>
       <c r="B22" t="n">
-        <v>79176</v>
+        <v>90797</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,52 +3073,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444326</v>
+        <v>444476</v>
       </c>
       <c r="R22" t="n">
-        <v>7029781</v>
+        <v>7029720</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3141,7 +3136,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3151,12 +3146,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På tunna döda grenar på gammal levande gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3183,10 +3178,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122310342</v>
+        <v>122311003</v>
       </c>
       <c r="B23" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3199,34 +3194,48 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444461</v>
+        <v>444511</v>
       </c>
       <c r="R23" t="n">
-        <v>7029933</v>
+        <v>7029847</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3258,7 +3267,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3268,12 +3277,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Längsta bål 50 cm lång, på gammal gran</t>
+          <t>Födosökte på död björk och sedan död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3293,17 +3302,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122311754</v>
+        <v>122311206</v>
       </c>
       <c r="B24" t="n">
-        <v>90797</v>
+        <v>74747</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3316,21 +3325,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3340,10 +3349,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444435</v>
+        <v>444516</v>
       </c>
       <c r="R24" t="n">
-        <v>7029665</v>
+        <v>7029733</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3375,7 +3384,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3385,12 +3394,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,17 +3419,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122308365</v>
+        <v>122311084</v>
       </c>
       <c r="B25" t="n">
-        <v>57527</v>
+        <v>77582</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3433,43 +3442,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444341</v>
+        <v>444545</v>
       </c>
       <c r="R25" t="n">
-        <v>7029799</v>
+        <v>7029748</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122335985</v>
+        <v>122335946</v>
       </c>
       <c r="B26" t="n">
-        <v>74747</v>
+        <v>78645</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3559,21 +3559,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444412</v>
+        <v>444551</v>
       </c>
       <c r="R26" t="n">
-        <v>7029863</v>
+        <v>7029838</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3670,10 +3670,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122335951</v>
+        <v>122335982</v>
       </c>
       <c r="B27" t="n">
-        <v>78838</v>
+        <v>78645</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3682,41 +3682,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230552</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444495</v>
+        <v>444384</v>
       </c>
       <c r="R27" t="n">
-        <v>7029958</v>
+        <v>7029877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3748,7 +3745,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3758,7 +3755,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3767,7 +3764,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3801,10 +3797,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122308186</v>
+        <v>122335941</v>
       </c>
       <c r="B28" t="n">
-        <v>78838</v>
+        <v>79176</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3817,37 +3813,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230552</v>
+        <v>1350</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444341</v>
+        <v>444485</v>
       </c>
       <c r="R28" t="n">
-        <v>7029799</v>
+        <v>7029724</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3879,7 +3872,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3889,12 +3882,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På döda grenar på gammal levande gran  (40 cm dbh)  gammal granskog</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3903,29 +3891,43 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122335953</v>
+        <v>122335942</v>
       </c>
       <c r="B29" t="n">
-        <v>77582</v>
+        <v>79183</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3934,25 +3936,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>1353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3962,10 +3964,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444453</v>
+        <v>444485</v>
       </c>
       <c r="R29" t="n">
-        <v>7029951</v>
+        <v>7029724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3997,7 +3999,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4007,7 +4009,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4049,10 +4051,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122335979</v>
+        <v>122335948</v>
       </c>
       <c r="B30" t="n">
-        <v>74559</v>
+        <v>78645</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4061,25 +4063,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4089,10 +4091,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444384</v>
+        <v>444546</v>
       </c>
       <c r="R30" t="n">
-        <v>7029877</v>
+        <v>7029872</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4124,7 +4126,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4134,7 +4136,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4176,10 +4178,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122335938</v>
+        <v>122311201</v>
       </c>
       <c r="B31" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4192,34 +4194,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444470</v>
+        <v>444531</v>
       </c>
       <c r="R31" t="n">
-        <v>7029684</v>
+        <v>7029734</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4251,7 +4258,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4261,7 +4268,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,41 +4284,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122335945</v>
+        <v>122335958</v>
       </c>
       <c r="B32" t="n">
-        <v>90797</v>
+        <v>78645</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4319,21 +4316,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4343,10 +4340,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444549</v>
+        <v>444308</v>
       </c>
       <c r="R32" t="n">
-        <v>7029834</v>
+        <v>7029944</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4378,7 +4375,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4388,7 +4385,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4430,7 +4427,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122335952</v>
+        <v>122331092</v>
       </c>
       <c r="B33" t="n">
         <v>78645</v>
@@ -4466,17 +4463,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>MD19:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444479</v>
+        <v>444336</v>
       </c>
       <c r="R33" t="n">
-        <v>7029961</v>
+        <v>7029947</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4505,7 +4502,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4515,7 +4512,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4526,41 +4523,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122335974</v>
+        <v>122335945</v>
       </c>
       <c r="B34" t="n">
-        <v>79183</v>
+        <v>90797</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4569,25 +4551,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1353</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4597,10 +4579,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444362</v>
+        <v>444549</v>
       </c>
       <c r="R34" t="n">
-        <v>7029827</v>
+        <v>7029834</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4632,7 +4614,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4642,12 +4624,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På två träd intill varandra.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4671,7 +4648,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Klenare gran under grov asp # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4689,10 +4666,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122335958</v>
+        <v>122335953</v>
       </c>
       <c r="B35" t="n">
-        <v>78645</v>
+        <v>77582</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4705,21 +4682,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4729,10 +4706,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444308</v>
+        <v>444453</v>
       </c>
       <c r="R35" t="n">
-        <v>7029944</v>
+        <v>7029951</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4764,7 +4741,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4774,7 +4751,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4816,10 +4793,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122331092</v>
+        <v>122335971</v>
       </c>
       <c r="B36" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4832,37 +4809,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>MD19:Krokom, SE-JA, SE, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444336</v>
+        <v>444319</v>
       </c>
       <c r="R36" t="n">
-        <v>7029947</v>
+        <v>7029774</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4891,7 +4877,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4901,7 +4887,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4916,22 +4902,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122335937</v>
+        <v>122335950</v>
       </c>
       <c r="B37" t="n">
-        <v>74747</v>
+        <v>79176</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4940,25 +4926,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1350</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4968,10 +4954,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444451</v>
+        <v>444495</v>
       </c>
       <c r="R37" t="n">
-        <v>7029662</v>
+        <v>7029958</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5003,7 +4989,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5013,7 +4999,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5037,7 +5023,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Tunn, död kvist # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5055,10 +5041,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122311201</v>
+        <v>122335980</v>
       </c>
       <c r="B38" t="n">
-        <v>57374</v>
+        <v>74747</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5071,39 +5057,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444531</v>
+        <v>444384</v>
       </c>
       <c r="R38" t="n">
-        <v>7029734</v>
+        <v>7029877</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5135,7 +5116,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5145,12 +5126,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5161,26 +5137,41 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122335983</v>
+        <v>122331094</v>
       </c>
       <c r="B39" t="n">
-        <v>57527</v>
+        <v>74747</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5193,46 +5184,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>MD13:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444373</v>
+        <v>444497</v>
       </c>
       <c r="R39" t="n">
-        <v>7029874</v>
+        <v>7029726</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5261,7 +5243,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5271,7 +5253,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5286,22 +5268,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122335943</v>
+        <v>122335957</v>
       </c>
       <c r="B40" t="n">
-        <v>90775</v>
+        <v>78645</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5314,21 +5296,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5338,10 +5320,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444544</v>
+        <v>444349</v>
       </c>
       <c r="R40" t="n">
-        <v>7029746</v>
+        <v>7029951</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5373,7 +5355,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5383,7 +5365,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5425,10 +5407,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122335948</v>
+        <v>122335949</v>
       </c>
       <c r="B41" t="n">
-        <v>78645</v>
+        <v>79630</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5437,38 +5419,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444546</v>
+        <v>444532</v>
       </c>
       <c r="R41" t="n">
-        <v>7029872</v>
+        <v>7029934</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5500,7 +5485,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5510,7 +5495,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5519,22 +5504,23 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5552,10 +5538,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122331094</v>
+        <v>122335981</v>
       </c>
       <c r="B42" t="n">
-        <v>74747</v>
+        <v>77582</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5568,37 +5554,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>MD13:Krokom, SE-JA, SE, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444497</v>
+        <v>444384</v>
       </c>
       <c r="R42" t="n">
-        <v>7029726</v>
+        <v>7029877</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5627,7 +5613,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5637,7 +5623,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5648,26 +5634,41 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122335981</v>
+        <v>122335984</v>
       </c>
       <c r="B43" t="n">
-        <v>77582</v>
+        <v>78645</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5680,21 +5681,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5704,10 +5705,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444384</v>
+        <v>444412</v>
       </c>
       <c r="R43" t="n">
-        <v>7029877</v>
+        <v>7029863</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5739,7 +5740,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5749,7 +5750,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5791,7 +5792,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122335957</v>
+        <v>122335972</v>
       </c>
       <c r="B44" t="n">
         <v>78645</v>
@@ -5831,10 +5832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444349</v>
+        <v>444362</v>
       </c>
       <c r="R44" t="n">
-        <v>7029951</v>
+        <v>7029793</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5866,7 +5867,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5876,7 +5877,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5918,10 +5919,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122335980</v>
+        <v>122331096</v>
       </c>
       <c r="B45" t="n">
-        <v>74747</v>
+        <v>57374</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5934,37 +5935,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>MD6:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444384</v>
+        <v>444409</v>
       </c>
       <c r="R45" t="n">
-        <v>7029877</v>
+        <v>7029858</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5993,7 +5994,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6003,7 +6004,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6014,41 +6015,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122335970</v>
+        <v>122335974</v>
       </c>
       <c r="B46" t="n">
-        <v>79176</v>
+        <v>79183</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6057,25 +6043,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6085,10 +6071,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444342</v>
+        <v>444362</v>
       </c>
       <c r="R46" t="n">
-        <v>7029789</v>
+        <v>7029827</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6120,7 +6106,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6130,7 +6116,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På två träd intill varandra.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6154,7 +6145,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Äldre gran, närmare 40 cm dbh # Picea abies</t>
+          <t>Klenare gran under grov asp # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6172,10 +6163,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122335950</v>
+        <v>122335979</v>
       </c>
       <c r="B47" t="n">
-        <v>79176</v>
+        <v>74559</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6184,25 +6175,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1350</v>
+        <v>6428</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6212,10 +6203,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444495</v>
+        <v>444384</v>
       </c>
       <c r="R47" t="n">
-        <v>7029958</v>
+        <v>7029877</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6247,7 +6238,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6257,7 +6248,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6281,7 +6272,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Tunn, död kvist # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6299,10 +6290,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122335941</v>
+        <v>122335952</v>
       </c>
       <c r="B48" t="n">
-        <v>79176</v>
+        <v>78645</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6311,25 +6302,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1350</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6339,10 +6330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444485</v>
+        <v>444479</v>
       </c>
       <c r="R48" t="n">
-        <v>7029724</v>
+        <v>7029961</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6374,7 +6365,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6384,7 +6375,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6426,10 +6417,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122335973</v>
+        <v>122335938</v>
       </c>
       <c r="B49" t="n">
-        <v>90779</v>
+        <v>90797</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6442,21 +6433,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6466,10 +6457,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444359</v>
+        <v>444470</v>
       </c>
       <c r="R49" t="n">
-        <v>7029807</v>
+        <v>7029684</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6501,7 +6492,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6511,7 +6502,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6553,10 +6544,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122335966</v>
+        <v>122335963</v>
       </c>
       <c r="B50" t="n">
-        <v>74559</v>
+        <v>90779</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6565,25 +6556,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6593,10 +6584,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444342</v>
+        <v>444259</v>
       </c>
       <c r="R50" t="n">
-        <v>7029789</v>
+        <v>7029839</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6628,7 +6619,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6638,7 +6629,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6680,10 +6671,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122335971</v>
+        <v>122335977</v>
       </c>
       <c r="B51" t="n">
-        <v>57374</v>
+        <v>74747</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6696,43 +6687,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444319</v>
+        <v>444368</v>
       </c>
       <c r="R51" t="n">
-        <v>7029774</v>
+        <v>7029868</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6764,7 +6746,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6774,7 +6756,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6785,6 +6767,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6801,10 +6798,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122335959</v>
+        <v>122335975</v>
       </c>
       <c r="B52" t="n">
-        <v>78838</v>
+        <v>79181</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6813,25 +6810,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>230552</v>
+        <v>1352</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6844,10 +6841,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444304</v>
+        <v>444362</v>
       </c>
       <c r="R52" t="n">
-        <v>7029940</v>
+        <v>7029827</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6879,7 +6876,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6889,7 +6886,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6904,17 +6901,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Nedfallen gren # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6932,10 +6929,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122335946</v>
+        <v>122335983</v>
       </c>
       <c r="B53" t="n">
-        <v>78645</v>
+        <v>57527</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6948,37 +6945,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444551</v>
+        <v>444373</v>
       </c>
       <c r="R53" t="n">
-        <v>7029838</v>
+        <v>7029874</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7007,7 +7013,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7017,7 +7023,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7028,21 +7034,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7059,10 +7050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122335965</v>
+        <v>122335959</v>
       </c>
       <c r="B54" t="n">
-        <v>74745</v>
+        <v>78838</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7075,34 +7066,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6486</v>
+        <v>230552</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444338</v>
+        <v>444304</v>
       </c>
       <c r="R54" t="n">
-        <v>7029793</v>
+        <v>7029940</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7134,7 +7128,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7144,7 +7138,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7153,6 +7147,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7186,7 +7181,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122335977</v>
+        <v>122335937</v>
       </c>
       <c r="B55" t="n">
         <v>74747</v>
@@ -7226,10 +7221,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444368</v>
+        <v>444451</v>
       </c>
       <c r="R55" t="n">
-        <v>7029868</v>
+        <v>7029662</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7261,7 +7256,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7271,7 +7266,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7313,10 +7308,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122335963</v>
+        <v>122331091</v>
       </c>
       <c r="B56" t="n">
-        <v>90779</v>
+        <v>90797</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7329,37 +7324,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>MD20:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444259</v>
+        <v>444319</v>
       </c>
       <c r="R56" t="n">
-        <v>7029839</v>
+        <v>7029805</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7388,7 +7383,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7398,7 +7393,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7409,41 +7404,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122335960</v>
+        <v>122335951</v>
       </c>
       <c r="B57" t="n">
-        <v>79183</v>
+        <v>78838</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7452,37 +7432,29 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1353</v>
+        <v>230552</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -7491,10 +7463,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444304</v>
+        <v>444495</v>
       </c>
       <c r="R57" t="n">
-        <v>7029940</v>
+        <v>7029958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7526,7 +7498,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7536,7 +7508,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7579,10 +7551,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122335984</v>
+        <v>122308186</v>
       </c>
       <c r="B58" t="n">
-        <v>78645</v>
+        <v>78838</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7591,38 +7563,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>230552</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444412</v>
+        <v>444341</v>
       </c>
       <c r="R58" t="n">
-        <v>7029863</v>
+        <v>7029799</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7654,7 +7629,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7664,7 +7639,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På döda grenar på gammal levande gran  (40 cm dbh)  gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7673,43 +7653,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122335954</v>
+        <v>122335960</v>
       </c>
       <c r="B59" t="n">
-        <v>74747</v>
+        <v>79183</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7718,38 +7684,49 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>1353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444397</v>
+        <v>444304</v>
       </c>
       <c r="R59" t="n">
-        <v>7029925</v>
+        <v>7029940</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7781,7 +7758,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7791,7 +7768,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7800,6 +7777,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7833,10 +7811,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122335961</v>
+        <v>122335936</v>
       </c>
       <c r="B60" t="n">
-        <v>80904</v>
+        <v>78645</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7845,25 +7823,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3929</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7873,10 +7851,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444278</v>
+        <v>444418</v>
       </c>
       <c r="R60" t="n">
-        <v>7029870</v>
+        <v>7029686</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7908,7 +7886,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7918,7 +7896,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7932,17 +7910,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gråal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Alnus incana</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Alnus incana</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7960,10 +7938,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122331096</v>
+        <v>122331095</v>
       </c>
       <c r="B61" t="n">
-        <v>57374</v>
+        <v>90797</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7976,37 +7954,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>MD6:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD5:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444409</v>
+        <v>444429</v>
       </c>
       <c r="R61" t="n">
-        <v>7029858</v>
+        <v>7029670</v>
       </c>
       <c r="S61" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8035,7 +8013,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8045,7 +8023,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8072,10 +8050,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122335949</v>
+        <v>122335954</v>
       </c>
       <c r="B62" t="n">
-        <v>79630</v>
+        <v>74747</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8084,41 +8062,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444532</v>
+        <v>444397</v>
       </c>
       <c r="R62" t="n">
-        <v>7029934</v>
+        <v>7029925</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8150,7 +8125,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8160,7 +8135,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8169,23 +8144,22 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8203,10 +8177,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122335942</v>
+        <v>122335985</v>
       </c>
       <c r="B63" t="n">
-        <v>79183</v>
+        <v>74747</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8215,25 +8189,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1353</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8243,10 +8217,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444485</v>
+        <v>444412</v>
       </c>
       <c r="R63" t="n">
-        <v>7029724</v>
+        <v>7029863</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8278,7 +8252,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8288,7 +8262,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8330,10 +8304,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122335982</v>
+        <v>122331093</v>
       </c>
       <c r="B64" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8346,37 +8320,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>MD15:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444384</v>
+        <v>444391</v>
       </c>
       <c r="R64" t="n">
-        <v>7029877</v>
+        <v>7029904</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8405,7 +8379,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8415,7 +8389,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8426,41 +8400,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122331091</v>
+        <v>122335947</v>
       </c>
       <c r="B65" t="n">
-        <v>90797</v>
+        <v>77582</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8473,37 +8432,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>MD20:Krokom, SE-JA, SE, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444319</v>
+        <v>444551</v>
       </c>
       <c r="R65" t="n">
-        <v>7029805</v>
+        <v>7029838</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8532,7 +8491,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8542,7 +8501,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8553,26 +8512,41 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122335936</v>
+        <v>122335976</v>
       </c>
       <c r="B66" t="n">
-        <v>78645</v>
+        <v>79630</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8581,38 +8555,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444418</v>
+        <v>444362</v>
       </c>
       <c r="R66" t="n">
-        <v>7029686</v>
+        <v>7029827</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8644,7 +8621,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8654,7 +8631,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8663,22 +8640,23 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8696,10 +8674,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122335975</v>
+        <v>122335965</v>
       </c>
       <c r="B67" t="n">
-        <v>79181</v>
+        <v>74745</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8708,41 +8686,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1352</v>
+        <v>6486</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444362</v>
+        <v>444338</v>
       </c>
       <c r="R67" t="n">
-        <v>7029827</v>
+        <v>7029793</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8774,7 +8749,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8784,7 +8759,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8793,23 +8768,22 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Nedfallen gren # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8827,10 +8801,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122335947</v>
+        <v>122335973</v>
       </c>
       <c r="B68" t="n">
-        <v>77582</v>
+        <v>90779</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8843,21 +8817,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8867,10 +8841,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444551</v>
+        <v>444359</v>
       </c>
       <c r="R68" t="n">
-        <v>7029838</v>
+        <v>7029807</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8902,7 +8876,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8912,7 +8886,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8954,10 +8928,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122331095</v>
+        <v>122335961</v>
       </c>
       <c r="B69" t="n">
-        <v>90797</v>
+        <v>80904</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8966,41 +8940,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>3929</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Roth.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>MD5:Krokom, SE-JA, SE, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444429</v>
+        <v>444278</v>
       </c>
       <c r="R69" t="n">
-        <v>7029670</v>
+        <v>7029870</v>
       </c>
       <c r="S69" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9029,7 +9003,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9039,7 +9013,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9050,26 +9024,41 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122335972</v>
+        <v>122335966</v>
       </c>
       <c r="B70" t="n">
-        <v>78645</v>
+        <v>74559</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9078,25 +9067,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9106,10 +9095,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444362</v>
+        <v>444342</v>
       </c>
       <c r="R70" t="n">
-        <v>7029793</v>
+        <v>7029789</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9141,7 +9130,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9151,7 +9140,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9193,10 +9182,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122331093</v>
+        <v>122335943</v>
       </c>
       <c r="B71" t="n">
-        <v>57374</v>
+        <v>90775</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9209,37 +9198,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>MD15:Krokom, SE-JA, SE, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444391</v>
+        <v>444544</v>
       </c>
       <c r="R71" t="n">
-        <v>7029904</v>
+        <v>7029746</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9268,7 +9257,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9278,7 +9267,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9289,26 +9278,41 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Elin Albrechtsson, Lisa Johansson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122335976</v>
+        <v>122335970</v>
       </c>
       <c r="B72" t="n">
-        <v>79630</v>
+        <v>79176</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9317,41 +9321,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6456</v>
+        <v>1350</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444362</v>
+        <v>444342</v>
       </c>
       <c r="R72" t="n">
-        <v>7029827</v>
+        <v>7029789</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9383,7 +9384,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9393,7 +9394,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9402,23 +9403,22 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Äldre gran, närmare 40 cm dbh # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124398951</v>
+        <v>124397876</v>
       </c>
       <c r="B73" t="n">
-        <v>79348</v>
+        <v>91413</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,52 +9448,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1353</v>
+        <v>4217</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444424</v>
+        <v>444498</v>
       </c>
       <c r="R73" t="n">
-        <v>7029691</v>
+        <v>7029879</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9525,7 +9511,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9535,12 +9521,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9560,17 +9546,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124397408</v>
+        <v>124399357</v>
       </c>
       <c r="B74" t="n">
-        <v>79851</v>
+        <v>79066</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9583,37 +9569,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>6459</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444276</v>
+        <v>444468</v>
       </c>
       <c r="R74" t="n">
-        <v>7030094</v>
+        <v>7029811</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9642,7 +9628,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9652,12 +9638,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9672,22 +9658,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124397463</v>
+        <v>124398118</v>
       </c>
       <c r="B75" t="n">
-        <v>91012</v>
+        <v>91950</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9696,46 +9682,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444279</v>
+        <v>444492</v>
       </c>
       <c r="R75" t="n">
-        <v>7030095</v>
+        <v>7029851</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9764,7 +9745,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9774,12 +9755,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9794,22 +9775,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124399926</v>
+        <v>124396185</v>
       </c>
       <c r="B76" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9818,50 +9799,50 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444478</v>
+        <v>444287</v>
       </c>
       <c r="R76" t="n">
-        <v>7029836</v>
+        <v>7030000</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9890,7 +9871,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9900,12 +9881,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På gran, bredvid asp</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9925,17 +9901,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124398709</v>
+        <v>124396061</v>
       </c>
       <c r="B77" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9944,50 +9920,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444401</v>
+        <v>444402</v>
       </c>
       <c r="R77" t="n">
-        <v>7029685</v>
+        <v>7030044</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10016,7 +9983,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10026,12 +9993,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10042,26 +10004,41 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>August Nordin, Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124399091</v>
+        <v>124397408</v>
       </c>
       <c r="B78" t="n">
-        <v>79795</v>
+        <v>79851</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10074,37 +10051,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444439</v>
+        <v>444276</v>
       </c>
       <c r="R78" t="n">
-        <v>7029686</v>
+        <v>7030094</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10133,7 +10110,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10143,12 +10120,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10168,17 +10145,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124397972</v>
+        <v>124399157</v>
       </c>
       <c r="B79" t="n">
-        <v>79341</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10187,25 +10164,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1350</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10215,13 +10192,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444487</v>
+        <v>444448</v>
       </c>
       <c r="R79" t="n">
-        <v>7029857</v>
+        <v>7029741</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10250,7 +10227,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10260,12 +10237,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10285,17 +10262,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124399571</v>
+        <v>124399597</v>
       </c>
       <c r="B80" t="n">
-        <v>91030</v>
+        <v>91705</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10304,46 +10281,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444478</v>
+        <v>444456</v>
       </c>
       <c r="R80" t="n">
-        <v>7029836</v>
+        <v>7029772</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10387,7 +10359,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10402,22 +10374,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124396024</v>
+        <v>124398839</v>
       </c>
       <c r="B81" t="n">
-        <v>79920</v>
+        <v>78998</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10426,41 +10398,50 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>230552</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444388</v>
+        <v>444409</v>
       </c>
       <c r="R81" t="n">
-        <v>7030037</v>
+        <v>7029694</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10489,7 +10470,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10499,12 +10480,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10524,17 +10505,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124397708</v>
+        <v>124399819</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10547,26 +10528,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10580,13 +10561,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444403</v>
+        <v>444478</v>
       </c>
       <c r="R82" t="n">
-        <v>7029971</v>
+        <v>7029836</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10615,7 +10596,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10625,7 +10606,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10645,17 +10631,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124396061</v>
+        <v>124396028</v>
       </c>
       <c r="B83" t="n">
-        <v>79851</v>
+        <v>79857</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10668,21 +10654,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>229748</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10698,7 +10684,7 @@
         <v>7030044</v>
       </c>
       <c r="S83" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10779,10 +10765,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124399997</v>
+        <v>124399926</v>
       </c>
       <c r="B84" t="n">
-        <v>79348</v>
+        <v>79341</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10791,30 +10777,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10822,24 +10808,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444448</v>
+        <v>444478</v>
       </c>
       <c r="R84" t="n">
-        <v>7029784</v>
+        <v>7029836</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10868,7 +10849,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10878,12 +10859,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10898,22 +10879,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124396185</v>
+        <v>124397664</v>
       </c>
       <c r="B85" t="n">
-        <v>91030</v>
+        <v>95335</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10922,50 +10903,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444287</v>
+        <v>444403</v>
       </c>
       <c r="R85" t="n">
-        <v>7030000</v>
+        <v>7030010</v>
       </c>
       <c r="S85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10994,7 +10966,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11004,7 +10976,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11019,22 +10996,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124398118</v>
+        <v>124399091</v>
       </c>
       <c r="B86" t="n">
-        <v>91950</v>
+        <v>79795</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11047,21 +11024,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4769</v>
+        <v>6456</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11071,13 +11048,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444492</v>
+        <v>444439</v>
       </c>
       <c r="R86" t="n">
-        <v>7029851</v>
+        <v>7029686</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11106,7 +11083,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11116,12 +11093,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11148,10 +11125,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124398297</v>
+        <v>124397708</v>
       </c>
       <c r="B87" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11160,41 +11137,50 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444498</v>
+        <v>444403</v>
       </c>
       <c r="R87" t="n">
-        <v>7029821</v>
+        <v>7029971</v>
       </c>
       <c r="S87" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11223,7 +11209,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11233,12 +11219,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På gråal</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11258,17 +11239,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124399656</v>
+        <v>124398951</v>
       </c>
       <c r="B88" t="n">
-        <v>79851</v>
+        <v>79348</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11277,41 +11258,55 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229497</v>
+        <v>1353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444478</v>
+        <v>444424</v>
       </c>
       <c r="R88" t="n">
-        <v>7029836</v>
+        <v>7029691</v>
       </c>
       <c r="S88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11340,7 +11335,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11350,12 +11345,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11370,22 +11365,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124398668</v>
+        <v>124399409</v>
       </c>
       <c r="B89" t="n">
-        <v>79341</v>
+        <v>91282</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11394,50 +11389,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1350</v>
+        <v>73</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444415</v>
+        <v>444464</v>
       </c>
       <c r="R89" t="n">
-        <v>7029660</v>
+        <v>7029781</v>
       </c>
       <c r="S89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11466,7 +11452,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11476,12 +11462,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11496,22 +11482,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124398979</v>
+        <v>124398408</v>
       </c>
       <c r="B90" t="n">
-        <v>91030</v>
+        <v>77743</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11524,46 +11510,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444424</v>
+        <v>444419</v>
       </c>
       <c r="R90" t="n">
-        <v>7029676</v>
+        <v>7029740</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11592,7 +11569,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11602,7 +11579,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11629,7 +11611,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124398327</v>
+        <v>124398979</v>
       </c>
       <c r="B91" t="n">
         <v>91030</v>
@@ -11662,17 +11644,26 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444463</v>
+        <v>444424</v>
       </c>
       <c r="R91" t="n">
-        <v>7029765</v>
+        <v>7029676</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11704,7 +11695,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11714,12 +11705,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11734,22 +11720,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124398839</v>
+        <v>124399850</v>
       </c>
       <c r="B92" t="n">
-        <v>78998</v>
+        <v>79927</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11758,50 +11744,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>230552</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444409</v>
+        <v>444432</v>
       </c>
       <c r="R92" t="n">
-        <v>7029694</v>
+        <v>7029779</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11830,7 +11807,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11840,12 +11817,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11872,10 +11849,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124400074</v>
+        <v>124398297</v>
       </c>
       <c r="B93" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11884,55 +11861,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444429</v>
+        <v>444498</v>
       </c>
       <c r="R93" t="n">
-        <v>7029784</v>
+        <v>7029821</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11961,7 +11924,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11971,12 +11934,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11991,22 +11954,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124399850</v>
+        <v>124398668</v>
       </c>
       <c r="B94" t="n">
-        <v>79927</v>
+        <v>79341</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12015,41 +11978,50 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6464</v>
+        <v>1350</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444432</v>
+        <v>444415</v>
       </c>
       <c r="R94" t="n">
-        <v>7029779</v>
+        <v>7029660</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12078,7 +12050,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12088,12 +12060,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12108,22 +12080,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124399409</v>
+        <v>124399571</v>
       </c>
       <c r="B95" t="n">
-        <v>91282</v>
+        <v>91030</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12136,37 +12108,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444464</v>
+        <v>444478</v>
       </c>
       <c r="R95" t="n">
-        <v>7029781</v>
+        <v>7029836</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12195,7 +12172,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12205,12 +12182,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12225,22 +12202,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124396028</v>
+        <v>124398709</v>
       </c>
       <c r="B96" t="n">
-        <v>79857</v>
+        <v>79348</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12249,41 +12226,50 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229748</v>
+        <v>1353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444402</v>
+        <v>444401</v>
       </c>
       <c r="R96" t="n">
-        <v>7030044</v>
+        <v>7029685</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12312,7 +12298,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12322,7 +12308,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12333,41 +12324,26 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124398748</v>
+        <v>124396024</v>
       </c>
       <c r="B97" t="n">
-        <v>79341</v>
+        <v>79920</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12376,50 +12352,41 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1350</v>
+        <v>6462</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444401</v>
+        <v>444388</v>
       </c>
       <c r="R97" t="n">
-        <v>7029685</v>
+        <v>7030037</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12448,7 +12415,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12458,12 +12425,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12483,17 +12450,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124399357</v>
+        <v>124399273</v>
       </c>
       <c r="B98" t="n">
-        <v>79066</v>
+        <v>91030</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12502,28 +12469,37 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
@@ -12536,7 +12512,7 @@
         <v>7029811</v>
       </c>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12565,7 +12541,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12575,7 +12551,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -12607,10 +12583,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124399819</v>
+        <v>124397463</v>
       </c>
       <c r="B99" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12623,46 +12599,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444478</v>
+        <v>444279</v>
       </c>
       <c r="R99" t="n">
-        <v>7029836</v>
+        <v>7030095</v>
       </c>
       <c r="S99" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12691,7 +12663,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12701,12 +12673,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12726,17 +12698,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124399157</v>
+        <v>124399997</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>79348</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12745,28 +12717,42 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
@@ -12776,7 +12762,7 @@
         <v>444448</v>
       </c>
       <c r="R100" t="n">
-        <v>7029741</v>
+        <v>7029784</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12808,7 +12794,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12818,12 +12804,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12850,10 +12836,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124399597</v>
+        <v>124399656</v>
       </c>
       <c r="B101" t="n">
-        <v>91705</v>
+        <v>79851</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12862,25 +12848,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>67</v>
+        <v>229497</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12890,13 +12876,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444456</v>
+        <v>444478</v>
       </c>
       <c r="R101" t="n">
-        <v>7029772</v>
+        <v>7029836</v>
       </c>
       <c r="S101" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12925,7 +12911,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12935,12 +12921,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12955,22 +12941,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124398408</v>
+        <v>124398327</v>
       </c>
       <c r="B102" t="n">
-        <v>77743</v>
+        <v>91030</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12983,21 +12969,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13007,13 +12993,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444419</v>
+        <v>444463</v>
       </c>
       <c r="R102" t="n">
-        <v>7029740</v>
+        <v>7029765</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13042,7 +13028,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13052,12 +13038,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13072,22 +13058,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124397664</v>
+        <v>124397972</v>
       </c>
       <c r="B103" t="n">
-        <v>95335</v>
+        <v>79341</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13096,38 +13082,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2809</v>
+        <v>1350</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444403</v>
+        <v>444487</v>
       </c>
       <c r="R103" t="n">
-        <v>7030010</v>
+        <v>7029857</v>
       </c>
       <c r="S103" t="n">
         <v>6</v>
@@ -13159,7 +13145,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13169,12 +13155,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13194,17 +13180,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124399273</v>
+        <v>124400074</v>
       </c>
       <c r="B104" t="n">
-        <v>91030</v>
+        <v>79348</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13213,35 +13199,40 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>1353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -13250,13 +13241,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444468</v>
+        <v>444429</v>
       </c>
       <c r="R104" t="n">
-        <v>7029811</v>
+        <v>7029784</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13285,7 +13276,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13295,12 +13286,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13315,22 +13306,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124397876</v>
+        <v>124398748</v>
       </c>
       <c r="B105" t="n">
-        <v>91413</v>
+        <v>79341</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13339,38 +13330,47 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4217</v>
+        <v>1350</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444498</v>
+        <v>444401</v>
       </c>
       <c r="R105" t="n">
-        <v>7029879</v>
+        <v>7029685</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124397876</v>
+        <v>124399157</v>
       </c>
       <c r="B73" t="n">
-        <v>91413</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,38 +9448,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444498</v>
+        <v>444448</v>
       </c>
       <c r="R73" t="n">
-        <v>7029879</v>
+        <v>7029741</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9546,17 +9546,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124399357</v>
+        <v>124397664</v>
       </c>
       <c r="B74" t="n">
-        <v>79066</v>
+        <v>95335</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9569,37 +9569,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6459</v>
+        <v>2809</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444468</v>
+        <v>444403</v>
       </c>
       <c r="R74" t="n">
-        <v>7029811</v>
+        <v>7030010</v>
       </c>
       <c r="S74" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9658,22 +9658,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124398118</v>
+        <v>124398327</v>
       </c>
       <c r="B75" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9682,25 +9682,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9710,13 +9710,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444492</v>
+        <v>444463</v>
       </c>
       <c r="R75" t="n">
-        <v>7029851</v>
+        <v>7029765</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9787,10 +9787,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124396185</v>
+        <v>124397463</v>
       </c>
       <c r="B76" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9803,31 +9803,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9836,13 +9832,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444287</v>
+        <v>444279</v>
       </c>
       <c r="R76" t="n">
-        <v>7030000</v>
+        <v>7030095</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9871,7 +9867,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9881,7 +9877,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9901,17 +9902,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124396061</v>
+        <v>124399997</v>
       </c>
       <c r="B77" t="n">
-        <v>79851</v>
+        <v>79348</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9920,41 +9921,55 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>1353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444402</v>
+        <v>444448</v>
       </c>
       <c r="R77" t="n">
-        <v>7030044</v>
+        <v>7029784</v>
       </c>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9983,7 +9998,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9993,7 +10008,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10004,41 +10024,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>August Nordin, Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124397408</v>
+        <v>124398839</v>
       </c>
       <c r="B78" t="n">
-        <v>79851</v>
+        <v>78998</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10047,41 +10052,50 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229497</v>
+        <v>230552</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444276</v>
+        <v>444409</v>
       </c>
       <c r="R78" t="n">
-        <v>7030094</v>
+        <v>7029694</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10110,7 +10124,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10120,12 +10134,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10145,17 +10159,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124399157</v>
+        <v>124398297</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10164,25 +10178,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10192,13 +10206,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444448</v>
+        <v>444498</v>
       </c>
       <c r="R79" t="n">
-        <v>7029741</v>
+        <v>7029821</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10227,7 +10241,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10237,12 +10251,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10257,22 +10271,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124399597</v>
+        <v>124397972</v>
       </c>
       <c r="B80" t="n">
-        <v>91705</v>
+        <v>79341</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10285,21 +10299,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>67</v>
+        <v>1350</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10309,13 +10323,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444456</v>
+        <v>444487</v>
       </c>
       <c r="R80" t="n">
-        <v>7029772</v>
+        <v>7029857</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10344,7 +10358,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10354,12 +10368,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10379,17 +10393,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124398839</v>
+        <v>124396185</v>
       </c>
       <c r="B81" t="n">
-        <v>78998</v>
+        <v>91030</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10398,50 +10412,50 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>230552</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444409</v>
+        <v>444287</v>
       </c>
       <c r="R81" t="n">
-        <v>7029694</v>
+        <v>7030000</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10470,7 +10484,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10480,12 +10494,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10500,22 +10509,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124399819</v>
+        <v>124399926</v>
       </c>
       <c r="B82" t="n">
-        <v>79891</v>
+        <v>79341</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10524,30 +10533,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>1350</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10596,7 +10605,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10606,12 +10615,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10638,10 +10647,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124396028</v>
+        <v>124399357</v>
       </c>
       <c r="B83" t="n">
-        <v>79857</v>
+        <v>79066</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10654,21 +10663,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229748</v>
+        <v>6459</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10678,13 +10687,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444402</v>
+        <v>444468</v>
       </c>
       <c r="R83" t="n">
-        <v>7030044</v>
+        <v>7029811</v>
       </c>
       <c r="S83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10713,7 +10722,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10723,7 +10732,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10734,21 +10748,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10758,17 +10757,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124399926</v>
+        <v>124397708</v>
       </c>
       <c r="B84" t="n">
-        <v>79341</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10777,30 +10776,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1350</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10814,13 +10813,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444478</v>
+        <v>444403</v>
       </c>
       <c r="R84" t="n">
-        <v>7029836</v>
+        <v>7029971</v>
       </c>
       <c r="S84" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10849,7 +10848,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10859,12 +10858,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På gran, bredvid asp</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10884,17 +10878,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124397664</v>
+        <v>124399571</v>
       </c>
       <c r="B85" t="n">
-        <v>95335</v>
+        <v>91030</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10903,41 +10897,46 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444403</v>
+        <v>444478</v>
       </c>
       <c r="R85" t="n">
-        <v>7030010</v>
+        <v>7029836</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10966,7 +10965,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10976,12 +10975,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10996,22 +10995,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124399091</v>
+        <v>124397876</v>
       </c>
       <c r="B86" t="n">
-        <v>79795</v>
+        <v>91413</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11024,34 +11023,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6456</v>
+        <v>4217</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444439</v>
+        <v>444498</v>
       </c>
       <c r="R86" t="n">
-        <v>7029686</v>
+        <v>7029879</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11083,7 +11082,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11093,12 +11092,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11118,17 +11117,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124397708</v>
+        <v>124396028</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>79857</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11137,50 +11136,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444403</v>
+        <v>444402</v>
       </c>
       <c r="R87" t="n">
-        <v>7029971</v>
+        <v>7030044</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11209,7 +11199,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11219,7 +11209,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11230,6 +11220,21 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11239,17 +11244,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>August Nordin, Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124398951</v>
+        <v>124399091</v>
       </c>
       <c r="B88" t="n">
-        <v>79348</v>
+        <v>79795</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11258,52 +11263,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1353</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444424</v>
+        <v>444439</v>
       </c>
       <c r="R88" t="n">
-        <v>7029691</v>
+        <v>7029686</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11335,7 +11326,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11345,12 +11336,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11370,17 +11361,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124399409</v>
+        <v>124399850</v>
       </c>
       <c r="B89" t="n">
-        <v>91282</v>
+        <v>79927</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11389,25 +11380,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>73</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11417,13 +11408,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444464</v>
+        <v>444432</v>
       </c>
       <c r="R89" t="n">
-        <v>7029781</v>
+        <v>7029779</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11452,7 +11443,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11462,12 +11453,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11494,10 +11485,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124398408</v>
+        <v>124396024</v>
       </c>
       <c r="B90" t="n">
-        <v>77743</v>
+        <v>79920</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11506,25 +11497,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11534,13 +11525,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444419</v>
+        <v>444388</v>
       </c>
       <c r="R90" t="n">
-        <v>7029740</v>
+        <v>7030037</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11569,7 +11560,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11579,12 +11570,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11599,22 +11590,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124398979</v>
+        <v>124398951</v>
       </c>
       <c r="B91" t="n">
-        <v>91030</v>
+        <v>79348</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11623,35 +11614,40 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5432</v>
+        <v>1353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11663,7 +11659,7 @@
         <v>444424</v>
       </c>
       <c r="R91" t="n">
-        <v>7029676</v>
+        <v>7029691</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11695,7 +11691,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11705,7 +11701,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11720,22 +11721,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124399850</v>
+        <v>124398748</v>
       </c>
       <c r="B92" t="n">
-        <v>79927</v>
+        <v>79341</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11744,41 +11745,50 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>1350</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444432</v>
+        <v>444401</v>
       </c>
       <c r="R92" t="n">
-        <v>7029779</v>
+        <v>7029685</v>
       </c>
       <c r="S92" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11807,7 +11817,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11817,12 +11827,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11849,7 +11859,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124398297</v>
+        <v>124399656</v>
       </c>
       <c r="B93" t="n">
         <v>79851</v>
@@ -11889,13 +11899,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444498</v>
+        <v>444478</v>
       </c>
       <c r="R93" t="n">
-        <v>7029821</v>
+        <v>7029836</v>
       </c>
       <c r="S93" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11924,7 +11934,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11934,12 +11944,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11966,10 +11976,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124398668</v>
+        <v>124399409</v>
       </c>
       <c r="B94" t="n">
-        <v>79341</v>
+        <v>91282</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11978,50 +11988,41 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1350</v>
+        <v>73</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444415</v>
+        <v>444464</v>
       </c>
       <c r="R94" t="n">
-        <v>7029660</v>
+        <v>7029781</v>
       </c>
       <c r="S94" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12050,7 +12051,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12060,12 +12061,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12080,22 +12081,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124399571</v>
+        <v>124398118</v>
       </c>
       <c r="B95" t="n">
-        <v>91030</v>
+        <v>91950</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12104,46 +12105,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444478</v>
+        <v>444492</v>
       </c>
       <c r="R95" t="n">
-        <v>7029836</v>
+        <v>7029851</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12172,7 +12168,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12182,12 +12178,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12202,22 +12198,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124398709</v>
+        <v>124398408</v>
       </c>
       <c r="B96" t="n">
-        <v>79348</v>
+        <v>77743</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12226,50 +12222,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1353</v>
+        <v>228579</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444401</v>
+        <v>444419</v>
       </c>
       <c r="R96" t="n">
-        <v>7029685</v>
+        <v>7029740</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12298,7 +12285,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12308,12 +12295,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12328,22 +12315,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124396024</v>
+        <v>124399273</v>
       </c>
       <c r="B97" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12352,41 +12339,50 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444388</v>
+        <v>444468</v>
       </c>
       <c r="R97" t="n">
-        <v>7030037</v>
+        <v>7029811</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12415,7 +12411,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12425,12 +12421,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12445,22 +12441,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124399273</v>
+        <v>124398709</v>
       </c>
       <c r="B98" t="n">
-        <v>91030</v>
+        <v>79348</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12469,35 +12465,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>1353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12506,13 +12502,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444468</v>
+        <v>444401</v>
       </c>
       <c r="R98" t="n">
-        <v>7029811</v>
+        <v>7029685</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12541,7 +12537,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12551,12 +12547,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12571,22 +12567,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124397463</v>
+        <v>124398668</v>
       </c>
       <c r="B99" t="n">
-        <v>91012</v>
+        <v>79341</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12595,46 +12591,50 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1350</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444279</v>
+        <v>444415</v>
       </c>
       <c r="R99" t="n">
-        <v>7030095</v>
+        <v>7029660</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12698,17 +12698,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124399997</v>
+        <v>124397408</v>
       </c>
       <c r="B100" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12717,55 +12717,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444448</v>
+        <v>444276</v>
       </c>
       <c r="R100" t="n">
-        <v>7029784</v>
+        <v>7030094</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12794,7 +12780,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12804,12 +12790,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12836,10 +12822,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124399656</v>
+        <v>124399819</v>
       </c>
       <c r="B101" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12848,28 +12834,37 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
@@ -12911,7 +12906,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12921,12 +12916,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12953,7 +12948,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124398327</v>
+        <v>124398979</v>
       </c>
       <c r="B102" t="n">
         <v>91030</v>
@@ -12986,17 +12981,26 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444463</v>
+        <v>444424</v>
       </c>
       <c r="R102" t="n">
-        <v>7029765</v>
+        <v>7029676</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13028,7 +13032,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13038,12 +13042,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13058,22 +13057,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124397972</v>
+        <v>124396061</v>
       </c>
       <c r="B103" t="n">
-        <v>79341</v>
+        <v>79851</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13082,25 +13081,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1350</v>
+        <v>229497</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13110,13 +13109,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444487</v>
+        <v>444402</v>
       </c>
       <c r="R103" t="n">
-        <v>7029857</v>
+        <v>7030044</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13145,7 +13144,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13155,12 +13154,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13171,26 +13165,41 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>August Nordin, Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124400074</v>
+        <v>124399597</v>
       </c>
       <c r="B104" t="n">
-        <v>79348</v>
+        <v>91705</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13199,55 +13208,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1353</v>
+        <v>67</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444429</v>
+        <v>444456</v>
       </c>
       <c r="R104" t="n">
-        <v>7029784</v>
+        <v>7029772</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13276,7 +13271,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13286,12 +13281,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13318,10 +13313,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124398748</v>
+        <v>124400074</v>
       </c>
       <c r="B105" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13330,25 +13325,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -13361,19 +13356,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444401</v>
+        <v>444429</v>
       </c>
       <c r="R105" t="n">
-        <v>7029685</v>
+        <v>7029784</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124399157</v>
+        <v>124398951</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>79348</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,38 +9448,52 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444448</v>
+        <v>444424</v>
       </c>
       <c r="R73" t="n">
-        <v>7029741</v>
+        <v>7029691</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9511,7 +9525,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9521,12 +9535,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9546,17 +9560,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124397664</v>
+        <v>124397876</v>
       </c>
       <c r="B74" t="n">
-        <v>95335</v>
+        <v>91413</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9569,21 +9583,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2809</v>
+        <v>4217</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9593,13 +9607,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444403</v>
+        <v>444498</v>
       </c>
       <c r="R74" t="n">
-        <v>7030010</v>
+        <v>7029879</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9628,7 +9642,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9638,12 +9652,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9663,17 +9677,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124398327</v>
+        <v>124397408</v>
       </c>
       <c r="B75" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9682,41 +9696,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444463</v>
+        <v>444276</v>
       </c>
       <c r="R75" t="n">
-        <v>7029765</v>
+        <v>7030094</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9745,7 +9759,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9755,12 +9769,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9787,10 +9801,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124397463</v>
+        <v>124398118</v>
       </c>
       <c r="B76" t="n">
-        <v>91012</v>
+        <v>91950</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9799,46 +9813,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444279</v>
+        <v>444492</v>
       </c>
       <c r="R76" t="n">
-        <v>7030095</v>
+        <v>7029851</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9867,7 +9876,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9877,12 +9886,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9897,22 +9906,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124399997</v>
+        <v>124399357</v>
       </c>
       <c r="B77" t="n">
-        <v>79348</v>
+        <v>79066</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9921,55 +9930,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1353</v>
+        <v>6459</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444448</v>
+        <v>444468</v>
       </c>
       <c r="R77" t="n">
-        <v>7029784</v>
+        <v>7029811</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9998,7 +9993,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10008,12 +10003,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10028,22 +10023,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124398839</v>
+        <v>124400074</v>
       </c>
       <c r="B78" t="n">
-        <v>78998</v>
+        <v>79348</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10052,30 +10047,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>230552</v>
+        <v>1353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10083,19 +10078,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444409</v>
+        <v>444429</v>
       </c>
       <c r="R78" t="n">
-        <v>7029694</v>
+        <v>7029784</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10134,12 +10134,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10166,10 +10166,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124398297</v>
+        <v>124399571</v>
       </c>
       <c r="B79" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10178,41 +10178,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444498</v>
+        <v>444478</v>
       </c>
       <c r="R79" t="n">
-        <v>7029821</v>
+        <v>7029836</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10241,7 +10246,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10251,12 +10256,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10283,10 +10288,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124397972</v>
+        <v>124398839</v>
       </c>
       <c r="B80" t="n">
-        <v>79341</v>
+        <v>78998</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10299,37 +10304,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1350</v>
+        <v>230552</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444487</v>
+        <v>444409</v>
       </c>
       <c r="R80" t="n">
-        <v>7029857</v>
+        <v>7029694</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10358,7 +10372,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10368,12 +10382,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10393,17 +10407,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124396185</v>
+        <v>124396024</v>
       </c>
       <c r="B81" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10412,50 +10426,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444287</v>
+        <v>444388</v>
       </c>
       <c r="R81" t="n">
-        <v>7030000</v>
+        <v>7030037</v>
       </c>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10484,7 +10489,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10494,7 +10499,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10509,22 +10519,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124399926</v>
+        <v>124399091</v>
       </c>
       <c r="B82" t="n">
-        <v>79341</v>
+        <v>79795</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10533,50 +10543,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1350</v>
+        <v>6456</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444478</v>
+        <v>444439</v>
       </c>
       <c r="R82" t="n">
-        <v>7029836</v>
+        <v>7029686</v>
       </c>
       <c r="S82" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10605,7 +10606,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10615,12 +10616,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10635,22 +10636,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124399357</v>
+        <v>124396185</v>
       </c>
       <c r="B83" t="n">
-        <v>79066</v>
+        <v>91030</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10659,41 +10660,50 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444468</v>
+        <v>444287</v>
       </c>
       <c r="R83" t="n">
-        <v>7029811</v>
+        <v>7030000</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10722,7 +10732,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10732,12 +10742,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10757,17 +10762,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124397708</v>
+        <v>124398709</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>79348</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10776,30 +10781,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10813,13 +10818,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444403</v>
+        <v>444401</v>
       </c>
       <c r="R84" t="n">
-        <v>7029971</v>
+        <v>7029685</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10848,7 +10853,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10858,7 +10863,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10873,22 +10883,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124399571</v>
+        <v>124397463</v>
       </c>
       <c r="B85" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10901,21 +10911,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10926,17 +10936,17 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444478</v>
+        <v>444279</v>
       </c>
       <c r="R85" t="n">
-        <v>7029836</v>
+        <v>7030095</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10965,7 +10975,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10975,12 +10985,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11000,17 +11010,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124397876</v>
+        <v>124398668</v>
       </c>
       <c r="B86" t="n">
-        <v>91413</v>
+        <v>79341</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11019,41 +11029,50 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4217</v>
+        <v>1350</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444498</v>
+        <v>444415</v>
       </c>
       <c r="R86" t="n">
-        <v>7029879</v>
+        <v>7029660</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11082,7 +11101,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11092,12 +11111,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11112,22 +11131,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124396028</v>
+        <v>124397708</v>
       </c>
       <c r="B87" t="n">
-        <v>79857</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11136,41 +11155,50 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444402</v>
+        <v>444403</v>
       </c>
       <c r="R87" t="n">
-        <v>7030044</v>
+        <v>7029971</v>
       </c>
       <c r="S87" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11199,7 +11227,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11209,7 +11237,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11220,21 +11248,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11244,17 +11257,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>August Nordin, Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124399091</v>
+        <v>124398748</v>
       </c>
       <c r="B88" t="n">
-        <v>79795</v>
+        <v>79341</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11263,38 +11276,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>1350</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444439</v>
+        <v>444401</v>
       </c>
       <c r="R88" t="n">
-        <v>7029686</v>
+        <v>7029685</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11326,7 +11348,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11336,12 +11358,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11361,17 +11383,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124399850</v>
+        <v>124399926</v>
       </c>
       <c r="B89" t="n">
-        <v>79927</v>
+        <v>79341</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11380,41 +11402,50 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6464</v>
+        <v>1350</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444432</v>
+        <v>444478</v>
       </c>
       <c r="R89" t="n">
-        <v>7029779</v>
+        <v>7029836</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11443,7 +11474,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11453,12 +11484,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11473,22 +11504,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124396024</v>
+        <v>124398297</v>
       </c>
       <c r="B90" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11501,21 +11532,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11525,13 +11556,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444388</v>
+        <v>444498</v>
       </c>
       <c r="R90" t="n">
-        <v>7030037</v>
+        <v>7029821</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11560,7 +11591,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11570,12 +11601,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11590,22 +11621,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124398951</v>
+        <v>124399656</v>
       </c>
       <c r="B91" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11614,55 +11645,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444424</v>
+        <v>444478</v>
       </c>
       <c r="R91" t="n">
-        <v>7029691</v>
+        <v>7029836</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11691,7 +11708,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11701,12 +11718,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11721,22 +11738,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124398748</v>
+        <v>124399997</v>
       </c>
       <c r="B92" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11745,25 +11762,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11776,16 +11793,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444401</v>
+        <v>444448</v>
       </c>
       <c r="R92" t="n">
-        <v>7029685</v>
+        <v>7029784</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11817,7 +11839,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11827,12 +11849,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11859,10 +11881,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124399656</v>
+        <v>124399273</v>
       </c>
       <c r="B93" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11871,41 +11893,50 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444478</v>
+        <v>444468</v>
       </c>
       <c r="R93" t="n">
-        <v>7029836</v>
+        <v>7029811</v>
       </c>
       <c r="S93" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11934,7 +11965,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11944,12 +11975,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11976,10 +12007,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124399409</v>
+        <v>124399157</v>
       </c>
       <c r="B94" t="n">
-        <v>91282</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11992,21 +12023,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>73</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12016,10 +12047,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444464</v>
+        <v>444448</v>
       </c>
       <c r="R94" t="n">
-        <v>7029781</v>
+        <v>7029741</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12051,7 +12082,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12061,12 +12092,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12093,10 +12124,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124398118</v>
+        <v>124396028</v>
       </c>
       <c r="B95" t="n">
-        <v>91950</v>
+        <v>79857</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12109,21 +12140,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4769</v>
+        <v>229748</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12133,13 +12164,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444492</v>
+        <v>444402</v>
       </c>
       <c r="R95" t="n">
-        <v>7029851</v>
+        <v>7030044</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12168,7 +12199,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12178,12 +12209,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:48</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12194,26 +12220,41 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124398408</v>
+        <v>124397664</v>
       </c>
       <c r="B96" t="n">
-        <v>77743</v>
+        <v>95335</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12222,41 +12263,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444419</v>
+        <v>444403</v>
       </c>
       <c r="R96" t="n">
-        <v>7029740</v>
+        <v>7030010</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12285,7 +12326,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12295,12 +12336,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12315,22 +12356,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124399273</v>
+        <v>124397972</v>
       </c>
       <c r="B97" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12339,50 +12380,41 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444468</v>
+        <v>444487</v>
       </c>
       <c r="R97" t="n">
-        <v>7029811</v>
+        <v>7029857</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12411,7 +12443,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12421,12 +12453,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12441,22 +12473,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124398709</v>
+        <v>124399850</v>
       </c>
       <c r="B98" t="n">
-        <v>79348</v>
+        <v>79927</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12465,50 +12497,41 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1353</v>
+        <v>6464</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444401</v>
+        <v>444432</v>
       </c>
       <c r="R98" t="n">
-        <v>7029685</v>
+        <v>7029779</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12537,7 +12560,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12547,12 +12570,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12579,10 +12602,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124398668</v>
+        <v>124396061</v>
       </c>
       <c r="B99" t="n">
-        <v>79341</v>
+        <v>79851</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12591,50 +12614,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1350</v>
+        <v>229497</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444415</v>
+        <v>444402</v>
       </c>
       <c r="R99" t="n">
-        <v>7029660</v>
+        <v>7030044</v>
       </c>
       <c r="S99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12663,7 +12677,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12673,12 +12687,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12689,6 +12698,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -12698,17 +12722,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124397408</v>
+        <v>124398327</v>
       </c>
       <c r="B100" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12717,41 +12741,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444276</v>
+        <v>444463</v>
       </c>
       <c r="R100" t="n">
-        <v>7030094</v>
+        <v>7029765</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12780,7 +12804,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12790,12 +12814,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12822,10 +12846,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124399819</v>
+        <v>124398408</v>
       </c>
       <c r="B101" t="n">
-        <v>79891</v>
+        <v>77743</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12838,46 +12862,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444478</v>
+        <v>444419</v>
       </c>
       <c r="R101" t="n">
-        <v>7029836</v>
+        <v>7029740</v>
       </c>
       <c r="S101" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12906,7 +12921,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12916,12 +12931,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13069,10 +13084,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124396061</v>
+        <v>124399409</v>
       </c>
       <c r="B103" t="n">
-        <v>79851</v>
+        <v>91282</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13081,25 +13096,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229497</v>
+        <v>73</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13109,13 +13124,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444402</v>
+        <v>444464</v>
       </c>
       <c r="R103" t="n">
-        <v>7030044</v>
+        <v>7029781</v>
       </c>
       <c r="S103" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13144,7 +13159,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13154,7 +13169,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13165,31 +13185,16 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>August Nordin, Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -13313,10 +13318,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124400074</v>
+        <v>124399819</v>
       </c>
       <c r="B105" t="n">
-        <v>79348</v>
+        <v>79891</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13325,25 +13330,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1353</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -13356,24 +13361,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444429</v>
+        <v>444478</v>
       </c>
       <c r="R105" t="n">
-        <v>7029784</v>
+        <v>7029836</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13432,12 +13432,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9567,10 +9567,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124397876</v>
+        <v>124397972</v>
       </c>
       <c r="B74" t="n">
-        <v>91413</v>
+        <v>79341</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9579,41 +9579,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4217</v>
+        <v>1350</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444498</v>
+        <v>444487</v>
       </c>
       <c r="R74" t="n">
-        <v>7029879</v>
+        <v>7029857</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9677,17 +9677,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124397408</v>
+        <v>124398709</v>
       </c>
       <c r="B75" t="n">
-        <v>79851</v>
+        <v>79348</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9696,41 +9696,50 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>1353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444276</v>
+        <v>444401</v>
       </c>
       <c r="R75" t="n">
-        <v>7030094</v>
+        <v>7029685</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9759,7 +9768,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9769,12 +9778,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9794,17 +9803,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124398118</v>
+        <v>124399656</v>
       </c>
       <c r="B76" t="n">
-        <v>91950</v>
+        <v>79851</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9817,21 +9826,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4769</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9841,13 +9850,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444492</v>
+        <v>444478</v>
       </c>
       <c r="R76" t="n">
-        <v>7029851</v>
+        <v>7029836</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9876,7 +9885,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9886,12 +9895,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9906,22 +9915,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124399357</v>
+        <v>124398118</v>
       </c>
       <c r="B77" t="n">
-        <v>79066</v>
+        <v>91950</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9934,21 +9943,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6459</v>
+        <v>4769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9958,13 +9967,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444468</v>
+        <v>444492</v>
       </c>
       <c r="R77" t="n">
-        <v>7029811</v>
+        <v>7029851</v>
       </c>
       <c r="S77" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9993,7 +10002,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10003,12 +10012,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10023,22 +10032,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124400074</v>
+        <v>124397463</v>
       </c>
       <c r="B78" t="n">
-        <v>79348</v>
+        <v>91012</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10047,55 +10056,46 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1353</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444429</v>
+        <v>444279</v>
       </c>
       <c r="R78" t="n">
-        <v>7029784</v>
+        <v>7030095</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10134,12 +10134,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10154,22 +10154,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124399571</v>
+        <v>124396028</v>
       </c>
       <c r="B79" t="n">
-        <v>91030</v>
+        <v>79857</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10178,46 +10178,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>229748</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444478</v>
+        <v>444402</v>
       </c>
       <c r="R79" t="n">
-        <v>7029836</v>
+        <v>7030044</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10246,7 +10241,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10256,12 +10251,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10272,6 +10262,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -10281,17 +10286,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124398839</v>
+        <v>124399850</v>
       </c>
       <c r="B80" t="n">
-        <v>78998</v>
+        <v>79927</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10300,50 +10305,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>230552</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444409</v>
+        <v>444432</v>
       </c>
       <c r="R80" t="n">
-        <v>7029694</v>
+        <v>7029779</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10372,7 +10368,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10382,12 +10378,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10414,10 +10410,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124396024</v>
+        <v>124399409</v>
       </c>
       <c r="B81" t="n">
-        <v>79920</v>
+        <v>91282</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10426,25 +10422,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>73</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10454,13 +10450,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444388</v>
+        <v>444464</v>
       </c>
       <c r="R81" t="n">
-        <v>7030037</v>
+        <v>7029781</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10489,7 +10485,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10499,12 +10495,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10524,17 +10520,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124399091</v>
+        <v>124398668</v>
       </c>
       <c r="B82" t="n">
-        <v>79795</v>
+        <v>79341</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10543,41 +10539,50 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6456</v>
+        <v>1350</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444439</v>
+        <v>444415</v>
       </c>
       <c r="R82" t="n">
-        <v>7029686</v>
+        <v>7029660</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10606,7 +10611,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10616,12 +10621,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10636,7 +10641,7 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -10648,10 +10653,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124396185</v>
+        <v>124396024</v>
       </c>
       <c r="B83" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10660,50 +10665,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444287</v>
+        <v>444388</v>
       </c>
       <c r="R83" t="n">
-        <v>7030000</v>
+        <v>7030037</v>
       </c>
       <c r="S83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10732,7 +10728,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10742,7 +10738,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10757,22 +10758,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124398709</v>
+        <v>124398297</v>
       </c>
       <c r="B84" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10781,50 +10782,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444401</v>
+        <v>444498</v>
       </c>
       <c r="R84" t="n">
-        <v>7029685</v>
+        <v>7029821</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10853,7 +10845,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10863,12 +10855,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10883,22 +10875,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124397463</v>
+        <v>124397408</v>
       </c>
       <c r="B85" t="n">
-        <v>91012</v>
+        <v>79851</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10907,46 +10899,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444279</v>
+        <v>444276</v>
       </c>
       <c r="R85" t="n">
-        <v>7030095</v>
+        <v>7030094</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10975,7 +10962,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10985,12 +10972,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11005,22 +10992,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124398668</v>
+        <v>124399091</v>
       </c>
       <c r="B86" t="n">
-        <v>79341</v>
+        <v>79795</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11029,50 +11016,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1350</v>
+        <v>6456</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444415</v>
+        <v>444439</v>
       </c>
       <c r="R86" t="n">
-        <v>7029660</v>
+        <v>7029686</v>
       </c>
       <c r="S86" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11101,7 +11079,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11111,12 +11089,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11131,22 +11109,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124397708</v>
+        <v>124399357</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>79066</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11155,50 +11133,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444403</v>
+        <v>444468</v>
       </c>
       <c r="R87" t="n">
-        <v>7029971</v>
+        <v>7029811</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11227,7 +11196,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11237,7 +11206,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11257,17 +11231,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124398748</v>
+        <v>124398327</v>
       </c>
       <c r="B88" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11276,47 +11250,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444401</v>
+        <v>444463</v>
       </c>
       <c r="R88" t="n">
-        <v>7029685</v>
+        <v>7029765</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11348,7 +11313,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11358,12 +11323,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11390,10 +11355,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124399926</v>
+        <v>124399819</v>
       </c>
       <c r="B89" t="n">
-        <v>79341</v>
+        <v>79891</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11402,30 +11367,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1350</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11474,7 +11439,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11484,12 +11449,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11516,10 +11481,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124398297</v>
+        <v>124399597</v>
       </c>
       <c r="B90" t="n">
-        <v>79851</v>
+        <v>91705</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11528,25 +11493,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229497</v>
+        <v>67</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11556,13 +11521,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444498</v>
+        <v>444456</v>
       </c>
       <c r="R90" t="n">
-        <v>7029821</v>
+        <v>7029772</v>
       </c>
       <c r="S90" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11591,7 +11556,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11601,12 +11566,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11621,22 +11586,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124399656</v>
+        <v>124398839</v>
       </c>
       <c r="B91" t="n">
-        <v>79851</v>
+        <v>78998</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11645,41 +11610,50 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
+        <v>230552</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444478</v>
+        <v>444409</v>
       </c>
       <c r="R91" t="n">
-        <v>7029836</v>
+        <v>7029694</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11708,7 +11682,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11718,12 +11692,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11738,22 +11712,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124399997</v>
+        <v>124398748</v>
       </c>
       <c r="B92" t="n">
-        <v>79348</v>
+        <v>79341</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11762,25 +11736,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11793,21 +11767,16 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444448</v>
+        <v>444401</v>
       </c>
       <c r="R92" t="n">
-        <v>7029784</v>
+        <v>7029685</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11839,7 +11808,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11849,12 +11818,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11881,10 +11850,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124399273</v>
+        <v>124397708</v>
       </c>
       <c r="B93" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11897,31 +11866,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11930,13 +11899,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444468</v>
+        <v>444403</v>
       </c>
       <c r="R93" t="n">
-        <v>7029811</v>
+        <v>7029971</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11965,7 +11934,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11975,12 +11944,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12000,17 +11964,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124399157</v>
+        <v>124397664</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12019,41 +11983,41 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444448</v>
+        <v>444403</v>
       </c>
       <c r="R94" t="n">
-        <v>7029741</v>
+        <v>7030010</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12082,7 +12046,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12092,12 +12056,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12117,17 +12081,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124396028</v>
+        <v>124398408</v>
       </c>
       <c r="B95" t="n">
-        <v>79857</v>
+        <v>77743</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12136,25 +12100,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229748</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12164,13 +12128,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444402</v>
+        <v>444419</v>
       </c>
       <c r="R95" t="n">
-        <v>7030044</v>
+        <v>7029740</v>
       </c>
       <c r="S95" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12199,7 +12163,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12209,7 +12173,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12220,21 +12189,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12244,17 +12198,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124397664</v>
+        <v>124399273</v>
       </c>
       <c r="B96" t="n">
-        <v>95335</v>
+        <v>91030</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12263,41 +12217,50 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444403</v>
+        <v>444468</v>
       </c>
       <c r="R96" t="n">
-        <v>7030010</v>
+        <v>7029811</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12326,7 +12289,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12336,12 +12299,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12356,22 +12319,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Emil Nordin, Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124397972</v>
+        <v>124396061</v>
       </c>
       <c r="B97" t="n">
-        <v>79341</v>
+        <v>79851</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12380,25 +12343,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1350</v>
+        <v>229497</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12408,13 +12371,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444487</v>
+        <v>444402</v>
       </c>
       <c r="R97" t="n">
-        <v>7029857</v>
+        <v>7030044</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12443,7 +12406,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12453,12 +12416,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12469,26 +12427,41 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124399850</v>
+        <v>124398979</v>
       </c>
       <c r="B98" t="n">
-        <v>79927</v>
+        <v>91030</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12497,41 +12470,50 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444432</v>
+        <v>444424</v>
       </c>
       <c r="R98" t="n">
-        <v>7029779</v>
+        <v>7029676</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12560,7 +12542,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12570,12 +12552,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12590,22 +12567,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124396061</v>
+        <v>124399571</v>
       </c>
       <c r="B99" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12614,41 +12591,46 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444402</v>
+        <v>444478</v>
       </c>
       <c r="R99" t="n">
-        <v>7030044</v>
+        <v>7029836</v>
       </c>
       <c r="S99" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12677,7 +12659,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12687,7 +12669,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12698,21 +12685,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -12722,17 +12694,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124398327</v>
+        <v>124399926</v>
       </c>
       <c r="B100" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12741,41 +12713,50 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444463</v>
+        <v>444478</v>
       </c>
       <c r="R100" t="n">
-        <v>7029765</v>
+        <v>7029836</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12804,7 +12785,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12814,12 +12795,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12834,7 +12815,7 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
@@ -12846,10 +12827,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124398408</v>
+        <v>124400074</v>
       </c>
       <c r="B101" t="n">
-        <v>77743</v>
+        <v>79348</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12858,41 +12839,55 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228579</v>
+        <v>1353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444419</v>
+        <v>444429</v>
       </c>
       <c r="R101" t="n">
-        <v>7029740</v>
+        <v>7029784</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12921,7 +12916,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12931,12 +12926,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12951,22 +12946,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124398979</v>
+        <v>124397876</v>
       </c>
       <c r="B102" t="n">
-        <v>91030</v>
+        <v>91413</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12975,47 +12970,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444424</v>
+        <v>444498</v>
       </c>
       <c r="R102" t="n">
-        <v>7029676</v>
+        <v>7029879</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13047,7 +13033,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13057,7 +13043,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13072,22 +13063,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124399409</v>
+        <v>124396185</v>
       </c>
       <c r="B103" t="n">
-        <v>91282</v>
+        <v>91030</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13100,37 +13091,46 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444464</v>
+        <v>444287</v>
       </c>
       <c r="R103" t="n">
-        <v>7029781</v>
+        <v>7030000</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13169,12 +13169,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13189,22 +13184,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124399597</v>
+        <v>124399997</v>
       </c>
       <c r="B104" t="n">
-        <v>91705</v>
+        <v>79348</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13213,41 +13208,55 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>67</v>
+        <v>1353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444456</v>
+        <v>444448</v>
       </c>
       <c r="R104" t="n">
-        <v>7029772</v>
+        <v>7029784</v>
       </c>
       <c r="S104" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13276,7 +13285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13286,12 +13295,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13318,10 +13327,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124399819</v>
+        <v>124399157</v>
       </c>
       <c r="B105" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13334,46 +13343,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444478</v>
+        <v>444448</v>
       </c>
       <c r="R105" t="n">
-        <v>7029836</v>
+        <v>7029741</v>
       </c>
       <c r="S105" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13432,12 +13432,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -10653,10 +10653,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124396024</v>
+        <v>124398297</v>
       </c>
       <c r="B83" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10669,21 +10669,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10693,13 +10693,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444388</v>
+        <v>444498</v>
       </c>
       <c r="R83" t="n">
-        <v>7030037</v>
+        <v>7029821</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10738,12 +10738,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10758,22 +10758,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124398297</v>
+        <v>124396024</v>
       </c>
       <c r="B84" t="n">
-        <v>79851</v>
+        <v>79920</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10810,13 +10810,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444498</v>
+        <v>444388</v>
       </c>
       <c r="R84" t="n">
-        <v>7029821</v>
+        <v>7030037</v>
       </c>
       <c r="S84" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10855,12 +10855,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10875,12 +10875,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -11238,10 +11238,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124398327</v>
+        <v>124399819</v>
       </c>
       <c r="B88" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11254,37 +11254,46 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444463</v>
+        <v>444478</v>
       </c>
       <c r="R88" t="n">
-        <v>7029765</v>
+        <v>7029836</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11313,7 +11322,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11323,12 +11332,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11343,22 +11352,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124399819</v>
+        <v>124398327</v>
       </c>
       <c r="B89" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11371,46 +11380,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444478</v>
+        <v>444463</v>
       </c>
       <c r="R89" t="n">
-        <v>7029836</v>
+        <v>7029765</v>
       </c>
       <c r="S89" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11449,12 +11449,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11469,22 +11469,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124399597</v>
+        <v>124398839</v>
       </c>
       <c r="B90" t="n">
-        <v>91705</v>
+        <v>78998</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11497,37 +11497,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>67</v>
+        <v>230552</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444456</v>
+        <v>444409</v>
       </c>
       <c r="R90" t="n">
-        <v>7029772</v>
+        <v>7029694</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11556,7 +11565,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11566,12 +11575,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11598,10 +11607,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124398839</v>
+        <v>124399597</v>
       </c>
       <c r="B91" t="n">
-        <v>78998</v>
+        <v>91705</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11614,46 +11623,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>230552</v>
+        <v>67</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444409</v>
+        <v>444456</v>
       </c>
       <c r="R91" t="n">
-        <v>7029694</v>
+        <v>7029772</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11692,12 +11692,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12579,10 +12579,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124399571</v>
+        <v>124399926</v>
       </c>
       <c r="B99" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12591,31 +12591,35 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12630,7 +12634,7 @@
         <v>7029836</v>
       </c>
       <c r="S99" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12659,7 +12663,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12669,12 +12673,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12694,17 +12698,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124399926</v>
+        <v>124399571</v>
       </c>
       <c r="B100" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12713,35 +12717,31 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12756,7 +12756,7 @@
         <v>7029836</v>
       </c>
       <c r="S100" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -13196,10 +13196,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124399997</v>
+        <v>124399157</v>
       </c>
       <c r="B104" t="n">
-        <v>79348</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13208,42 +13208,28 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
@@ -13253,7 +13239,7 @@
         <v>444448</v>
       </c>
       <c r="R104" t="n">
-        <v>7029784</v>
+        <v>7029741</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13285,7 +13271,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13295,12 +13281,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13327,10 +13313,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124399157</v>
+        <v>124399997</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>79348</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13339,28 +13325,42 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
@@ -13370,7 +13370,7 @@
         <v>444448</v>
       </c>
       <c r="R105" t="n">
-        <v>7029741</v>
+        <v>7029784</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124398951</v>
+        <v>124397876</v>
       </c>
       <c r="B73" t="n">
-        <v>79348</v>
+        <v>91413</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,52 +9448,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1353</v>
+        <v>4217</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444424</v>
+        <v>444498</v>
       </c>
       <c r="R73" t="n">
-        <v>7029691</v>
+        <v>7029879</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9525,7 +9511,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9535,12 +9521,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9560,7 +9546,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9684,10 +9670,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124398709</v>
+        <v>124399597</v>
       </c>
       <c r="B75" t="n">
-        <v>79348</v>
+        <v>91705</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9696,50 +9682,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1353</v>
+        <v>67</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444401</v>
+        <v>444456</v>
       </c>
       <c r="R75" t="n">
-        <v>7029685</v>
+        <v>7029772</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9768,7 +9745,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9778,12 +9755,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9803,17 +9780,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124399656</v>
+        <v>124399926</v>
       </c>
       <c r="B76" t="n">
-        <v>79851</v>
+        <v>79341</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9822,28 +9799,37 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>1350</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
@@ -9885,7 +9871,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9895,12 +9881,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9927,10 +9913,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124398118</v>
+        <v>124398951</v>
       </c>
       <c r="B77" t="n">
-        <v>91950</v>
+        <v>79348</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9939,41 +9925,55 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>1353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444492</v>
+        <v>444424</v>
       </c>
       <c r="R77" t="n">
-        <v>7029851</v>
+        <v>7029691</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10044,10 +10044,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124397463</v>
+        <v>124396028</v>
       </c>
       <c r="B78" t="n">
-        <v>91012</v>
+        <v>79857</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10056,46 +10056,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>229748</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444279</v>
+        <v>444402</v>
       </c>
       <c r="R78" t="n">
-        <v>7030095</v>
+        <v>7030044</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10124,7 +10119,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10134,12 +10129,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10150,6 +10140,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -10159,17 +10164,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124396028</v>
+        <v>124398297</v>
       </c>
       <c r="B79" t="n">
-        <v>79857</v>
+        <v>79851</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10182,21 +10187,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229748</v>
+        <v>229497</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10206,13 +10211,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444402</v>
+        <v>444498</v>
       </c>
       <c r="R79" t="n">
-        <v>7030044</v>
+        <v>7029821</v>
       </c>
       <c r="S79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10241,7 +10246,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10251,7 +10256,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10262,21 +10272,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -10286,17 +10281,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124399850</v>
+        <v>124398408</v>
       </c>
       <c r="B80" t="n">
-        <v>79927</v>
+        <v>77743</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10305,25 +10300,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10333,13 +10328,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444432</v>
+        <v>444419</v>
       </c>
       <c r="R80" t="n">
-        <v>7029779</v>
+        <v>7029740</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10368,7 +10363,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10378,12 +10373,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10398,22 +10393,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124399409</v>
+        <v>124399157</v>
       </c>
       <c r="B81" t="n">
-        <v>91282</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10426,21 +10421,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>73</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10450,10 +10445,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444464</v>
+        <v>444448</v>
       </c>
       <c r="R81" t="n">
-        <v>7029781</v>
+        <v>7029741</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10485,7 +10480,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10495,12 +10490,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10520,14 +10515,14 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124398668</v>
+        <v>124398748</v>
       </c>
       <c r="B82" t="n">
         <v>79341</v>
@@ -10562,7 +10557,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10576,13 +10571,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444415</v>
+        <v>444401</v>
       </c>
       <c r="R82" t="n">
-        <v>7029660</v>
+        <v>7029685</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10611,7 +10606,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10621,12 +10616,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10641,7 +10636,7 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -10653,10 +10648,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124398297</v>
+        <v>124396185</v>
       </c>
       <c r="B83" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10665,41 +10660,50 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444498</v>
+        <v>444287</v>
       </c>
       <c r="R83" t="n">
-        <v>7029821</v>
+        <v>7030000</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10728,7 +10732,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10738,12 +10742,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gråal</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10763,17 +10762,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124396024</v>
+        <v>124398839</v>
       </c>
       <c r="B84" t="n">
-        <v>79920</v>
+        <v>78998</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10782,41 +10781,50 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>230552</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444388</v>
+        <v>444409</v>
       </c>
       <c r="R84" t="n">
-        <v>7030037</v>
+        <v>7029694</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10845,7 +10853,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10855,12 +10863,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10880,17 +10888,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124397408</v>
+        <v>124399850</v>
       </c>
       <c r="B85" t="n">
-        <v>79851</v>
+        <v>79927</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10903,37 +10911,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444276</v>
+        <v>444432</v>
       </c>
       <c r="R85" t="n">
-        <v>7030094</v>
+        <v>7029779</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10962,7 +10970,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10972,12 +10980,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11004,10 +11012,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124399091</v>
+        <v>124397408</v>
       </c>
       <c r="B86" t="n">
-        <v>79795</v>
+        <v>79851</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11020,37 +11028,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444439</v>
+        <v>444276</v>
       </c>
       <c r="R86" t="n">
-        <v>7029686</v>
+        <v>7030094</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11079,7 +11087,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11089,12 +11097,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11121,10 +11129,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124399357</v>
+        <v>124396061</v>
       </c>
       <c r="B87" t="n">
-        <v>79066</v>
+        <v>79851</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11137,21 +11145,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6459</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11161,13 +11169,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444468</v>
+        <v>444402</v>
       </c>
       <c r="R87" t="n">
-        <v>7029811</v>
+        <v>7030044</v>
       </c>
       <c r="S87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11196,7 +11204,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11206,12 +11214,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11222,6 +11225,21 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11231,17 +11249,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124399819</v>
+        <v>124397708</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11254,26 +11272,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11287,13 +11305,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444478</v>
+        <v>444403</v>
       </c>
       <c r="R88" t="n">
-        <v>7029836</v>
+        <v>7029971</v>
       </c>
       <c r="S88" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11322,7 +11340,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11332,12 +11350,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11357,17 +11370,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124398327</v>
+        <v>124398118</v>
       </c>
       <c r="B89" t="n">
-        <v>91030</v>
+        <v>91950</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11376,25 +11389,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11404,13 +11417,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444463</v>
+        <v>444492</v>
       </c>
       <c r="R89" t="n">
-        <v>7029765</v>
+        <v>7029851</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11439,7 +11452,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11449,12 +11462,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11474,17 +11487,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124398839</v>
+        <v>124397463</v>
       </c>
       <c r="B90" t="n">
-        <v>78998</v>
+        <v>91012</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11493,47 +11506,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>230552</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444409</v>
+        <v>444279</v>
       </c>
       <c r="R90" t="n">
-        <v>7029694</v>
+        <v>7030095</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11565,7 +11574,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11575,12 +11584,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11595,22 +11604,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124399597</v>
+        <v>124398709</v>
       </c>
       <c r="B91" t="n">
-        <v>91705</v>
+        <v>79348</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11619,41 +11628,50 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>67</v>
+        <v>1353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444456</v>
+        <v>444401</v>
       </c>
       <c r="R91" t="n">
-        <v>7029772</v>
+        <v>7029685</v>
       </c>
       <c r="S91" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11682,7 +11700,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11692,12 +11710,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11724,10 +11742,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124398748</v>
+        <v>124398979</v>
       </c>
       <c r="B92" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11736,35 +11754,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11773,10 +11791,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444401</v>
+        <v>444424</v>
       </c>
       <c r="R92" t="n">
-        <v>7029685</v>
+        <v>7029676</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11808,7 +11826,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11818,12 +11836,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11838,22 +11851,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124397708</v>
+        <v>124398327</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11866,46 +11879,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444403</v>
+        <v>444463</v>
       </c>
       <c r="R93" t="n">
-        <v>7029971</v>
+        <v>7029765</v>
       </c>
       <c r="S93" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11934,7 +11938,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11944,7 +11948,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11959,22 +11968,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124397664</v>
+        <v>124399571</v>
       </c>
       <c r="B94" t="n">
-        <v>95335</v>
+        <v>91030</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11983,41 +11992,46 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444403</v>
+        <v>444478</v>
       </c>
       <c r="R94" t="n">
-        <v>7030010</v>
+        <v>7029836</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12046,7 +12060,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12056,12 +12070,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12076,22 +12090,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124398408</v>
+        <v>124399357</v>
       </c>
       <c r="B95" t="n">
-        <v>77743</v>
+        <v>79066</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12100,25 +12114,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>6459</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12128,13 +12142,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444419</v>
+        <v>444468</v>
       </c>
       <c r="R95" t="n">
-        <v>7029740</v>
+        <v>7029811</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12163,7 +12177,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12173,12 +12187,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12198,17 +12212,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124399273</v>
+        <v>124399819</v>
       </c>
       <c r="B96" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12221,31 +12235,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -12254,13 +12268,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444468</v>
+        <v>444478</v>
       </c>
       <c r="R96" t="n">
-        <v>7029811</v>
+        <v>7029836</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12289,7 +12303,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12299,12 +12313,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12331,10 +12345,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124396061</v>
+        <v>124396024</v>
       </c>
       <c r="B97" t="n">
-        <v>79851</v>
+        <v>79920</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12347,21 +12361,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12371,13 +12385,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444402</v>
+        <v>444388</v>
       </c>
       <c r="R97" t="n">
-        <v>7030044</v>
+        <v>7030037</v>
       </c>
       <c r="S97" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12419,6 +12433,11 @@
           <t>15:44</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12427,41 +12446,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124398979</v>
+        <v>124398668</v>
       </c>
       <c r="B98" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12470,35 +12474,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12507,13 +12511,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444424</v>
+        <v>444415</v>
       </c>
       <c r="R98" t="n">
-        <v>7029676</v>
+        <v>7029660</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12542,7 +12546,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12552,7 +12556,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12579,10 +12588,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124399926</v>
+        <v>124399656</v>
       </c>
       <c r="B99" t="n">
-        <v>79341</v>
+        <v>79851</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12591,37 +12600,28 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1350</v>
+        <v>229497</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12698,17 +12698,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124399571</v>
+        <v>124399091</v>
       </c>
       <c r="B100" t="n">
-        <v>91030</v>
+        <v>79795</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12717,46 +12717,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444478</v>
+        <v>444439</v>
       </c>
       <c r="R100" t="n">
-        <v>7029836</v>
+        <v>7029686</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12785,7 +12780,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12795,12 +12790,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12815,12 +12810,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12958,10 +12953,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124397876</v>
+        <v>124399997</v>
       </c>
       <c r="B102" t="n">
-        <v>91413</v>
+        <v>79348</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12970,38 +12965,52 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4217</v>
+        <v>1353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444498</v>
+        <v>444448</v>
       </c>
       <c r="R102" t="n">
-        <v>7029879</v>
+        <v>7029784</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13033,7 +13042,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13043,12 +13052,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13068,17 +13077,17 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124396185</v>
+        <v>124399409</v>
       </c>
       <c r="B103" t="n">
-        <v>91030</v>
+        <v>91282</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13091,46 +13100,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444287</v>
+        <v>444464</v>
       </c>
       <c r="R103" t="n">
-        <v>7030000</v>
+        <v>7029781</v>
       </c>
       <c r="S103" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13169,7 +13169,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13184,22 +13189,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124399157</v>
+        <v>124399273</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13212,37 +13217,46 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444448</v>
+        <v>444468</v>
       </c>
       <c r="R104" t="n">
-        <v>7029741</v>
+        <v>7029811</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13271,7 +13285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13281,12 +13295,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13301,22 +13315,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124399997</v>
+        <v>124397664</v>
       </c>
       <c r="B105" t="n">
-        <v>79348</v>
+        <v>95335</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13325,55 +13339,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1353</v>
+        <v>2809</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444448</v>
+        <v>444403</v>
       </c>
       <c r="R105" t="n">
-        <v>7029784</v>
+        <v>7030010</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -10769,10 +10769,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124398839</v>
+        <v>124399850</v>
       </c>
       <c r="B84" t="n">
-        <v>78998</v>
+        <v>79927</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10781,50 +10781,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>230552</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444409</v>
+        <v>444432</v>
       </c>
       <c r="R84" t="n">
-        <v>7029694</v>
+        <v>7029779</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10853,7 +10844,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10863,12 +10854,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10895,10 +10886,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124399850</v>
+        <v>124398839</v>
       </c>
       <c r="B85" t="n">
-        <v>79927</v>
+        <v>78998</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10907,41 +10898,50 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6464</v>
+        <v>230552</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444432</v>
+        <v>444409</v>
       </c>
       <c r="R85" t="n">
-        <v>7029779</v>
+        <v>7029694</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11129,10 +11129,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124396061</v>
+        <v>124397708</v>
       </c>
       <c r="B87" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11141,41 +11141,50 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444402</v>
+        <v>444403</v>
       </c>
       <c r="R87" t="n">
-        <v>7030044</v>
+        <v>7029971</v>
       </c>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11204,7 +11213,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11214,7 +11223,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11225,21 +11234,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11249,17 +11243,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124397708</v>
+        <v>124396061</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11268,50 +11262,41 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444403</v>
+        <v>444402</v>
       </c>
       <c r="R88" t="n">
-        <v>7029971</v>
+        <v>7030044</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11340,7 +11325,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11350,7 +11335,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11361,6 +11346,21 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -10769,10 +10769,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124399850</v>
+        <v>124398839</v>
       </c>
       <c r="B84" t="n">
-        <v>79927</v>
+        <v>78998</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10781,41 +10781,50 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6464</v>
+        <v>230552</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444432</v>
+        <v>444409</v>
       </c>
       <c r="R84" t="n">
-        <v>7029779</v>
+        <v>7029694</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10844,7 +10853,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10854,12 +10863,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10886,10 +10895,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124398839</v>
+        <v>124399850</v>
       </c>
       <c r="B85" t="n">
-        <v>78998</v>
+        <v>79927</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10898,50 +10907,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>230552</v>
+        <v>6464</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444409</v>
+        <v>444432</v>
       </c>
       <c r="R85" t="n">
-        <v>7029694</v>
+        <v>7029779</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11129,10 +11129,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124397708</v>
+        <v>124396061</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11141,50 +11141,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444403</v>
+        <v>444402</v>
       </c>
       <c r="R87" t="n">
-        <v>7029971</v>
+        <v>7030044</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11213,7 +11204,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11223,7 +11214,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11234,6 +11225,21 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11243,17 +11249,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124396061</v>
+        <v>124397708</v>
       </c>
       <c r="B88" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11262,41 +11268,50 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444402</v>
+        <v>444403</v>
       </c>
       <c r="R88" t="n">
-        <v>7030044</v>
+        <v>7029971</v>
       </c>
       <c r="S88" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11325,7 +11340,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11335,7 +11350,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11346,21 +11361,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -11742,10 +11742,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124398979</v>
+        <v>124399357</v>
       </c>
       <c r="B92" t="n">
-        <v>91030</v>
+        <v>79066</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11754,50 +11754,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444424</v>
+        <v>444468</v>
       </c>
       <c r="R92" t="n">
-        <v>7029676</v>
+        <v>7029811</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11826,7 +11817,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11836,7 +11827,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11856,17 +11852,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124398327</v>
+        <v>124399819</v>
       </c>
       <c r="B93" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11879,37 +11875,46 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444463</v>
+        <v>444478</v>
       </c>
       <c r="R93" t="n">
-        <v>7029765</v>
+        <v>7029836</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11938,7 +11943,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11948,12 +11953,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11968,19 +11973,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124399571</v>
+        <v>124398979</v>
       </c>
       <c r="B94" t="n">
         <v>91030</v>
@@ -12013,10 +12018,14 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -12025,13 +12034,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444478</v>
+        <v>444424</v>
       </c>
       <c r="R94" t="n">
-        <v>7029836</v>
+        <v>7029676</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12060,7 +12069,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12070,12 +12079,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12102,10 +12106,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124399357</v>
+        <v>124398327</v>
       </c>
       <c r="B95" t="n">
-        <v>79066</v>
+        <v>91030</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12114,25 +12118,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12142,13 +12146,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444468</v>
+        <v>444463</v>
       </c>
       <c r="R95" t="n">
-        <v>7029811</v>
+        <v>7029765</v>
       </c>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12177,7 +12181,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12187,12 +12191,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12207,7 +12211,7 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
@@ -12219,10 +12223,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124399819</v>
+        <v>124399571</v>
       </c>
       <c r="B96" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12235,31 +12239,27 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -12274,7 +12274,7 @@
         <v>7029836</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12313,12 +12313,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12345,10 +12345,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124396024</v>
+        <v>124399656</v>
       </c>
       <c r="B97" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12361,21 +12361,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12385,13 +12385,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444388</v>
+        <v>444478</v>
       </c>
       <c r="R97" t="n">
-        <v>7030037</v>
+        <v>7029836</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12430,12 +12430,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12450,22 +12450,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124398668</v>
+        <v>124396024</v>
       </c>
       <c r="B98" t="n">
-        <v>79341</v>
+        <v>79920</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12474,50 +12474,41 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1350</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444415</v>
+        <v>444388</v>
       </c>
       <c r="R98" t="n">
-        <v>7029660</v>
+        <v>7030037</v>
       </c>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12546,7 +12537,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12556,12 +12547,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12576,22 +12567,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124399656</v>
+        <v>124398668</v>
       </c>
       <c r="B99" t="n">
-        <v>79851</v>
+        <v>79341</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12600,41 +12591,50 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229497</v>
+        <v>1350</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444478</v>
+        <v>444415</v>
       </c>
       <c r="R99" t="n">
-        <v>7029836</v>
+        <v>7029660</v>
       </c>
       <c r="S99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124397876</v>
+        <v>124398748</v>
       </c>
       <c r="B73" t="n">
-        <v>91413</v>
+        <v>79341</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,38 +9448,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4217</v>
+        <v>1350</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444498</v>
+        <v>444401</v>
       </c>
       <c r="R73" t="n">
-        <v>7029879</v>
+        <v>7029685</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9511,7 +9520,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9521,12 +9530,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9546,17 +9555,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124397972</v>
+        <v>124397708</v>
       </c>
       <c r="B74" t="n">
-        <v>79341</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9565,41 +9574,50 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1350</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444487</v>
+        <v>444403</v>
       </c>
       <c r="R74" t="n">
-        <v>7029857</v>
+        <v>7029971</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9628,7 +9646,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9638,12 +9656,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9658,22 +9671,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124399597</v>
+        <v>124397664</v>
       </c>
       <c r="B75" t="n">
-        <v>91705</v>
+        <v>95335</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9682,41 +9695,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>67</v>
+        <v>2809</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444456</v>
+        <v>444403</v>
       </c>
       <c r="R75" t="n">
-        <v>7029772</v>
+        <v>7030010</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9745,7 +9758,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9755,12 +9768,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9780,17 +9793,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124399926</v>
+        <v>124399157</v>
       </c>
       <c r="B76" t="n">
-        <v>79341</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9799,50 +9812,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1350</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444478</v>
+        <v>444448</v>
       </c>
       <c r="R76" t="n">
-        <v>7029836</v>
+        <v>7029741</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9871,7 +9875,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9881,12 +9885,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9901,22 +9905,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124398951</v>
+        <v>124396061</v>
       </c>
       <c r="B77" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9925,55 +9929,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444424</v>
+        <v>444402</v>
       </c>
       <c r="R77" t="n">
-        <v>7029691</v>
+        <v>7030044</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10002,7 +9992,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10012,12 +10002,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10028,26 +10013,41 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124396028</v>
+        <v>124399997</v>
       </c>
       <c r="B78" t="n">
-        <v>79857</v>
+        <v>79348</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10056,41 +10056,55 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229748</v>
+        <v>1353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444402</v>
+        <v>444448</v>
       </c>
       <c r="R78" t="n">
-        <v>7030044</v>
+        <v>7029784</v>
       </c>
       <c r="S78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10119,7 +10133,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10129,7 +10143,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10140,31 +10159,16 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -10288,10 +10292,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124398408</v>
+        <v>124396185</v>
       </c>
       <c r="B80" t="n">
-        <v>77743</v>
+        <v>91030</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10304,37 +10308,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444419</v>
+        <v>444287</v>
       </c>
       <c r="R80" t="n">
-        <v>7029740</v>
+        <v>7030000</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10363,7 +10376,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10373,12 +10386,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På liten gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10398,17 +10406,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124399157</v>
+        <v>124398979</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10421,34 +10429,43 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444448</v>
+        <v>444424</v>
       </c>
       <c r="R81" t="n">
-        <v>7029741</v>
+        <v>7029676</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10480,7 +10497,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10490,12 +10507,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10510,7 +10522,7 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -10522,10 +10534,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124398748</v>
+        <v>124399850</v>
       </c>
       <c r="B82" t="n">
-        <v>79341</v>
+        <v>79927</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10534,50 +10546,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1350</v>
+        <v>6464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444401</v>
+        <v>444432</v>
       </c>
       <c r="R82" t="n">
-        <v>7029685</v>
+        <v>7029779</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10606,7 +10609,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10616,12 +10619,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10648,10 +10651,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124396185</v>
+        <v>124396024</v>
       </c>
       <c r="B83" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10660,50 +10663,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444287</v>
+        <v>444388</v>
       </c>
       <c r="R83" t="n">
-        <v>7030000</v>
+        <v>7030037</v>
       </c>
       <c r="S83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10732,7 +10726,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10742,7 +10736,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10757,22 +10756,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124398839</v>
+        <v>124399819</v>
       </c>
       <c r="B84" t="n">
-        <v>78998</v>
+        <v>79891</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10781,30 +10780,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>230552</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10818,13 +10817,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444409</v>
+        <v>444478</v>
       </c>
       <c r="R84" t="n">
-        <v>7029694</v>
+        <v>7029836</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10853,7 +10852,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10863,12 +10862,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10883,22 +10882,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124399850</v>
+        <v>124397972</v>
       </c>
       <c r="B85" t="n">
-        <v>79927</v>
+        <v>79341</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10907,25 +10906,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6464</v>
+        <v>1350</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10935,13 +10934,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444432</v>
+        <v>444487</v>
       </c>
       <c r="R85" t="n">
-        <v>7029779</v>
+        <v>7029857</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10970,7 +10969,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10980,12 +10979,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11005,17 +11004,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124397408</v>
+        <v>124399409</v>
       </c>
       <c r="B86" t="n">
-        <v>79851</v>
+        <v>91282</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11024,41 +11023,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>73</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444276</v>
+        <v>444464</v>
       </c>
       <c r="R86" t="n">
-        <v>7030094</v>
+        <v>7029781</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11087,7 +11086,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11097,12 +11096,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11129,7 +11128,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124396061</v>
+        <v>124397408</v>
       </c>
       <c r="B87" t="n">
         <v>79851</v>
@@ -11165,17 +11164,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444402</v>
+        <v>444276</v>
       </c>
       <c r="R87" t="n">
-        <v>7030044</v>
+        <v>7030094</v>
       </c>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11204,7 +11203,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11214,7 +11213,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11225,41 +11229,26 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124397708</v>
+        <v>124399571</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11272,31 +11261,27 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11305,13 +11290,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444403</v>
+        <v>444478</v>
       </c>
       <c r="R88" t="n">
-        <v>7029971</v>
+        <v>7029836</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11340,7 +11325,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11350,7 +11335,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11370,17 +11360,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124398118</v>
+        <v>124397876</v>
       </c>
       <c r="B89" t="n">
-        <v>91950</v>
+        <v>91413</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11393,37 +11383,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4769</v>
+        <v>4217</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444492</v>
+        <v>444498</v>
       </c>
       <c r="R89" t="n">
-        <v>7029851</v>
+        <v>7029879</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11452,7 +11442,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11462,12 +11452,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11487,17 +11477,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124397463</v>
+        <v>124398408</v>
       </c>
       <c r="B90" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11510,42 +11500,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444279</v>
+        <v>444419</v>
       </c>
       <c r="R90" t="n">
-        <v>7030095</v>
+        <v>7029740</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11574,7 +11559,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11584,12 +11569,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11609,17 +11594,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124398709</v>
+        <v>124399926</v>
       </c>
       <c r="B91" t="n">
-        <v>79348</v>
+        <v>79341</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11628,30 +11613,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11665,13 +11650,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444401</v>
+        <v>444478</v>
       </c>
       <c r="R91" t="n">
-        <v>7029685</v>
+        <v>7029836</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11700,7 +11685,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11710,12 +11695,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11730,22 +11715,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124399357</v>
+        <v>124399597</v>
       </c>
       <c r="B92" t="n">
-        <v>79066</v>
+        <v>91705</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11754,25 +11739,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6459</v>
+        <v>67</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11782,13 +11767,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444468</v>
+        <v>444456</v>
       </c>
       <c r="R92" t="n">
-        <v>7029811</v>
+        <v>7029772</v>
       </c>
       <c r="S92" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11817,7 +11802,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11827,12 +11812,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11847,7 +11832,7 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
@@ -11859,10 +11844,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124399819</v>
+        <v>124399091</v>
       </c>
       <c r="B93" t="n">
-        <v>79891</v>
+        <v>79795</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11871,50 +11856,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444478</v>
+        <v>444439</v>
       </c>
       <c r="R93" t="n">
-        <v>7029836</v>
+        <v>7029686</v>
       </c>
       <c r="S93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11943,7 +11919,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11953,12 +11929,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11973,22 +11949,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124398979</v>
+        <v>124399656</v>
       </c>
       <c r="B94" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11997,50 +11973,41 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444424</v>
+        <v>444478</v>
       </c>
       <c r="R94" t="n">
-        <v>7029676</v>
+        <v>7029836</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12069,7 +12036,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12079,7 +12046,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12106,10 +12078,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124398327</v>
+        <v>124399357</v>
       </c>
       <c r="B95" t="n">
-        <v>91030</v>
+        <v>79066</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12118,25 +12090,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12146,13 +12118,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444463</v>
+        <v>444468</v>
       </c>
       <c r="R95" t="n">
-        <v>7029765</v>
+        <v>7029811</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12181,7 +12153,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12191,12 +12163,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12211,7 +12183,7 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
@@ -12223,10 +12195,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124399571</v>
+        <v>124398839</v>
       </c>
       <c r="B96" t="n">
-        <v>91030</v>
+        <v>78998</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12235,31 +12207,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>230552</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -12268,13 +12244,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444478</v>
+        <v>444409</v>
       </c>
       <c r="R96" t="n">
-        <v>7029836</v>
+        <v>7029694</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12303,7 +12279,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12313,12 +12289,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12333,22 +12309,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124399656</v>
+        <v>124398327</v>
       </c>
       <c r="B97" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12357,25 +12333,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12385,13 +12361,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444478</v>
+        <v>444463</v>
       </c>
       <c r="R97" t="n">
-        <v>7029836</v>
+        <v>7029765</v>
       </c>
       <c r="S97" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12420,7 +12396,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12430,12 +12406,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12450,22 +12426,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124396024</v>
+        <v>124398118</v>
       </c>
       <c r="B98" t="n">
-        <v>79920</v>
+        <v>91950</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12478,21 +12454,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>4769</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12502,13 +12478,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444388</v>
+        <v>444492</v>
       </c>
       <c r="R98" t="n">
-        <v>7030037</v>
+        <v>7029851</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12537,7 +12513,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12547,12 +12523,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12572,7 +12548,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12705,10 +12681,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124399091</v>
+        <v>124396028</v>
       </c>
       <c r="B100" t="n">
-        <v>79795</v>
+        <v>79857</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12721,21 +12697,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6456</v>
+        <v>229748</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12745,13 +12721,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444439</v>
+        <v>444402</v>
       </c>
       <c r="R100" t="n">
-        <v>7029686</v>
+        <v>7030044</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12780,7 +12756,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12790,12 +12766,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:19</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12806,16 +12777,31 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12953,7 +12939,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124399997</v>
+        <v>124398709</v>
       </c>
       <c r="B102" t="n">
         <v>79348</v>
@@ -12996,24 +12982,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444448</v>
+        <v>444401</v>
       </c>
       <c r="R102" t="n">
-        <v>7029784</v>
+        <v>7029685</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13042,7 +13023,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13052,12 +13033,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13084,10 +13065,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124399409</v>
+        <v>124399273</v>
       </c>
       <c r="B103" t="n">
-        <v>91282</v>
+        <v>91030</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13100,37 +13081,46 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444464</v>
+        <v>444468</v>
       </c>
       <c r="R103" t="n">
-        <v>7029781</v>
+        <v>7029811</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13159,7 +13149,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13169,12 +13159,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13189,7 +13179,7 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
@@ -13201,10 +13191,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124399273</v>
+        <v>124398951</v>
       </c>
       <c r="B104" t="n">
-        <v>91030</v>
+        <v>79348</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13213,35 +13203,40 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>1353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -13250,13 +13245,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444468</v>
+        <v>444424</v>
       </c>
       <c r="R104" t="n">
-        <v>7029811</v>
+        <v>7029691</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13285,7 +13280,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13295,12 +13290,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13315,22 +13310,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124397664</v>
+        <v>124397463</v>
       </c>
       <c r="B105" t="n">
-        <v>95335</v>
+        <v>91012</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13339,41 +13334,46 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444403</v>
+        <v>444279</v>
       </c>
       <c r="R105" t="n">
-        <v>7030010</v>
+        <v>7030095</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13432,15 +13432,463 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>125009446</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79348</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1353</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Trådbrosklav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Ramalina thrausta</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>444364</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7029824</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>125009445</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79346</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1352</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Småflikig brosklav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Ramalina sinensis</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>444364</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7029824</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>125009443</v>
+      </c>
+      <c r="B108" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>444409</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7029856</v>
+      </c>
+      <c r="S108" t="n">
+        <v>13</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>125009447</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79795</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>444364</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7029824</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124398748</v>
+        <v>124400074</v>
       </c>
       <c r="B73" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,25 +9448,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -9479,19 +9479,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444401</v>
+        <v>444429</v>
       </c>
       <c r="R73" t="n">
-        <v>7029685</v>
+        <v>7029784</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9520,7 +9525,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9530,12 +9535,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9562,10 +9567,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124397708</v>
+        <v>124398327</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9578,46 +9583,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444403</v>
+        <v>444463</v>
       </c>
       <c r="R74" t="n">
-        <v>7029971</v>
+        <v>7029765</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9646,7 +9642,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9656,7 +9652,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9671,22 +9672,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124397664</v>
+        <v>124397972</v>
       </c>
       <c r="B75" t="n">
-        <v>95335</v>
+        <v>79341</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9695,38 +9696,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2809</v>
+        <v>1350</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444403</v>
+        <v>444487</v>
       </c>
       <c r="R75" t="n">
-        <v>7030010</v>
+        <v>7029857</v>
       </c>
       <c r="S75" t="n">
         <v>6</v>
@@ -9758,7 +9759,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9768,12 +9769,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9793,17 +9794,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124399157</v>
+        <v>124399997</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>79348</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9812,28 +9813,42 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
@@ -9843,7 +9858,7 @@
         <v>444448</v>
       </c>
       <c r="R76" t="n">
-        <v>7029741</v>
+        <v>7029784</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9875,7 +9890,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9885,12 +9900,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9917,10 +9932,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124396061</v>
+        <v>124399571</v>
       </c>
       <c r="B77" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9929,41 +9944,46 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444402</v>
+        <v>444478</v>
       </c>
       <c r="R77" t="n">
-        <v>7030044</v>
+        <v>7029836</v>
       </c>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9992,7 +10012,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10002,7 +10022,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10013,21 +10038,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10037,17 +10047,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124399997</v>
+        <v>124397664</v>
       </c>
       <c r="B78" t="n">
-        <v>79348</v>
+        <v>95335</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10056,55 +10066,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1353</v>
+        <v>2809</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444448</v>
+        <v>444403</v>
       </c>
       <c r="R78" t="n">
-        <v>7029784</v>
+        <v>7030010</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10133,7 +10129,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10143,12 +10139,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10168,17 +10164,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124398297</v>
+        <v>124398839</v>
       </c>
       <c r="B79" t="n">
-        <v>79851</v>
+        <v>78998</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10187,41 +10183,50 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229497</v>
+        <v>230552</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444498</v>
+        <v>444409</v>
       </c>
       <c r="R79" t="n">
-        <v>7029821</v>
+        <v>7029694</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10250,7 +10255,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10260,12 +10265,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10280,12 +10285,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10413,10 +10418,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124398979</v>
+        <v>124397463</v>
       </c>
       <c r="B81" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10429,43 +10434,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444424</v>
+        <v>444279</v>
       </c>
       <c r="R81" t="n">
-        <v>7029676</v>
+        <v>7030095</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10497,7 +10498,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10507,7 +10508,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10527,17 +10533,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124399850</v>
+        <v>124396028</v>
       </c>
       <c r="B82" t="n">
-        <v>79927</v>
+        <v>79857</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10550,21 +10556,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>229748</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10574,13 +10580,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444432</v>
+        <v>444402</v>
       </c>
       <c r="R82" t="n">
-        <v>7029779</v>
+        <v>7030044</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10609,7 +10615,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10619,12 +10625,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10635,26 +10636,41 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124396024</v>
+        <v>124399656</v>
       </c>
       <c r="B83" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10667,21 +10683,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10691,13 +10707,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444388</v>
+        <v>444478</v>
       </c>
       <c r="R83" t="n">
-        <v>7030037</v>
+        <v>7029836</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10726,7 +10742,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10736,12 +10752,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10756,22 +10772,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124399819</v>
+        <v>124399850</v>
       </c>
       <c r="B84" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10780,50 +10796,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444478</v>
+        <v>444432</v>
       </c>
       <c r="R84" t="n">
-        <v>7029836</v>
+        <v>7029779</v>
       </c>
       <c r="S84" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10852,7 +10859,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10862,12 +10869,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10882,19 +10889,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124397972</v>
+        <v>124398668</v>
       </c>
       <c r="B85" t="n">
         <v>79341</v>
@@ -10927,20 +10934,29 @@
           <t>(Arnold) Bitter</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444487</v>
+        <v>444415</v>
       </c>
       <c r="R85" t="n">
-        <v>7029857</v>
+        <v>7029660</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10969,7 +10985,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10979,12 +10995,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10999,22 +11015,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124399409</v>
+        <v>124398979</v>
       </c>
       <c r="B86" t="n">
-        <v>91282</v>
+        <v>91030</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11027,34 +11043,43 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444464</v>
+        <v>444424</v>
       </c>
       <c r="R86" t="n">
-        <v>7029781</v>
+        <v>7029676</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11086,7 +11111,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11096,12 +11121,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11116,22 +11136,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124397408</v>
+        <v>124398951</v>
       </c>
       <c r="B87" t="n">
-        <v>79851</v>
+        <v>79348</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11140,41 +11160,55 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>1353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444276</v>
+        <v>444424</v>
       </c>
       <c r="R87" t="n">
-        <v>7030094</v>
+        <v>7029691</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11203,7 +11237,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11213,12 +11247,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11245,10 +11279,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124399571</v>
+        <v>124397408</v>
       </c>
       <c r="B88" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11257,43 +11291,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444478</v>
+        <v>444276</v>
       </c>
       <c r="R88" t="n">
-        <v>7029836</v>
+        <v>7030094</v>
       </c>
       <c r="S88" t="n">
         <v>9</v>
@@ -11325,7 +11354,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11335,12 +11364,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11355,22 +11384,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124397876</v>
+        <v>124399597</v>
       </c>
       <c r="B89" t="n">
-        <v>91413</v>
+        <v>91705</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11379,41 +11408,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4217</v>
+        <v>67</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444498</v>
+        <v>444456</v>
       </c>
       <c r="R89" t="n">
-        <v>7029879</v>
+        <v>7029772</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11442,7 +11471,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11452,12 +11481,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11477,17 +11506,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124398408</v>
+        <v>124399819</v>
       </c>
       <c r="B90" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11500,37 +11529,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444419</v>
+        <v>444478</v>
       </c>
       <c r="R90" t="n">
-        <v>7029740</v>
+        <v>7029836</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11559,7 +11597,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11569,12 +11607,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11601,10 +11639,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124399926</v>
+        <v>124399157</v>
       </c>
       <c r="B91" t="n">
-        <v>79341</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11613,50 +11651,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1350</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444478</v>
+        <v>444448</v>
       </c>
       <c r="R91" t="n">
-        <v>7029836</v>
+        <v>7029741</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11685,7 +11714,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11695,12 +11724,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11715,22 +11744,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124399597</v>
+        <v>124398408</v>
       </c>
       <c r="B92" t="n">
-        <v>91705</v>
+        <v>77743</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11739,25 +11768,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>67</v>
+        <v>228579</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11767,13 +11796,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444456</v>
+        <v>444419</v>
       </c>
       <c r="R92" t="n">
-        <v>7029772</v>
+        <v>7029740</v>
       </c>
       <c r="S92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11802,7 +11831,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11812,12 +11841,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11832,22 +11861,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124399091</v>
+        <v>124398709</v>
       </c>
       <c r="B93" t="n">
-        <v>79795</v>
+        <v>79348</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11856,41 +11885,50 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6456</v>
+        <v>1353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444439</v>
+        <v>444401</v>
       </c>
       <c r="R93" t="n">
-        <v>7029686</v>
+        <v>7029685</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11919,7 +11957,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11929,12 +11967,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11961,10 +11999,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124399656</v>
+        <v>124398118</v>
       </c>
       <c r="B94" t="n">
-        <v>79851</v>
+        <v>91950</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11977,21 +12015,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229497</v>
+        <v>4769</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12001,13 +12039,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444478</v>
+        <v>444492</v>
       </c>
       <c r="R94" t="n">
-        <v>7029836</v>
+        <v>7029851</v>
       </c>
       <c r="S94" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12036,7 +12074,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12046,12 +12084,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12066,22 +12104,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124399357</v>
+        <v>124399273</v>
       </c>
       <c r="B95" t="n">
-        <v>79066</v>
+        <v>91030</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12090,28 +12128,37 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
@@ -12124,7 +12171,7 @@
         <v>7029811</v>
       </c>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12153,7 +12200,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12163,7 +12210,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -12188,17 +12235,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124398839</v>
+        <v>124396024</v>
       </c>
       <c r="B96" t="n">
-        <v>78998</v>
+        <v>79920</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12207,50 +12254,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>230552</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444409</v>
+        <v>444388</v>
       </c>
       <c r="R96" t="n">
-        <v>7029694</v>
+        <v>7030037</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12279,7 +12317,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12289,12 +12327,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12314,17 +12352,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124398327</v>
+        <v>124399409</v>
       </c>
       <c r="B97" t="n">
-        <v>91030</v>
+        <v>91282</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12337,21 +12375,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12361,10 +12399,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444463</v>
+        <v>444464</v>
       </c>
       <c r="R97" t="n">
-        <v>7029765</v>
+        <v>7029781</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12396,7 +12434,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12406,12 +12444,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12438,10 +12476,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124398118</v>
+        <v>124397708</v>
       </c>
       <c r="B98" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12450,41 +12488,50 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444492</v>
+        <v>444403</v>
       </c>
       <c r="R98" t="n">
-        <v>7029851</v>
+        <v>7029971</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12513,7 +12560,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12523,12 +12570,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:48</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12543,22 +12585,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124398668</v>
+        <v>124399357</v>
       </c>
       <c r="B99" t="n">
-        <v>79341</v>
+        <v>79066</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12567,47 +12609,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1350</v>
+        <v>6459</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444415</v>
+        <v>444468</v>
       </c>
       <c r="R99" t="n">
-        <v>7029660</v>
+        <v>7029811</v>
       </c>
       <c r="S99" t="n">
         <v>12</v>
@@ -12639,7 +12672,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12649,7 +12682,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -12681,10 +12714,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124396028</v>
+        <v>124398748</v>
       </c>
       <c r="B100" t="n">
-        <v>79857</v>
+        <v>79341</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12693,41 +12726,50 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229748</v>
+        <v>1350</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444402</v>
+        <v>444401</v>
       </c>
       <c r="R100" t="n">
-        <v>7030044</v>
+        <v>7029685</v>
       </c>
       <c r="S100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12756,7 +12798,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12766,7 +12808,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12777,41 +12824,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124400074</v>
+        <v>124396061</v>
       </c>
       <c r="B101" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12820,55 +12852,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444429</v>
+        <v>444402</v>
       </c>
       <c r="R101" t="n">
-        <v>7029784</v>
+        <v>7030044</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12897,7 +12915,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12907,12 +12925,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12923,26 +12936,41 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124398709</v>
+        <v>124399926</v>
       </c>
       <c r="B102" t="n">
-        <v>79348</v>
+        <v>79341</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12951,30 +12979,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12988,13 +13016,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444401</v>
+        <v>444478</v>
       </c>
       <c r="R102" t="n">
-        <v>7029685</v>
+        <v>7029836</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13023,7 +13051,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13033,12 +13061,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13053,22 +13081,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124399273</v>
+        <v>124399091</v>
       </c>
       <c r="B103" t="n">
-        <v>91030</v>
+        <v>79795</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13077,50 +13105,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444468</v>
+        <v>444439</v>
       </c>
       <c r="R103" t="n">
-        <v>7029811</v>
+        <v>7029686</v>
       </c>
       <c r="S103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13149,7 +13168,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13159,12 +13178,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13179,22 +13198,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124398951</v>
+        <v>124397876</v>
       </c>
       <c r="B104" t="n">
-        <v>79348</v>
+        <v>91413</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13203,52 +13222,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1353</v>
+        <v>4217</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444424</v>
+        <v>444498</v>
       </c>
       <c r="R104" t="n">
-        <v>7029691</v>
+        <v>7029879</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13280,7 +13285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13290,12 +13295,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13315,17 +13320,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124397463</v>
+        <v>124398297</v>
       </c>
       <c r="B105" t="n">
-        <v>91012</v>
+        <v>79851</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13334,46 +13339,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444279</v>
+        <v>444498</v>
       </c>
       <c r="R105" t="n">
-        <v>7030095</v>
+        <v>7029821</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13437,17 +13437,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009446</v>
+        <v>125009443</v>
       </c>
       <c r="B106" t="n">
-        <v>79348</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,41 +13456,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1353</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R106" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13556,10 +13556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125009445</v>
+        <v>125009447</v>
       </c>
       <c r="B107" t="n">
-        <v>79346</v>
+        <v>79795</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13568,25 +13568,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1352</v>
+        <v>6456</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009443</v>
+        <v>125009445</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>79346</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13684,37 +13684,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R108" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S108" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009447</v>
+        <v>125009446</v>
       </c>
       <c r="B109" t="n">
-        <v>79795</v>
+        <v>79348</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13792,25 +13792,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6456</v>
+        <v>1353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124400074</v>
+        <v>124398327</v>
       </c>
       <c r="B73" t="n">
-        <v>79348</v>
+        <v>91030</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,55 +9448,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1353</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444429</v>
+        <v>444463</v>
       </c>
       <c r="R73" t="n">
-        <v>7029784</v>
+        <v>7029765</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9525,7 +9511,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9535,12 +9521,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9567,10 +9553,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124398327</v>
+        <v>124397972</v>
       </c>
       <c r="B74" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9579,25 +9565,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9607,13 +9593,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444463</v>
+        <v>444487</v>
       </c>
       <c r="R74" t="n">
-        <v>7029765</v>
+        <v>7029857</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9642,7 +9628,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9652,12 +9638,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9677,17 +9663,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124397972</v>
+        <v>124399997</v>
       </c>
       <c r="B75" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9696,41 +9682,55 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444487</v>
+        <v>444448</v>
       </c>
       <c r="R75" t="n">
-        <v>7029857</v>
+        <v>7029784</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9794,17 +9794,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124399997</v>
+        <v>124398668</v>
       </c>
       <c r="B76" t="n">
-        <v>79348</v>
+        <v>79341</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9813,30 +9813,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9844,24 +9844,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444448</v>
+        <v>444415</v>
       </c>
       <c r="R76" t="n">
-        <v>7029784</v>
+        <v>7029660</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9890,7 +9885,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9900,12 +9895,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9920,19 +9915,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124399571</v>
+        <v>124398979</v>
       </c>
       <c r="B77" t="n">
         <v>91030</v>
@@ -9965,10 +9960,14 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9977,13 +9976,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444478</v>
+        <v>444424</v>
       </c>
       <c r="R77" t="n">
-        <v>7029836</v>
+        <v>7029676</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10012,7 +10011,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10022,12 +10021,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gammal granlåga</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10054,10 +10048,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124397664</v>
+        <v>124397876</v>
       </c>
       <c r="B78" t="n">
-        <v>95335</v>
+        <v>91413</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10070,21 +10064,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2809</v>
+        <v>4217</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10094,13 +10088,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444403</v>
+        <v>444498</v>
       </c>
       <c r="R78" t="n">
-        <v>7030010</v>
+        <v>7029879</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10129,7 +10123,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10139,12 +10133,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10164,17 +10158,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124398839</v>
+        <v>124398118</v>
       </c>
       <c r="B79" t="n">
-        <v>78998</v>
+        <v>91950</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10183,50 +10177,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>230552</v>
+        <v>4769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444409</v>
+        <v>444492</v>
       </c>
       <c r="R79" t="n">
-        <v>7029694</v>
+        <v>7029851</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10255,7 +10240,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10265,12 +10250,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10297,7 +10282,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124396185</v>
+        <v>124399273</v>
       </c>
       <c r="B80" t="n">
         <v>91030</v>
@@ -10332,7 +10317,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10342,17 +10327,17 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444287</v>
+        <v>444468</v>
       </c>
       <c r="R80" t="n">
-        <v>7030000</v>
+        <v>7029811</v>
       </c>
       <c r="S80" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10381,7 +10366,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10391,7 +10376,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10411,17 +10401,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124397463</v>
+        <v>124398839</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>78998</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10430,43 +10420,47 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>230552</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444279</v>
+        <v>444409</v>
       </c>
       <c r="R81" t="n">
-        <v>7030095</v>
+        <v>7029694</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10498,7 +10492,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10508,12 +10502,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10528,22 +10522,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124396028</v>
+        <v>124399819</v>
       </c>
       <c r="B82" t="n">
-        <v>79857</v>
+        <v>79891</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10552,38 +10546,47 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444402</v>
+        <v>444478</v>
       </c>
       <c r="R82" t="n">
-        <v>7030044</v>
+        <v>7029836</v>
       </c>
       <c r="S82" t="n">
         <v>11</v>
@@ -10615,7 +10618,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10625,7 +10628,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10636,21 +10644,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10660,7 +10653,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10777,17 +10770,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124399850</v>
+        <v>124396028</v>
       </c>
       <c r="B84" t="n">
-        <v>79927</v>
+        <v>79857</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10800,21 +10793,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6464</v>
+        <v>229748</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10824,13 +10817,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444432</v>
+        <v>444402</v>
       </c>
       <c r="R84" t="n">
-        <v>7029779</v>
+        <v>7030044</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10859,7 +10852,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10869,12 +10862,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10885,26 +10873,41 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124398668</v>
+        <v>124398951</v>
       </c>
       <c r="B85" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10913,30 +10916,30 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10944,19 +10947,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444415</v>
+        <v>444424</v>
       </c>
       <c r="R85" t="n">
-        <v>7029660</v>
+        <v>7029691</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10985,7 +10993,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10995,12 +11003,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11015,22 +11023,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124398979</v>
+        <v>124398748</v>
       </c>
       <c r="B86" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11039,35 +11047,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -11076,10 +11084,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444424</v>
+        <v>444401</v>
       </c>
       <c r="R86" t="n">
-        <v>7029676</v>
+        <v>7029685</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11111,7 +11119,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11121,7 +11129,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11136,7 +11149,7 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -11148,10 +11161,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124398951</v>
+        <v>124398297</v>
       </c>
       <c r="B87" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11160,55 +11173,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444424</v>
+        <v>444498</v>
       </c>
       <c r="R87" t="n">
-        <v>7029691</v>
+        <v>7029821</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11237,7 +11236,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11247,12 +11246,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11267,22 +11266,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124397408</v>
+        <v>124400074</v>
       </c>
       <c r="B88" t="n">
-        <v>79851</v>
+        <v>79348</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11291,41 +11290,55 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229497</v>
+        <v>1353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444276</v>
+        <v>444429</v>
       </c>
       <c r="R88" t="n">
-        <v>7030094</v>
+        <v>7029784</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11354,7 +11367,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11364,12 +11377,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11389,17 +11402,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124399597</v>
+        <v>124398408</v>
       </c>
       <c r="B89" t="n">
-        <v>91705</v>
+        <v>77743</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11408,25 +11421,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>67</v>
+        <v>228579</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11436,13 +11449,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444456</v>
+        <v>444419</v>
       </c>
       <c r="R89" t="n">
-        <v>7029772</v>
+        <v>7029740</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11471,7 +11484,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11481,12 +11494,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11501,22 +11514,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124399819</v>
+        <v>124399571</v>
       </c>
       <c r="B90" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11529,31 +11542,27 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11568,7 +11577,7 @@
         <v>7029836</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11597,7 +11606,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11607,12 +11616,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11639,10 +11648,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124399157</v>
+        <v>124396024</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11651,25 +11660,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11679,13 +11688,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444448</v>
+        <v>444388</v>
       </c>
       <c r="R91" t="n">
-        <v>7029741</v>
+        <v>7030037</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11714,7 +11723,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11724,12 +11733,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11749,17 +11758,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124398408</v>
+        <v>124399850</v>
       </c>
       <c r="B92" t="n">
-        <v>77743</v>
+        <v>79927</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11768,25 +11777,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11796,13 +11805,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444419</v>
+        <v>444432</v>
       </c>
       <c r="R92" t="n">
-        <v>7029740</v>
+        <v>7029779</v>
       </c>
       <c r="S92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11831,7 +11840,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11841,12 +11850,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11861,22 +11870,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124398709</v>
+        <v>124397463</v>
       </c>
       <c r="B93" t="n">
-        <v>79348</v>
+        <v>91012</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11885,50 +11894,46 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1353</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444401</v>
+        <v>444279</v>
       </c>
       <c r="R93" t="n">
-        <v>7029685</v>
+        <v>7030095</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11957,7 +11962,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11967,12 +11972,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11987,22 +11992,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124398118</v>
+        <v>124399091</v>
       </c>
       <c r="B94" t="n">
-        <v>91950</v>
+        <v>79795</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12015,21 +12020,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4769</v>
+        <v>6456</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12039,13 +12044,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444492</v>
+        <v>444439</v>
       </c>
       <c r="R94" t="n">
-        <v>7029851</v>
+        <v>7029686</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12074,7 +12079,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12084,12 +12089,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12116,10 +12121,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124399273</v>
+        <v>124398709</v>
       </c>
       <c r="B95" t="n">
-        <v>91030</v>
+        <v>79348</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12128,35 +12133,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>1353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -12165,13 +12170,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444468</v>
+        <v>444401</v>
       </c>
       <c r="R95" t="n">
-        <v>7029811</v>
+        <v>7029685</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12200,7 +12205,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12210,12 +12215,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12230,7 +12235,7 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
@@ -12242,10 +12247,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124396024</v>
+        <v>124399597</v>
       </c>
       <c r="B96" t="n">
-        <v>79920</v>
+        <v>91705</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12254,25 +12259,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>67</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -12282,10 +12287,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444388</v>
+        <v>444456</v>
       </c>
       <c r="R96" t="n">
-        <v>7030037</v>
+        <v>7029772</v>
       </c>
       <c r="S96" t="n">
         <v>8</v>
@@ -12317,7 +12322,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12327,12 +12332,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12352,17 +12357,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124399409</v>
+        <v>124396061</v>
       </c>
       <c r="B97" t="n">
-        <v>91282</v>
+        <v>79851</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12371,25 +12376,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>73</v>
+        <v>229497</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12399,13 +12404,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444464</v>
+        <v>444402</v>
       </c>
       <c r="R97" t="n">
-        <v>7029781</v>
+        <v>7030044</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12434,7 +12439,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12444,12 +12449,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12460,23 +12460,38 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124397708</v>
+        <v>124399157</v>
       </c>
       <c r="B98" t="n">
         <v>78810</v>
@@ -12509,29 +12524,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444403</v>
+        <v>444448</v>
       </c>
       <c r="R98" t="n">
-        <v>7029971</v>
+        <v>7029741</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12560,7 +12566,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12570,7 +12576,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12585,22 +12596,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124399357</v>
+        <v>124397708</v>
       </c>
       <c r="B99" t="n">
-        <v>79066</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12609,41 +12620,50 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444468</v>
+        <v>444403</v>
       </c>
       <c r="R99" t="n">
-        <v>7029811</v>
+        <v>7029971</v>
       </c>
       <c r="S99" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12672,7 +12692,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12682,12 +12702,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12707,17 +12722,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124398748</v>
+        <v>124399357</v>
       </c>
       <c r="B100" t="n">
-        <v>79341</v>
+        <v>79066</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12726,50 +12741,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1350</v>
+        <v>6459</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444401</v>
+        <v>444468</v>
       </c>
       <c r="R100" t="n">
-        <v>7029685</v>
+        <v>7029811</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12798,7 +12804,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12808,12 +12814,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12828,22 +12834,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124396061</v>
+        <v>124399926</v>
       </c>
       <c r="B101" t="n">
-        <v>79851</v>
+        <v>79341</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12852,41 +12858,50 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229497</v>
+        <v>1350</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444402</v>
+        <v>444478</v>
       </c>
       <c r="R101" t="n">
-        <v>7030044</v>
+        <v>7029836</v>
       </c>
       <c r="S101" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12915,7 +12930,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12925,7 +12940,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12936,21 +12956,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12960,17 +12965,17 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124399926</v>
+        <v>124397664</v>
       </c>
       <c r="B102" t="n">
-        <v>79341</v>
+        <v>95335</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12979,50 +12984,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1350</v>
+        <v>2809</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444478</v>
+        <v>444403</v>
       </c>
       <c r="R102" t="n">
-        <v>7029836</v>
+        <v>7030010</v>
       </c>
       <c r="S102" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13051,7 +13047,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13061,12 +13057,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13081,22 +13077,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124399091</v>
+        <v>124397408</v>
       </c>
       <c r="B103" t="n">
-        <v>79795</v>
+        <v>79851</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13109,37 +13105,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444439</v>
+        <v>444276</v>
       </c>
       <c r="R103" t="n">
-        <v>7029686</v>
+        <v>7030094</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13168,7 +13164,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13178,12 +13174,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13203,17 +13199,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124397876</v>
+        <v>124399409</v>
       </c>
       <c r="B104" t="n">
-        <v>91413</v>
+        <v>91282</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13222,38 +13218,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4217</v>
+        <v>73</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444498</v>
+        <v>444464</v>
       </c>
       <c r="R104" t="n">
-        <v>7029879</v>
+        <v>7029781</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13285,7 +13281,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13295,12 +13291,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13320,17 +13316,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124398297</v>
+        <v>124396185</v>
       </c>
       <c r="B105" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13339,41 +13335,50 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444498</v>
+        <v>444287</v>
       </c>
       <c r="R105" t="n">
-        <v>7029821</v>
+        <v>7030000</v>
       </c>
       <c r="S105" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13407,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13417,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På gråal</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13437,17 +13437,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009443</v>
+        <v>125009446</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>79348</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,41 +13456,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R106" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S106" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13556,10 +13556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125009447</v>
+        <v>125009445</v>
       </c>
       <c r="B107" t="n">
-        <v>79795</v>
+        <v>79346</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13568,25 +13568,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6456</v>
+        <v>1352</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009445</v>
+        <v>125009443</v>
       </c>
       <c r="B108" t="n">
-        <v>79346</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13684,37 +13684,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R108" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009446</v>
+        <v>125009447</v>
       </c>
       <c r="B109" t="n">
-        <v>79348</v>
+        <v>79795</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13792,25 +13792,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1353</v>
+        <v>6456</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -10048,10 +10048,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124397876</v>
+        <v>124398839</v>
       </c>
       <c r="B78" t="n">
-        <v>91413</v>
+        <v>78998</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10060,38 +10060,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4217</v>
+        <v>230552</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444498</v>
+        <v>444409</v>
       </c>
       <c r="R78" t="n">
-        <v>7029879</v>
+        <v>7029694</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10123,7 +10132,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10133,12 +10142,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10158,17 +10167,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124398118</v>
+        <v>124399819</v>
       </c>
       <c r="B79" t="n">
-        <v>91950</v>
+        <v>79891</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10177,41 +10186,50 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444492</v>
+        <v>444478</v>
       </c>
       <c r="R79" t="n">
-        <v>7029851</v>
+        <v>7029836</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10240,7 +10258,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10250,12 +10268,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10270,22 +10288,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124399273</v>
+        <v>124397876</v>
       </c>
       <c r="B80" t="n">
-        <v>91030</v>
+        <v>91413</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10294,50 +10312,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444468</v>
+        <v>444498</v>
       </c>
       <c r="R80" t="n">
-        <v>7029811</v>
+        <v>7029879</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10366,7 +10375,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10376,12 +10385,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10396,22 +10405,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124398839</v>
+        <v>124398118</v>
       </c>
       <c r="B81" t="n">
-        <v>78998</v>
+        <v>91950</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10420,50 +10429,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>230552</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444409</v>
+        <v>444492</v>
       </c>
       <c r="R81" t="n">
-        <v>7029694</v>
+        <v>7029851</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10534,10 +10534,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124399819</v>
+        <v>124399273</v>
       </c>
       <c r="B82" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10550,31 +10550,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444478</v>
+        <v>444468</v>
       </c>
       <c r="R82" t="n">
-        <v>7029836</v>
+        <v>7029811</v>
       </c>
       <c r="S82" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10628,12 +10628,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124398327</v>
+        <v>124397463</v>
       </c>
       <c r="B73" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9452,34 +9452,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444463</v>
+        <v>444279</v>
       </c>
       <c r="R73" t="n">
-        <v>7029765</v>
+        <v>7030095</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9511,7 +9516,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9521,12 +9526,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9541,22 +9546,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124397972</v>
+        <v>124397408</v>
       </c>
       <c r="B74" t="n">
-        <v>79341</v>
+        <v>79851</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9565,41 +9570,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1350</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444487</v>
+        <v>444276</v>
       </c>
       <c r="R74" t="n">
-        <v>7029857</v>
+        <v>7030094</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9628,7 +9633,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9638,12 +9643,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9663,17 +9668,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124399997</v>
+        <v>124397876</v>
       </c>
       <c r="B75" t="n">
-        <v>79348</v>
+        <v>91413</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9682,52 +9687,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1353</v>
+        <v>4217</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444448</v>
+        <v>444498</v>
       </c>
       <c r="R75" t="n">
-        <v>7029784</v>
+        <v>7029879</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9759,7 +9750,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9769,12 +9760,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9794,17 +9785,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124398668</v>
+        <v>124399571</v>
       </c>
       <c r="B76" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9813,35 +9804,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9850,13 +9837,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444415</v>
+        <v>444478</v>
       </c>
       <c r="R76" t="n">
-        <v>7029660</v>
+        <v>7029836</v>
       </c>
       <c r="S76" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9885,7 +9872,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9895,12 +9882,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9927,10 +9914,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124398979</v>
+        <v>124396028</v>
       </c>
       <c r="B77" t="n">
-        <v>91030</v>
+        <v>79857</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9939,50 +9926,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>229748</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444424</v>
+        <v>444402</v>
       </c>
       <c r="R77" t="n">
-        <v>7029676</v>
+        <v>7030044</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10011,7 +9989,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10021,7 +9999,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10032,6 +10010,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10041,17 +10034,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124398839</v>
+        <v>124398408</v>
       </c>
       <c r="B78" t="n">
-        <v>78998</v>
+        <v>77743</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10060,50 +10053,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>230552</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444409</v>
+        <v>444419</v>
       </c>
       <c r="R78" t="n">
-        <v>7029694</v>
+        <v>7029740</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10132,7 +10116,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10142,12 +10126,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10162,22 +10146,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124399819</v>
+        <v>124398668</v>
       </c>
       <c r="B79" t="n">
-        <v>79891</v>
+        <v>79341</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10186,30 +10170,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>1350</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10223,13 +10207,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444478</v>
+        <v>444415</v>
       </c>
       <c r="R79" t="n">
-        <v>7029836</v>
+        <v>7029660</v>
       </c>
       <c r="S79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10258,7 +10242,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10268,12 +10252,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10300,10 +10284,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124397876</v>
+        <v>124398839</v>
       </c>
       <c r="B80" t="n">
-        <v>91413</v>
+        <v>78998</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10312,38 +10296,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4217</v>
+        <v>230552</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444498</v>
+        <v>444409</v>
       </c>
       <c r="R80" t="n">
-        <v>7029879</v>
+        <v>7029694</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10375,7 +10368,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10385,12 +10378,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10410,17 +10403,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124398118</v>
+        <v>124398748</v>
       </c>
       <c r="B81" t="n">
-        <v>91950</v>
+        <v>79341</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10429,41 +10422,50 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>1350</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444492</v>
+        <v>444401</v>
       </c>
       <c r="R81" t="n">
-        <v>7029851</v>
+        <v>7029685</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10492,7 +10494,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10502,12 +10504,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10534,7 +10536,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124399273</v>
+        <v>124398327</v>
       </c>
       <c r="B82" t="n">
         <v>91030</v>
@@ -10567,29 +10569,20 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444468</v>
+        <v>444463</v>
       </c>
       <c r="R82" t="n">
-        <v>7029811</v>
+        <v>7029765</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10618,7 +10611,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10628,12 +10621,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10648,22 +10641,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124399656</v>
+        <v>124399357</v>
       </c>
       <c r="B83" t="n">
-        <v>79851</v>
+        <v>79066</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10676,21 +10669,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>6459</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10700,13 +10693,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444478</v>
+        <v>444468</v>
       </c>
       <c r="R83" t="n">
-        <v>7029836</v>
+        <v>7029811</v>
       </c>
       <c r="S83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10735,7 +10728,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10745,12 +10738,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10770,17 +10763,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124396028</v>
+        <v>124396185</v>
       </c>
       <c r="B84" t="n">
-        <v>79857</v>
+        <v>91030</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10789,41 +10782,50 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229748</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444402</v>
+        <v>444287</v>
       </c>
       <c r="R84" t="n">
-        <v>7030044</v>
+        <v>7030000</v>
       </c>
       <c r="S84" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10852,7 +10854,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10862,7 +10864,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10873,21 +10875,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10897,17 +10884,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124398951</v>
+        <v>124396024</v>
       </c>
       <c r="B85" t="n">
-        <v>79348</v>
+        <v>79920</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10916,55 +10903,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1353</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444424</v>
+        <v>444388</v>
       </c>
       <c r="R85" t="n">
-        <v>7029691</v>
+        <v>7030037</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10993,7 +10966,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11003,12 +10976,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11028,17 +11001,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124398748</v>
+        <v>124398979</v>
       </c>
       <c r="B86" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11047,35 +11020,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -11084,10 +11057,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444401</v>
+        <v>444424</v>
       </c>
       <c r="R86" t="n">
-        <v>7029685</v>
+        <v>7029676</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11119,7 +11092,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11129,12 +11102,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11149,7 +11117,7 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -11161,10 +11129,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124398297</v>
+        <v>124399157</v>
       </c>
       <c r="B87" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11173,25 +11141,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11201,13 +11169,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444498</v>
+        <v>444448</v>
       </c>
       <c r="R87" t="n">
-        <v>7029821</v>
+        <v>7029741</v>
       </c>
       <c r="S87" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11236,7 +11204,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11246,12 +11214,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11266,22 +11234,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124400074</v>
+        <v>124399819</v>
       </c>
       <c r="B88" t="n">
-        <v>79348</v>
+        <v>79891</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11290,25 +11258,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1353</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -11321,24 +11289,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444429</v>
+        <v>444478</v>
       </c>
       <c r="R88" t="n">
-        <v>7029784</v>
+        <v>7029836</v>
       </c>
       <c r="S88" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11367,7 +11330,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11377,12 +11340,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11397,7 +11360,7 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
@@ -11409,10 +11372,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124398408</v>
+        <v>124399409</v>
       </c>
       <c r="B89" t="n">
-        <v>77743</v>
+        <v>91282</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11425,21 +11388,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228579</v>
+        <v>73</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11449,13 +11412,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444419</v>
+        <v>444464</v>
       </c>
       <c r="R89" t="n">
-        <v>7029740</v>
+        <v>7029781</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11484,7 +11447,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11494,12 +11457,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11514,22 +11477,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124399571</v>
+        <v>124399850</v>
       </c>
       <c r="B90" t="n">
-        <v>91030</v>
+        <v>79927</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11538,46 +11501,41 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444478</v>
+        <v>444432</v>
       </c>
       <c r="R90" t="n">
-        <v>7029836</v>
+        <v>7029779</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11606,7 +11564,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11616,12 +11574,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11636,22 +11594,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124396024</v>
+        <v>124399597</v>
       </c>
       <c r="B91" t="n">
-        <v>79920</v>
+        <v>91705</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11660,25 +11618,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>67</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11688,10 +11646,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444388</v>
+        <v>444456</v>
       </c>
       <c r="R91" t="n">
-        <v>7030037</v>
+        <v>7029772</v>
       </c>
       <c r="S91" t="n">
         <v>8</v>
@@ -11723,7 +11681,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11733,12 +11691,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11758,17 +11716,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Emil Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124399850</v>
+        <v>124397708</v>
       </c>
       <c r="B92" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11777,38 +11735,47 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444432</v>
+        <v>444403</v>
       </c>
       <c r="R92" t="n">
-        <v>7029779</v>
+        <v>7029971</v>
       </c>
       <c r="S92" t="n">
         <v>8</v>
@@ -11840,7 +11807,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11850,12 +11817,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11870,22 +11832,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124397463</v>
+        <v>124398951</v>
       </c>
       <c r="B93" t="n">
-        <v>91012</v>
+        <v>79348</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11894,43 +11856,52 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>1353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444279</v>
+        <v>444424</v>
       </c>
       <c r="R93" t="n">
-        <v>7030095</v>
+        <v>7029691</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11962,7 +11933,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11972,12 +11943,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11992,22 +11963,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124399091</v>
+        <v>124398118</v>
       </c>
       <c r="B94" t="n">
-        <v>79795</v>
+        <v>91950</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12020,21 +11991,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6456</v>
+        <v>4769</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12044,13 +12015,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444439</v>
+        <v>444492</v>
       </c>
       <c r="R94" t="n">
-        <v>7029686</v>
+        <v>7029851</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12079,7 +12050,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12089,12 +12060,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12121,10 +12092,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124398709</v>
+        <v>124399091</v>
       </c>
       <c r="B95" t="n">
-        <v>79348</v>
+        <v>79795</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12133,50 +12104,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1353</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444401</v>
+        <v>444439</v>
       </c>
       <c r="R95" t="n">
-        <v>7029685</v>
+        <v>7029686</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12205,7 +12167,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12215,12 +12177,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12240,17 +12202,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124399597</v>
+        <v>124399926</v>
       </c>
       <c r="B96" t="n">
-        <v>91705</v>
+        <v>79341</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12263,37 +12225,46 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>67</v>
+        <v>1350</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444456</v>
+        <v>444478</v>
       </c>
       <c r="R96" t="n">
-        <v>7029772</v>
+        <v>7029836</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12322,7 +12293,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12332,12 +12303,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12352,19 +12323,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124396061</v>
+        <v>124399656</v>
       </c>
       <c r="B97" t="n">
         <v>79851</v>
@@ -12404,13 +12375,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444402</v>
+        <v>444478</v>
       </c>
       <c r="R97" t="n">
-        <v>7030044</v>
+        <v>7029836</v>
       </c>
       <c r="S97" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12439,7 +12410,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12449,7 +12420,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12460,21 +12436,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12484,17 +12445,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124399157</v>
+        <v>124399273</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12507,37 +12468,46 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444448</v>
+        <v>444468</v>
       </c>
       <c r="R98" t="n">
-        <v>7029741</v>
+        <v>7029811</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12566,7 +12536,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12576,12 +12546,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12596,22 +12566,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124397708</v>
+        <v>124398297</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12620,50 +12590,41 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444403</v>
+        <v>444498</v>
       </c>
       <c r="R99" t="n">
-        <v>7029971</v>
+        <v>7029821</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12692,7 +12653,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12702,7 +12663,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12722,17 +12688,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124399357</v>
+        <v>124400074</v>
       </c>
       <c r="B100" t="n">
-        <v>79066</v>
+        <v>79348</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12741,41 +12707,55 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6459</v>
+        <v>1353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444468</v>
+        <v>444429</v>
       </c>
       <c r="R100" t="n">
-        <v>7029811</v>
+        <v>7029784</v>
       </c>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12804,7 +12784,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12814,12 +12794,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12834,19 +12814,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124399926</v>
+        <v>124397972</v>
       </c>
       <c r="B101" t="n">
         <v>79341</v>
@@ -12879,29 +12859,20 @@
           <t>(Arnold) Bitter</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444478</v>
+        <v>444487</v>
       </c>
       <c r="R101" t="n">
-        <v>7029836</v>
+        <v>7029857</v>
       </c>
       <c r="S101" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12930,7 +12901,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12940,12 +12911,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12960,22 +12931,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124397664</v>
+        <v>124396061</v>
       </c>
       <c r="B102" t="n">
-        <v>95335</v>
+        <v>79851</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12988,37 +12959,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2809</v>
+        <v>229497</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444403</v>
+        <v>444402</v>
       </c>
       <c r="R102" t="n">
-        <v>7030010</v>
+        <v>7030044</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13047,7 +13018,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13057,12 +13028,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13073,26 +13039,41 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124397408</v>
+        <v>124398709</v>
       </c>
       <c r="B103" t="n">
-        <v>79851</v>
+        <v>79348</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13101,41 +13082,50 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229497</v>
+        <v>1353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444276</v>
+        <v>444401</v>
       </c>
       <c r="R103" t="n">
-        <v>7030094</v>
+        <v>7029685</v>
       </c>
       <c r="S103" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13164,7 +13154,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13174,12 +13164,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13199,17 +13189,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124399409</v>
+        <v>124399997</v>
       </c>
       <c r="B104" t="n">
-        <v>91282</v>
+        <v>79348</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13218,38 +13208,52 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>73</v>
+        <v>1353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444464</v>
+        <v>444448</v>
       </c>
       <c r="R104" t="n">
-        <v>7029781</v>
+        <v>7029784</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13281,7 +13285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13291,12 +13295,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13323,10 +13327,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124396185</v>
+        <v>124397664</v>
       </c>
       <c r="B105" t="n">
-        <v>91030</v>
+        <v>95335</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13335,50 +13339,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444287</v>
+        <v>444403</v>
       </c>
       <c r="R105" t="n">
-        <v>7030000</v>
+        <v>7030010</v>
       </c>
       <c r="S105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13407,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13417,7 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13432,22 +13432,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009446</v>
+        <v>125009443</v>
       </c>
       <c r="B106" t="n">
-        <v>79348</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,41 +13456,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1353</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R106" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13556,10 +13556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125009445</v>
+        <v>125009446</v>
       </c>
       <c r="B107" t="n">
-        <v>79346</v>
+        <v>79348</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13568,25 +13568,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009443</v>
+        <v>125009447</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13680,41 +13680,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R108" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S108" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009447</v>
+        <v>125009445</v>
       </c>
       <c r="B109" t="n">
-        <v>79795</v>
+        <v>79346</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13792,25 +13792,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6456</v>
+        <v>1352</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124397463</v>
+        <v>124396028</v>
       </c>
       <c r="B73" t="n">
-        <v>91012</v>
+        <v>79857</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,46 +9448,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>229748</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444279</v>
+        <v>444402</v>
       </c>
       <c r="R73" t="n">
-        <v>7030095</v>
+        <v>7030044</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9516,7 +9511,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9526,12 +9521,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9542,6 +9532,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9551,17 +9556,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124397408</v>
+        <v>124399926</v>
       </c>
       <c r="B74" t="n">
-        <v>79851</v>
+        <v>79341</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9570,41 +9575,50 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>1350</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444276</v>
+        <v>444478</v>
       </c>
       <c r="R74" t="n">
-        <v>7030094</v>
+        <v>7029836</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9633,7 +9647,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9643,12 +9657,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9663,22 +9677,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124397876</v>
+        <v>124399819</v>
       </c>
       <c r="B75" t="n">
-        <v>91413</v>
+        <v>79891</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9687,41 +9701,50 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4217</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444498</v>
+        <v>444478</v>
       </c>
       <c r="R75" t="n">
-        <v>7029879</v>
+        <v>7029836</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9750,7 +9773,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9760,12 +9783,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9780,22 +9803,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124399571</v>
+        <v>124399850</v>
       </c>
       <c r="B76" t="n">
-        <v>91030</v>
+        <v>79927</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9804,46 +9827,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444478</v>
+        <v>444432</v>
       </c>
       <c r="R76" t="n">
-        <v>7029836</v>
+        <v>7029779</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9872,7 +9890,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9882,12 +9900,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9902,22 +9920,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124396028</v>
+        <v>124399571</v>
       </c>
       <c r="B77" t="n">
-        <v>79857</v>
+        <v>91030</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9926,41 +9944,46 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229748</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444402</v>
+        <v>444478</v>
       </c>
       <c r="R77" t="n">
-        <v>7030044</v>
+        <v>7029836</v>
       </c>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9989,7 +10012,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9999,7 +10022,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10010,21 +10038,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10034,17 +10047,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124398408</v>
+        <v>124398748</v>
       </c>
       <c r="B78" t="n">
-        <v>77743</v>
+        <v>79341</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10053,41 +10066,50 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>1350</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444419</v>
+        <v>444401</v>
       </c>
       <c r="R78" t="n">
-        <v>7029740</v>
+        <v>7029685</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10116,7 +10138,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10126,12 +10148,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10146,22 +10168,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124398668</v>
+        <v>124400074</v>
       </c>
       <c r="B79" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10170,30 +10192,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10201,19 +10223,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444415</v>
+        <v>444429</v>
       </c>
       <c r="R79" t="n">
-        <v>7029660</v>
+        <v>7029784</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10242,7 +10269,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10252,12 +10279,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10272,22 +10299,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124398839</v>
+        <v>124398327</v>
       </c>
       <c r="B80" t="n">
-        <v>78998</v>
+        <v>91030</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10296,47 +10323,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>230552</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444409</v>
+        <v>444463</v>
       </c>
       <c r="R80" t="n">
-        <v>7029694</v>
+        <v>7029765</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10368,7 +10386,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10378,12 +10396,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10410,10 +10428,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124398748</v>
+        <v>124399273</v>
       </c>
       <c r="B81" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10422,35 +10440,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10459,13 +10477,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444401</v>
+        <v>444468</v>
       </c>
       <c r="R81" t="n">
-        <v>7029685</v>
+        <v>7029811</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10494,7 +10512,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10504,12 +10522,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10524,22 +10542,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124398327</v>
+        <v>124398668</v>
       </c>
       <c r="B82" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10548,41 +10566,50 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444463</v>
+        <v>444415</v>
       </c>
       <c r="R82" t="n">
-        <v>7029765</v>
+        <v>7029660</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10611,7 +10638,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10621,12 +10648,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10641,22 +10668,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124399357</v>
+        <v>124399091</v>
       </c>
       <c r="B83" t="n">
-        <v>79066</v>
+        <v>79795</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10669,21 +10696,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6459</v>
+        <v>6456</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10693,13 +10720,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444468</v>
+        <v>444439</v>
       </c>
       <c r="R83" t="n">
-        <v>7029811</v>
+        <v>7029686</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10728,7 +10755,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10738,12 +10765,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10758,12 +10785,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10891,10 +10918,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124396024</v>
+        <v>124398839</v>
       </c>
       <c r="B85" t="n">
-        <v>79920</v>
+        <v>78998</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10903,41 +10930,50 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>230552</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444388</v>
+        <v>444409</v>
       </c>
       <c r="R85" t="n">
-        <v>7030037</v>
+        <v>7029694</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10966,7 +11002,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10976,12 +11012,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11001,17 +11037,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124398979</v>
+        <v>124399597</v>
       </c>
       <c r="B86" t="n">
-        <v>91030</v>
+        <v>91705</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11020,50 +11056,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444424</v>
+        <v>444456</v>
       </c>
       <c r="R86" t="n">
-        <v>7029676</v>
+        <v>7029772</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11092,7 +11119,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11102,7 +11129,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11117,22 +11149,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124399157</v>
+        <v>124397408</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11141,41 +11173,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444448</v>
+        <v>444276</v>
       </c>
       <c r="R87" t="n">
-        <v>7029741</v>
+        <v>7030094</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11204,7 +11236,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11214,12 +11246,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11246,10 +11278,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124399819</v>
+        <v>124396024</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11258,50 +11290,41 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444478</v>
+        <v>444388</v>
       </c>
       <c r="R88" t="n">
-        <v>7029836</v>
+        <v>7030037</v>
       </c>
       <c r="S88" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11330,7 +11353,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11340,12 +11363,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11360,22 +11383,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124399409</v>
+        <v>124398979</v>
       </c>
       <c r="B89" t="n">
-        <v>91282</v>
+        <v>91030</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11388,34 +11411,43 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444464</v>
+        <v>444424</v>
       </c>
       <c r="R89" t="n">
-        <v>7029781</v>
+        <v>7029676</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11447,7 +11479,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11457,12 +11489,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11477,22 +11504,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124399850</v>
+        <v>124398951</v>
       </c>
       <c r="B90" t="n">
-        <v>79927</v>
+        <v>79348</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11501,41 +11528,55 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6464</v>
+        <v>1353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444432</v>
+        <v>444424</v>
       </c>
       <c r="R90" t="n">
-        <v>7029779</v>
+        <v>7029691</v>
       </c>
       <c r="S90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11564,7 +11605,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11574,12 +11615,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11606,10 +11647,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124399597</v>
+        <v>124398408</v>
       </c>
       <c r="B91" t="n">
-        <v>91705</v>
+        <v>77743</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11618,25 +11659,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>67</v>
+        <v>228579</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11646,13 +11687,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444456</v>
+        <v>444419</v>
       </c>
       <c r="R91" t="n">
-        <v>7029772</v>
+        <v>7029740</v>
       </c>
       <c r="S91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11681,7 +11722,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11691,12 +11732,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11711,22 +11752,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124397708</v>
+        <v>124398709</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>79348</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11735,30 +11776,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11772,13 +11813,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444403</v>
+        <v>444401</v>
       </c>
       <c r="R92" t="n">
-        <v>7029971</v>
+        <v>7029685</v>
       </c>
       <c r="S92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11807,7 +11848,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11817,7 +11858,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11832,22 +11878,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124398951</v>
+        <v>124397876</v>
       </c>
       <c r="B93" t="n">
-        <v>79348</v>
+        <v>91413</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11856,52 +11902,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1353</v>
+        <v>4217</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444424</v>
+        <v>444498</v>
       </c>
       <c r="R93" t="n">
-        <v>7029691</v>
+        <v>7029879</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11933,7 +11965,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11943,12 +11975,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11968,17 +12000,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124398118</v>
+        <v>124399157</v>
       </c>
       <c r="B94" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11987,25 +12019,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12015,13 +12047,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444492</v>
+        <v>444448</v>
       </c>
       <c r="R94" t="n">
-        <v>7029851</v>
+        <v>7029741</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12050,7 +12082,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12060,12 +12092,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12092,10 +12124,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124399091</v>
+        <v>124397664</v>
       </c>
       <c r="B95" t="n">
-        <v>79795</v>
+        <v>95335</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12108,37 +12140,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444439</v>
+        <v>444403</v>
       </c>
       <c r="R95" t="n">
-        <v>7029686</v>
+        <v>7030010</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12167,7 +12199,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12177,12 +12209,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12202,17 +12234,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124399926</v>
+        <v>124396061</v>
       </c>
       <c r="B96" t="n">
-        <v>79341</v>
+        <v>79851</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12221,50 +12253,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1350</v>
+        <v>229497</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444478</v>
+        <v>444402</v>
       </c>
       <c r="R96" t="n">
-        <v>7029836</v>
+        <v>7030044</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12293,7 +12316,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12303,12 +12326,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>På gran, bredvid asp</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12319,6 +12337,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12328,7 +12361,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -12452,10 +12485,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124399273</v>
+        <v>124399409</v>
       </c>
       <c r="B98" t="n">
-        <v>91030</v>
+        <v>91282</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12468,46 +12501,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444468</v>
+        <v>444464</v>
       </c>
       <c r="R98" t="n">
-        <v>7029811</v>
+        <v>7029781</v>
       </c>
       <c r="S98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12536,7 +12560,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12546,12 +12570,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12566,12 +12590,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12695,10 +12719,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124400074</v>
+        <v>124397463</v>
       </c>
       <c r="B100" t="n">
-        <v>79348</v>
+        <v>91012</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12707,55 +12731,46 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1353</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444429</v>
+        <v>444279</v>
       </c>
       <c r="R100" t="n">
-        <v>7029784</v>
+        <v>7030095</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12784,7 +12799,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12794,12 +12809,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12814,12 +12829,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12943,10 +12958,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124396061</v>
+        <v>124399997</v>
       </c>
       <c r="B102" t="n">
-        <v>79851</v>
+        <v>79348</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12955,41 +12970,55 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229497</v>
+        <v>1353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444402</v>
+        <v>444448</v>
       </c>
       <c r="R102" t="n">
-        <v>7030044</v>
+        <v>7029784</v>
       </c>
       <c r="S102" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13018,7 +13047,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13028,7 +13057,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13039,41 +13073,26 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124398709</v>
+        <v>124399357</v>
       </c>
       <c r="B103" t="n">
-        <v>79348</v>
+        <v>79066</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13082,50 +13101,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1353</v>
+        <v>6459</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444401</v>
+        <v>444468</v>
       </c>
       <c r="R103" t="n">
-        <v>7029685</v>
+        <v>7029811</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13154,7 +13164,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13164,12 +13174,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13184,22 +13194,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124399997</v>
+        <v>124398118</v>
       </c>
       <c r="B104" t="n">
-        <v>79348</v>
+        <v>91950</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13208,55 +13218,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1353</v>
+        <v>4769</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444448</v>
+        <v>444492</v>
       </c>
       <c r="R104" t="n">
-        <v>7029784</v>
+        <v>7029851</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13285,7 +13281,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13295,12 +13291,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13327,10 +13323,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124397664</v>
+        <v>124397708</v>
       </c>
       <c r="B105" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13339,41 +13335,50 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
         <v>444403</v>
       </c>
       <c r="R105" t="n">
-        <v>7030010</v>
+        <v>7029971</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13407,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13417,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13432,22 +13432,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009443</v>
+        <v>125009445</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>79346</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13460,37 +13460,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R106" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S106" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13556,10 +13556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125009446</v>
+        <v>125009443</v>
       </c>
       <c r="B107" t="n">
-        <v>79348</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13568,41 +13568,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R107" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009447</v>
+        <v>125009446</v>
       </c>
       <c r="B108" t="n">
-        <v>79795</v>
+        <v>79348</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13680,25 +13680,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6456</v>
+        <v>1353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009445</v>
+        <v>125009447</v>
       </c>
       <c r="B109" t="n">
-        <v>79346</v>
+        <v>79795</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13792,25 +13792,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1352</v>
+        <v>6456</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -10054,10 +10054,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124398748</v>
+        <v>124400074</v>
       </c>
       <c r="B78" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10066,25 +10066,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10097,19 +10097,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444401</v>
+        <v>444429</v>
       </c>
       <c r="R78" t="n">
-        <v>7029685</v>
+        <v>7029784</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10138,7 +10143,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10148,12 +10153,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10180,10 +10185,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124400074</v>
+        <v>124398748</v>
       </c>
       <c r="B79" t="n">
-        <v>79348</v>
+        <v>79341</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10192,25 +10197,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10223,24 +10228,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444429</v>
+        <v>444401</v>
       </c>
       <c r="R79" t="n">
-        <v>7029784</v>
+        <v>7029685</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -12485,10 +12485,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124399409</v>
+        <v>124398297</v>
       </c>
       <c r="B98" t="n">
-        <v>91282</v>
+        <v>79851</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12497,25 +12497,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>73</v>
+        <v>229497</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444464</v>
+        <v>444498</v>
       </c>
       <c r="R98" t="n">
-        <v>7029781</v>
+        <v>7029821</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12570,12 +12570,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12590,22 +12590,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124398297</v>
+        <v>124399409</v>
       </c>
       <c r="B99" t="n">
-        <v>79851</v>
+        <v>91282</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12614,25 +12614,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229497</v>
+        <v>73</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12642,13 +12642,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444498</v>
+        <v>444464</v>
       </c>
       <c r="R99" t="n">
-        <v>7029821</v>
+        <v>7029781</v>
       </c>
       <c r="S99" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12687,12 +12687,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12707,12 +12707,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -11161,10 +11161,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124397408</v>
+        <v>124396024</v>
       </c>
       <c r="B87" t="n">
-        <v>79851</v>
+        <v>79920</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11177,37 +11177,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444276</v>
+        <v>444388</v>
       </c>
       <c r="R87" t="n">
-        <v>7030094</v>
+        <v>7030037</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11271,17 +11271,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124396024</v>
+        <v>124397408</v>
       </c>
       <c r="B88" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11294,37 +11294,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444388</v>
+        <v>444276</v>
       </c>
       <c r="R88" t="n">
-        <v>7030037</v>
+        <v>7030094</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -12719,10 +12719,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124397463</v>
+        <v>124397972</v>
       </c>
       <c r="B100" t="n">
-        <v>91012</v>
+        <v>79341</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12731,46 +12731,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>1350</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444279</v>
+        <v>444487</v>
       </c>
       <c r="R100" t="n">
-        <v>7030095</v>
+        <v>7029857</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12799,7 +12794,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12809,12 +12804,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12829,22 +12824,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124397972</v>
+        <v>124399997</v>
       </c>
       <c r="B101" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12853,41 +12848,55 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444487</v>
+        <v>444448</v>
       </c>
       <c r="R101" t="n">
-        <v>7029857</v>
+        <v>7029784</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12916,7 +12925,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12926,12 +12935,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12951,17 +12960,17 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124399997</v>
+        <v>124399357</v>
       </c>
       <c r="B102" t="n">
-        <v>79348</v>
+        <v>79066</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12970,55 +12979,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1353</v>
+        <v>6459</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444448</v>
+        <v>444468</v>
       </c>
       <c r="R102" t="n">
-        <v>7029784</v>
+        <v>7029811</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13047,7 +13042,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13057,12 +13052,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13077,22 +13072,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124399357</v>
+        <v>124398118</v>
       </c>
       <c r="B103" t="n">
-        <v>79066</v>
+        <v>91950</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13105,21 +13100,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6459</v>
+        <v>4769</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13129,13 +13124,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444468</v>
+        <v>444492</v>
       </c>
       <c r="R103" t="n">
-        <v>7029811</v>
+        <v>7029851</v>
       </c>
       <c r="S103" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13164,7 +13159,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13174,12 +13169,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13194,22 +13189,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124398118</v>
+        <v>124397708</v>
       </c>
       <c r="B104" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13218,41 +13213,50 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444492</v>
+        <v>444403</v>
       </c>
       <c r="R104" t="n">
-        <v>7029851</v>
+        <v>7029971</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13281,7 +13285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13291,12 +13295,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:48</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13311,22 +13310,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124397708</v>
+        <v>124397463</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13339,46 +13338,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444403</v>
+        <v>444279</v>
       </c>
       <c r="R105" t="n">
-        <v>7029971</v>
+        <v>7030095</v>
       </c>
       <c r="S105" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13407,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13417,7 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124396028</v>
+        <v>124399819</v>
       </c>
       <c r="B73" t="n">
-        <v>79857</v>
+        <v>79891</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,38 +9448,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444402</v>
+        <v>444478</v>
       </c>
       <c r="R73" t="n">
-        <v>7030044</v>
+        <v>7029836</v>
       </c>
       <c r="S73" t="n">
         <v>11</v>
@@ -9511,7 +9520,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9521,7 +9530,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9532,21 +9546,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9556,17 +9555,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124399926</v>
+        <v>124399157</v>
       </c>
       <c r="B74" t="n">
-        <v>79341</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9575,50 +9574,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1350</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444478</v>
+        <v>444448</v>
       </c>
       <c r="R74" t="n">
-        <v>7029836</v>
+        <v>7029741</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9647,7 +9637,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9657,12 +9647,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9677,22 +9667,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124399819</v>
+        <v>124396028</v>
       </c>
       <c r="B75" t="n">
-        <v>79891</v>
+        <v>79857</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9701,47 +9691,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444478</v>
+        <v>444402</v>
       </c>
       <c r="R75" t="n">
-        <v>7029836</v>
+        <v>7030044</v>
       </c>
       <c r="S75" t="n">
         <v>11</v>
@@ -9773,7 +9754,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9783,12 +9764,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9799,6 +9775,21 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9808,17 +9799,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124399850</v>
+        <v>124399597</v>
       </c>
       <c r="B76" t="n">
-        <v>79927</v>
+        <v>91705</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9827,25 +9818,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>67</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9855,10 +9846,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444432</v>
+        <v>444456</v>
       </c>
       <c r="R76" t="n">
-        <v>7029779</v>
+        <v>7029772</v>
       </c>
       <c r="S76" t="n">
         <v>8</v>
@@ -9890,7 +9881,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9900,12 +9891,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9932,10 +9923,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124399571</v>
+        <v>124399926</v>
       </c>
       <c r="B77" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9944,31 +9935,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9983,7 +9978,7 @@
         <v>7029836</v>
       </c>
       <c r="S77" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10012,7 +10007,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10022,12 +10017,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10054,10 +10049,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124400074</v>
+        <v>124398118</v>
       </c>
       <c r="B78" t="n">
-        <v>79348</v>
+        <v>91950</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10066,55 +10061,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1353</v>
+        <v>4769</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444429</v>
+        <v>444492</v>
       </c>
       <c r="R78" t="n">
-        <v>7029784</v>
+        <v>7029851</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10143,7 +10124,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10153,12 +10134,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10185,10 +10166,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124398748</v>
+        <v>124397463</v>
       </c>
       <c r="B79" t="n">
-        <v>79341</v>
+        <v>91012</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10197,47 +10178,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1350</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444401</v>
+        <v>444279</v>
       </c>
       <c r="R79" t="n">
-        <v>7029685</v>
+        <v>7030095</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10269,7 +10246,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10279,12 +10256,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10299,22 +10276,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124398327</v>
+        <v>124398408</v>
       </c>
       <c r="B80" t="n">
-        <v>91030</v>
+        <v>77743</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10327,21 +10304,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10351,13 +10328,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444463</v>
+        <v>444419</v>
       </c>
       <c r="R80" t="n">
-        <v>7029765</v>
+        <v>7029740</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10386,7 +10363,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10396,12 +10373,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10416,22 +10393,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124399273</v>
+        <v>124399997</v>
       </c>
       <c r="B81" t="n">
-        <v>91030</v>
+        <v>79348</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10440,35 +10417,40 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>1353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10477,13 +10459,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444468</v>
+        <v>444448</v>
       </c>
       <c r="R81" t="n">
-        <v>7029811</v>
+        <v>7029784</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10512,7 +10494,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10522,12 +10504,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10542,22 +10524,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124398668</v>
+        <v>124399409</v>
       </c>
       <c r="B82" t="n">
-        <v>79341</v>
+        <v>91282</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10566,50 +10548,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1350</v>
+        <v>73</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444415</v>
+        <v>444464</v>
       </c>
       <c r="R82" t="n">
-        <v>7029660</v>
+        <v>7029781</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10638,7 +10611,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10648,12 +10621,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10668,22 +10641,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124399091</v>
+        <v>124398748</v>
       </c>
       <c r="B83" t="n">
-        <v>79795</v>
+        <v>79341</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10692,38 +10665,47 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6456</v>
+        <v>1350</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444439</v>
+        <v>444401</v>
       </c>
       <c r="R83" t="n">
-        <v>7029686</v>
+        <v>7029685</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10755,7 +10737,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10765,12 +10747,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10797,7 +10779,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124396185</v>
+        <v>124399571</v>
       </c>
       <c r="B84" t="n">
         <v>91030</v>
@@ -10830,29 +10812,25 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444287</v>
+        <v>444478</v>
       </c>
       <c r="R84" t="n">
-        <v>7030000</v>
+        <v>7029836</v>
       </c>
       <c r="S84" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10881,7 +10859,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10891,7 +10869,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10911,17 +10894,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124398839</v>
+        <v>124397408</v>
       </c>
       <c r="B85" t="n">
-        <v>78998</v>
+        <v>79851</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10930,50 +10913,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>230552</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444409</v>
+        <v>444276</v>
       </c>
       <c r="R85" t="n">
-        <v>7029694</v>
+        <v>7030094</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11002,7 +10976,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11012,12 +10986,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11037,17 +11011,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124399597</v>
+        <v>124397876</v>
       </c>
       <c r="B86" t="n">
-        <v>91705</v>
+        <v>91413</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11056,41 +11030,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>67</v>
+        <v>4217</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444456</v>
+        <v>444498</v>
       </c>
       <c r="R86" t="n">
-        <v>7029772</v>
+        <v>7029879</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11119,7 +11093,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11129,12 +11103,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11154,17 +11128,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124396024</v>
+        <v>124398979</v>
       </c>
       <c r="B87" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11173,41 +11147,50 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444388</v>
+        <v>444424</v>
       </c>
       <c r="R87" t="n">
-        <v>7030037</v>
+        <v>7029676</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11236,7 +11219,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11246,12 +11229,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11266,22 +11244,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124397408</v>
+        <v>124397708</v>
       </c>
       <c r="B88" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11290,41 +11268,50 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444276</v>
+        <v>444403</v>
       </c>
       <c r="R88" t="n">
-        <v>7030094</v>
+        <v>7029971</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11353,7 +11340,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11363,12 +11350,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11383,22 +11365,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124398979</v>
+        <v>124398297</v>
       </c>
       <c r="B89" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11407,50 +11389,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444424</v>
+        <v>444498</v>
       </c>
       <c r="R89" t="n">
-        <v>7029676</v>
+        <v>7029821</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11479,7 +11452,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11489,7 +11462,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11516,10 +11494,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124398951</v>
+        <v>124399091</v>
       </c>
       <c r="B90" t="n">
-        <v>79348</v>
+        <v>79795</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11528,52 +11506,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1353</v>
+        <v>6456</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444424</v>
+        <v>444439</v>
       </c>
       <c r="R90" t="n">
-        <v>7029691</v>
+        <v>7029686</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11605,7 +11569,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11615,12 +11579,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11647,10 +11611,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124398408</v>
+        <v>124398709</v>
       </c>
       <c r="B91" t="n">
-        <v>77743</v>
+        <v>79348</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11659,41 +11623,50 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228579</v>
+        <v>1353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444419</v>
+        <v>444401</v>
       </c>
       <c r="R91" t="n">
-        <v>7029740</v>
+        <v>7029685</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11722,7 +11695,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11732,12 +11705,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11752,22 +11725,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124398709</v>
+        <v>124398668</v>
       </c>
       <c r="B92" t="n">
-        <v>79348</v>
+        <v>79341</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11776,30 +11749,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11813,13 +11786,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444401</v>
+        <v>444415</v>
       </c>
       <c r="R92" t="n">
-        <v>7029685</v>
+        <v>7029660</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11848,7 +11821,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11858,12 +11831,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11878,22 +11851,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124397876</v>
+        <v>124399850</v>
       </c>
       <c r="B93" t="n">
-        <v>91413</v>
+        <v>79927</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11906,37 +11879,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4217</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444498</v>
+        <v>444432</v>
       </c>
       <c r="R93" t="n">
-        <v>7029879</v>
+        <v>7029779</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11965,7 +11938,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11975,12 +11948,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12000,17 +11973,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124399157</v>
+        <v>124396185</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12023,37 +11996,46 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444448</v>
+        <v>444287</v>
       </c>
       <c r="R94" t="n">
-        <v>7029741</v>
+        <v>7030000</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12082,7 +12064,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12092,12 +12074,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12112,12 +12089,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -12241,10 +12218,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124396061</v>
+        <v>124399273</v>
       </c>
       <c r="B96" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12253,41 +12230,50 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444402</v>
+        <v>444468</v>
       </c>
       <c r="R96" t="n">
-        <v>7030044</v>
+        <v>7029811</v>
       </c>
       <c r="S96" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12316,7 +12302,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12326,7 +12312,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12337,21 +12328,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12361,17 +12337,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124399656</v>
+        <v>124400074</v>
       </c>
       <c r="B97" t="n">
-        <v>79851</v>
+        <v>79348</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12380,41 +12356,55 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>1353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444478</v>
+        <v>444429</v>
       </c>
       <c r="R97" t="n">
-        <v>7029836</v>
+        <v>7029784</v>
       </c>
       <c r="S97" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12443,7 +12433,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12453,12 +12443,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12473,7 +12463,7 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
@@ -12485,10 +12475,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124398297</v>
+        <v>124397972</v>
       </c>
       <c r="B98" t="n">
-        <v>79851</v>
+        <v>79341</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12497,25 +12487,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229497</v>
+        <v>1350</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -12525,13 +12515,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444498</v>
+        <v>444487</v>
       </c>
       <c r="R98" t="n">
-        <v>7029821</v>
+        <v>7029857</v>
       </c>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12560,7 +12550,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12570,12 +12560,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12590,22 +12580,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124399409</v>
+        <v>124398839</v>
       </c>
       <c r="B99" t="n">
-        <v>91282</v>
+        <v>78998</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12614,38 +12604,47 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>73</v>
+        <v>230552</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444464</v>
+        <v>444409</v>
       </c>
       <c r="R99" t="n">
-        <v>7029781</v>
+        <v>7029694</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12677,7 +12676,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12687,12 +12686,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12719,10 +12718,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124397972</v>
+        <v>124399357</v>
       </c>
       <c r="B100" t="n">
-        <v>79341</v>
+        <v>79066</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12731,25 +12730,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1350</v>
+        <v>6459</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12759,13 +12758,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444487</v>
+        <v>444468</v>
       </c>
       <c r="R100" t="n">
-        <v>7029857</v>
+        <v>7029811</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12794,7 +12793,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12804,12 +12803,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12824,22 +12823,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124399997</v>
+        <v>124399656</v>
       </c>
       <c r="B101" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12848,55 +12847,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444448</v>
+        <v>444478</v>
       </c>
       <c r="R101" t="n">
-        <v>7029784</v>
+        <v>7029836</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12925,7 +12910,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12935,12 +12920,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12955,7 +12940,7 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
@@ -12967,10 +12952,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124399357</v>
+        <v>124396024</v>
       </c>
       <c r="B102" t="n">
-        <v>79066</v>
+        <v>79920</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12983,21 +12968,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6459</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13007,13 +12992,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444468</v>
+        <v>444388</v>
       </c>
       <c r="R102" t="n">
-        <v>7029811</v>
+        <v>7030037</v>
       </c>
       <c r="S102" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13042,7 +13027,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13052,12 +13037,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13072,22 +13057,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124398118</v>
+        <v>124398327</v>
       </c>
       <c r="B103" t="n">
-        <v>91950</v>
+        <v>91030</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13096,25 +13081,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13124,13 +13109,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444492</v>
+        <v>444463</v>
       </c>
       <c r="R103" t="n">
-        <v>7029851</v>
+        <v>7029765</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13159,7 +13144,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13169,12 +13154,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13201,10 +13186,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124397708</v>
+        <v>124398951</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>79348</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13213,30 +13198,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13244,19 +13229,24 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444403</v>
+        <v>444424</v>
       </c>
       <c r="R104" t="n">
-        <v>7029971</v>
+        <v>7029691</v>
       </c>
       <c r="S104" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13285,7 +13275,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13295,7 +13285,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13310,22 +13305,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124397463</v>
+        <v>124396061</v>
       </c>
       <c r="B105" t="n">
-        <v>91012</v>
+        <v>79851</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13334,46 +13329,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444279</v>
+        <v>444402</v>
       </c>
       <c r="R105" t="n">
-        <v>7030095</v>
+        <v>7030044</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13392,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13402,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13428,6 +13413,21 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -13437,17 +13437,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009445</v>
+        <v>125009446</v>
       </c>
       <c r="B106" t="n">
-        <v>79346</v>
+        <v>79348</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,25 +13456,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13556,10 +13556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125009443</v>
+        <v>125009447</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13568,41 +13568,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R107" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S107" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009446</v>
+        <v>125009445</v>
       </c>
       <c r="B108" t="n">
-        <v>79348</v>
+        <v>79346</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13680,25 +13680,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009447</v>
+        <v>125009443</v>
       </c>
       <c r="B109" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13792,41 +13792,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R109" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124399819</v>
+        <v>124398297</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,50 +9448,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444478</v>
+        <v>444498</v>
       </c>
       <c r="R73" t="n">
-        <v>7029836</v>
+        <v>7029821</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9520,7 +9511,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9530,12 +9521,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9562,10 +9553,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124399157</v>
+        <v>124399409</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>91282</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9578,21 +9569,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>73</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9602,10 +9593,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444448</v>
+        <v>444464</v>
       </c>
       <c r="R74" t="n">
-        <v>7029741</v>
+        <v>7029781</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9637,7 +9628,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9647,12 +9638,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9679,10 +9670,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124396028</v>
+        <v>124399926</v>
       </c>
       <c r="B75" t="n">
-        <v>79857</v>
+        <v>79341</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9691,38 +9682,47 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229748</v>
+        <v>1350</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444402</v>
+        <v>444478</v>
       </c>
       <c r="R75" t="n">
-        <v>7030044</v>
+        <v>7029836</v>
       </c>
       <c r="S75" t="n">
         <v>11</v>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9764,7 +9764,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9775,21 +9780,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9799,17 +9789,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124399597</v>
+        <v>124396061</v>
       </c>
       <c r="B76" t="n">
-        <v>91705</v>
+        <v>79851</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9818,25 +9808,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>67</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9846,13 +9836,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444456</v>
+        <v>444402</v>
       </c>
       <c r="R76" t="n">
-        <v>7029772</v>
+        <v>7030044</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9881,7 +9871,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9891,12 +9881,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9907,26 +9892,41 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124399926</v>
+        <v>124396185</v>
       </c>
       <c r="B77" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9935,50 +9935,50 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444478</v>
+        <v>444287</v>
       </c>
       <c r="R77" t="n">
-        <v>7029836</v>
+        <v>7030000</v>
       </c>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10017,12 +10017,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gran, bredvid asp</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10042,17 +10037,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124398118</v>
+        <v>124397708</v>
       </c>
       <c r="B78" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10061,41 +10056,50 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444492</v>
+        <v>444403</v>
       </c>
       <c r="R78" t="n">
-        <v>7029851</v>
+        <v>7029971</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10124,7 +10128,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10134,12 +10138,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:48</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10154,22 +10153,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124397463</v>
+        <v>124399997</v>
       </c>
       <c r="B79" t="n">
-        <v>91012</v>
+        <v>79348</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10178,43 +10177,52 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>1353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444279</v>
+        <v>444448</v>
       </c>
       <c r="R79" t="n">
-        <v>7030095</v>
+        <v>7029784</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10246,7 +10254,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10256,12 +10264,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10276,22 +10284,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124398408</v>
+        <v>124396024</v>
       </c>
       <c r="B80" t="n">
-        <v>77743</v>
+        <v>79920</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10300,25 +10308,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10328,13 +10336,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444419</v>
+        <v>444388</v>
       </c>
       <c r="R80" t="n">
-        <v>7029740</v>
+        <v>7030037</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10363,7 +10371,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10373,12 +10381,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10393,22 +10401,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124399997</v>
+        <v>124398979</v>
       </c>
       <c r="B81" t="n">
-        <v>79348</v>
+        <v>91030</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10417,40 +10425,35 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1353</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10459,10 +10462,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444448</v>
+        <v>444424</v>
       </c>
       <c r="R81" t="n">
-        <v>7029784</v>
+        <v>7029676</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10494,7 +10497,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10504,12 +10507,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10524,22 +10522,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124399409</v>
+        <v>124399091</v>
       </c>
       <c r="B82" t="n">
-        <v>91282</v>
+        <v>79795</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10548,25 +10546,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>73</v>
+        <v>6456</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10576,10 +10574,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444464</v>
+        <v>444439</v>
       </c>
       <c r="R82" t="n">
-        <v>7029781</v>
+        <v>7029686</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10611,7 +10609,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10621,12 +10619,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10653,10 +10651,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124398748</v>
+        <v>124399273</v>
       </c>
       <c r="B83" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10665,35 +10663,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10702,13 +10700,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444401</v>
+        <v>444468</v>
       </c>
       <c r="R83" t="n">
-        <v>7029685</v>
+        <v>7029811</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10737,7 +10735,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10747,12 +10745,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10767,22 +10765,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124399571</v>
+        <v>124397408</v>
       </c>
       <c r="B84" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10791,43 +10789,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444478</v>
+        <v>444276</v>
       </c>
       <c r="R84" t="n">
-        <v>7029836</v>
+        <v>7030094</v>
       </c>
       <c r="S84" t="n">
         <v>9</v>
@@ -10859,7 +10852,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10869,12 +10862,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10889,22 +10882,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124397408</v>
+        <v>124399357</v>
       </c>
       <c r="B85" t="n">
-        <v>79851</v>
+        <v>79066</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10917,37 +10910,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>6459</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444276</v>
+        <v>444468</v>
       </c>
       <c r="R85" t="n">
-        <v>7030094</v>
+        <v>7029811</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10976,7 +10969,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10986,12 +10979,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11006,7 +10999,7 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
@@ -11018,10 +11011,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124397876</v>
+        <v>124399597</v>
       </c>
       <c r="B86" t="n">
-        <v>91413</v>
+        <v>91705</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11030,41 +11023,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4217</v>
+        <v>67</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444498</v>
+        <v>444456</v>
       </c>
       <c r="R86" t="n">
-        <v>7029879</v>
+        <v>7029772</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11093,7 +11086,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11103,12 +11096,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11128,17 +11121,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124398979</v>
+        <v>124398668</v>
       </c>
       <c r="B87" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11147,35 +11140,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11184,13 +11177,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444424</v>
+        <v>444415</v>
       </c>
       <c r="R87" t="n">
-        <v>7029676</v>
+        <v>7029660</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11219,7 +11212,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11229,7 +11222,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11249,17 +11247,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124397708</v>
+        <v>124398327</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11272,46 +11270,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444403</v>
+        <v>444463</v>
       </c>
       <c r="R88" t="n">
-        <v>7029971</v>
+        <v>7029765</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11340,7 +11329,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11350,7 +11339,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11365,22 +11359,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124398297</v>
+        <v>124398951</v>
       </c>
       <c r="B89" t="n">
-        <v>79851</v>
+        <v>79348</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11389,41 +11383,55 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229497</v>
+        <v>1353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444498</v>
+        <v>444424</v>
       </c>
       <c r="R89" t="n">
-        <v>7029821</v>
+        <v>7029691</v>
       </c>
       <c r="S89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11452,7 +11460,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11462,12 +11470,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gråal</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11482,22 +11490,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124399091</v>
+        <v>124398709</v>
       </c>
       <c r="B90" t="n">
-        <v>79795</v>
+        <v>79348</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11506,41 +11514,50 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6456</v>
+        <v>1353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444439</v>
+        <v>444401</v>
       </c>
       <c r="R90" t="n">
-        <v>7029686</v>
+        <v>7029685</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11569,7 +11586,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11579,12 +11596,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11604,17 +11621,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124398709</v>
+        <v>124398748</v>
       </c>
       <c r="B91" t="n">
-        <v>79348</v>
+        <v>79341</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11623,25 +11640,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Arnold) Bitter</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11666,7 +11683,7 @@
         <v>7029685</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11710,7 +11727,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11730,17 +11747,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124398668</v>
+        <v>124397876</v>
       </c>
       <c r="B92" t="n">
-        <v>79341</v>
+        <v>91413</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11749,50 +11766,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1350</v>
+        <v>4217</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444415</v>
+        <v>444498</v>
       </c>
       <c r="R92" t="n">
-        <v>7029660</v>
+        <v>7029879</v>
       </c>
       <c r="S92" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11821,7 +11829,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11831,12 +11839,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11851,12 +11859,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11980,10 +11988,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124396185</v>
+        <v>124399157</v>
       </c>
       <c r="B94" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11996,46 +12004,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444287</v>
+        <v>444448</v>
       </c>
       <c r="R94" t="n">
-        <v>7030000</v>
+        <v>7029741</v>
       </c>
       <c r="S94" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12064,7 +12063,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12074,7 +12073,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12089,22 +12093,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124397664</v>
+        <v>124398839</v>
       </c>
       <c r="B95" t="n">
-        <v>95335</v>
+        <v>78998</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12113,41 +12117,50 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2809</v>
+        <v>230552</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444403</v>
+        <v>444409</v>
       </c>
       <c r="R95" t="n">
-        <v>7030010</v>
+        <v>7029694</v>
       </c>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12176,7 +12189,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12186,12 +12199,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12211,17 +12224,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124399273</v>
+        <v>124399656</v>
       </c>
       <c r="B96" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12230,50 +12243,41 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444468</v>
+        <v>444478</v>
       </c>
       <c r="R96" t="n">
-        <v>7029811</v>
+        <v>7029836</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12302,7 +12306,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12312,12 +12316,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12344,10 +12348,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124400074</v>
+        <v>124397463</v>
       </c>
       <c r="B97" t="n">
-        <v>79348</v>
+        <v>91012</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12356,55 +12360,46 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1353</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444429</v>
+        <v>444279</v>
       </c>
       <c r="R97" t="n">
-        <v>7029784</v>
+        <v>7030095</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12433,7 +12428,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12443,12 +12438,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12463,22 +12458,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124397972</v>
+        <v>124400074</v>
       </c>
       <c r="B98" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12487,38 +12482,52 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444487</v>
+        <v>444429</v>
       </c>
       <c r="R98" t="n">
-        <v>7029857</v>
+        <v>7029784</v>
       </c>
       <c r="S98" t="n">
         <v>6</v>
@@ -12550,7 +12559,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12560,12 +12569,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12585,17 +12594,17 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124398839</v>
+        <v>124397972</v>
       </c>
       <c r="B99" t="n">
-        <v>78998</v>
+        <v>79341</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12608,46 +12617,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>230552</v>
+        <v>1350</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444409</v>
+        <v>444487</v>
       </c>
       <c r="R99" t="n">
-        <v>7029694</v>
+        <v>7029857</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12686,12 +12686,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12711,17 +12711,17 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124399357</v>
+        <v>124399571</v>
       </c>
       <c r="B100" t="n">
-        <v>79066</v>
+        <v>91030</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12730,41 +12730,46 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6459</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>444468</v>
+        <v>444478</v>
       </c>
       <c r="R100" t="n">
-        <v>7029811</v>
+        <v>7029836</v>
       </c>
       <c r="S100" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12793,7 +12798,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12803,12 +12808,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12835,10 +12840,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124399656</v>
+        <v>124398408</v>
       </c>
       <c r="B101" t="n">
-        <v>79851</v>
+        <v>77743</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12847,25 +12852,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229497</v>
+        <v>228579</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12875,13 +12880,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444478</v>
+        <v>444419</v>
       </c>
       <c r="R101" t="n">
-        <v>7029836</v>
+        <v>7029740</v>
       </c>
       <c r="S101" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12910,7 +12915,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12920,12 +12925,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12952,10 +12957,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124396024</v>
+        <v>124396028</v>
       </c>
       <c r="B102" t="n">
-        <v>79920</v>
+        <v>79857</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12968,21 +12973,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>229748</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12992,13 +12997,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444388</v>
+        <v>444402</v>
       </c>
       <c r="R102" t="n">
-        <v>7030037</v>
+        <v>7030044</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13040,11 +13045,6 @@
           <t>15:44</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -13053,26 +13053,41 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124398327</v>
+        <v>124398118</v>
       </c>
       <c r="B103" t="n">
-        <v>91030</v>
+        <v>91950</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13081,25 +13096,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13109,13 +13124,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444463</v>
+        <v>444492</v>
       </c>
       <c r="R103" t="n">
-        <v>7029765</v>
+        <v>7029851</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13144,7 +13159,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13154,12 +13169,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13179,17 +13194,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124398951</v>
+        <v>124399819</v>
       </c>
       <c r="B104" t="n">
-        <v>79348</v>
+        <v>79891</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13198,25 +13213,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1353</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -13229,24 +13244,19 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444424</v>
+        <v>444478</v>
       </c>
       <c r="R104" t="n">
-        <v>7029691</v>
+        <v>7029836</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13275,7 +13285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13285,12 +13295,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13305,7 +13315,7 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
@@ -13317,10 +13327,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124396061</v>
+        <v>124397664</v>
       </c>
       <c r="B105" t="n">
-        <v>79851</v>
+        <v>95335</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13333,37 +13343,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444402</v>
+        <v>444403</v>
       </c>
       <c r="R105" t="n">
-        <v>7030044</v>
+        <v>7030010</v>
       </c>
       <c r="S105" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13392,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13402,7 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13413,41 +13428,26 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009446</v>
+        <v>125009445</v>
       </c>
       <c r="B106" t="n">
-        <v>79348</v>
+        <v>79346</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,25 +13456,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13556,10 +13556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125009447</v>
+        <v>125009446</v>
       </c>
       <c r="B107" t="n">
-        <v>79795</v>
+        <v>79348</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13568,25 +13568,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6456</v>
+        <v>1353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009445</v>
+        <v>125009447</v>
       </c>
       <c r="B108" t="n">
-        <v>79346</v>
+        <v>79795</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13680,25 +13680,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1352</v>
+        <v>6456</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -9436,10 +9436,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124398297</v>
+        <v>124398979</v>
       </c>
       <c r="B73" t="n">
-        <v>79851</v>
+        <v>91030</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9448,41 +9448,50 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444498</v>
+        <v>444424</v>
       </c>
       <c r="R73" t="n">
-        <v>7029821</v>
+        <v>7029676</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9511,7 +9520,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9521,12 +9530,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:52</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gråal</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9553,10 +9557,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124399409</v>
+        <v>124397463</v>
       </c>
       <c r="B74" t="n">
-        <v>91282</v>
+        <v>91012</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9569,34 +9573,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444464</v>
+        <v>444279</v>
       </c>
       <c r="R74" t="n">
-        <v>7029781</v>
+        <v>7030095</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9628,7 +9637,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9638,12 +9647,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gammal asplåga i gammal granskog i bäckravin</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9658,22 +9667,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124399926</v>
+        <v>124396024</v>
       </c>
       <c r="B75" t="n">
-        <v>79341</v>
+        <v>79920</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9682,50 +9691,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1350</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444478</v>
+        <v>444388</v>
       </c>
       <c r="R75" t="n">
-        <v>7029836</v>
+        <v>7030037</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På gran, bredvid asp</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9784,19 +9784,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124396061</v>
+        <v>124397408</v>
       </c>
       <c r="B76" t="n">
         <v>79851</v>
@@ -9832,17 +9832,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>444402</v>
+        <v>444276</v>
       </c>
       <c r="R76" t="n">
-        <v>7030044</v>
+        <v>7030094</v>
       </c>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9881,7 +9881,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9892,41 +9897,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124396185</v>
+        <v>124399997</v>
       </c>
       <c r="B77" t="n">
-        <v>91030</v>
+        <v>79348</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9935,50 +9925,55 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>1353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>444287</v>
+        <v>444448</v>
       </c>
       <c r="R77" t="n">
-        <v>7030000</v>
+        <v>7029784</v>
       </c>
       <c r="S77" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10007,7 +10002,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10017,7 +10012,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10032,22 +10032,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124397708</v>
+        <v>124399656</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10056,50 +10056,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>444403</v>
+        <v>444478</v>
       </c>
       <c r="R78" t="n">
-        <v>7029971</v>
+        <v>7029836</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10128,7 +10119,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10138,7 +10129,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10158,17 +10154,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124399997</v>
+        <v>124398327</v>
       </c>
       <c r="B79" t="n">
-        <v>79348</v>
+        <v>91030</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10177,52 +10173,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1353</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>444448</v>
+        <v>444463</v>
       </c>
       <c r="R79" t="n">
-        <v>7029784</v>
+        <v>7029765</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10254,7 +10236,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10264,12 +10246,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran stående under gammal lutande asp</t>
+          <t>På gammal gran vid bäck, i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10296,10 +10278,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124396024</v>
+        <v>124399409</v>
       </c>
       <c r="B80" t="n">
-        <v>79920</v>
+        <v>91282</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10308,25 +10290,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>73</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10336,13 +10318,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>444388</v>
+        <v>444464</v>
       </c>
       <c r="R80" t="n">
-        <v>7030037</v>
+        <v>7029781</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10371,7 +10353,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10381,12 +10363,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal asplåga i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10406,17 +10388,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124398979</v>
+        <v>124397664</v>
       </c>
       <c r="B81" t="n">
-        <v>91030</v>
+        <v>95335</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10425,50 +10407,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>444424</v>
+        <v>444403</v>
       </c>
       <c r="R81" t="n">
-        <v>7029676</v>
+        <v>7030010</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10497,7 +10470,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10507,7 +10480,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10522,22 +10500,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124399091</v>
+        <v>124398118</v>
       </c>
       <c r="B82" t="n">
-        <v>79795</v>
+        <v>91950</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10550,21 +10528,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6456</v>
+        <v>4769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10574,13 +10552,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>444439</v>
+        <v>444492</v>
       </c>
       <c r="R82" t="n">
-        <v>7029686</v>
+        <v>7029851</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10609,7 +10587,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10619,12 +10597,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På gammal asp i gammal granskog</t>
+          <t>På markenni bördig fuktig gammal granskog</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10651,10 +10629,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124399273</v>
+        <v>124397708</v>
       </c>
       <c r="B83" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10667,31 +10645,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10700,13 +10678,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>444468</v>
+        <v>444403</v>
       </c>
       <c r="R83" t="n">
-        <v>7029811</v>
+        <v>7029971</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10735,7 +10713,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10745,12 +10723,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10770,17 +10743,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124397408</v>
+        <v>124399597</v>
       </c>
       <c r="B84" t="n">
-        <v>79851</v>
+        <v>91705</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10789,41 +10762,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>67</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>444276</v>
+        <v>444456</v>
       </c>
       <c r="R84" t="n">
-        <v>7030094</v>
+        <v>7029772</v>
       </c>
       <c r="S84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10852,7 +10825,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10862,12 +10835,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal grov asp i gammal granskog</t>
+          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10894,10 +10867,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124399357</v>
+        <v>124399850</v>
       </c>
       <c r="B85" t="n">
-        <v>79066</v>
+        <v>79927</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10910,21 +10883,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6459</v>
+        <v>6464</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10934,13 +10907,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>444468</v>
+        <v>444432</v>
       </c>
       <c r="R85" t="n">
-        <v>7029811</v>
+        <v>7029779</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10969,7 +10942,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10979,12 +10952,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10999,22 +10972,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124399597</v>
+        <v>124398839</v>
       </c>
       <c r="B86" t="n">
-        <v>91705</v>
+        <v>78998</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11027,37 +11000,46 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>67</v>
+        <v>230552</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>444456</v>
+        <v>444409</v>
       </c>
       <c r="R86" t="n">
-        <v>7029772</v>
+        <v>7029694</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11086,7 +11068,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11096,12 +11078,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På bark på klen gammal granlåga (12 cm diameter) i gammal granskog i bäckravin</t>
+          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11128,10 +11110,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124398668</v>
+        <v>124398709</v>
       </c>
       <c r="B87" t="n">
-        <v>79341</v>
+        <v>79348</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11140,30 +11122,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11177,13 +11159,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>444415</v>
+        <v>444401</v>
       </c>
       <c r="R87" t="n">
-        <v>7029660</v>
+        <v>7029685</v>
       </c>
       <c r="S87" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11212,7 +11194,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11222,12 +11204,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11242,22 +11224,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124398327</v>
+        <v>124398297</v>
       </c>
       <c r="B88" t="n">
-        <v>91030</v>
+        <v>79851</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11266,25 +11248,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11294,13 +11276,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>444463</v>
+        <v>444498</v>
       </c>
       <c r="R88" t="n">
-        <v>7029765</v>
+        <v>7029821</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11329,7 +11311,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11339,12 +11321,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På gammal gran vid bäck, i gammal granskog</t>
+          <t>På gråal</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11359,22 +11341,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124398951</v>
+        <v>124397876</v>
       </c>
       <c r="B89" t="n">
-        <v>79348</v>
+        <v>91413</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11383,52 +11365,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1353</v>
+        <v>4217</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>444424</v>
+        <v>444498</v>
       </c>
       <c r="R89" t="n">
-        <v>7029691</v>
+        <v>7029879</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11460,7 +11428,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11470,12 +11438,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
+          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11495,17 +11463,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124398709</v>
+        <v>124396028</v>
       </c>
       <c r="B90" t="n">
-        <v>79348</v>
+        <v>79857</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11514,50 +11482,41 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1353</v>
+        <v>229748</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>444401</v>
+        <v>444402</v>
       </c>
       <c r="R90" t="n">
-        <v>7029685</v>
+        <v>7030044</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11586,7 +11545,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11596,12 +11555,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På tunn död kvist på gammal grov levande gran i gammal granskog vid bäck, bäckravin</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11612,26 +11566,41 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124398748</v>
+        <v>124399357</v>
       </c>
       <c r="B91" t="n">
-        <v>79341</v>
+        <v>79066</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11640,50 +11609,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1350</v>
+        <v>6459</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>444401</v>
+        <v>444468</v>
       </c>
       <c r="R91" t="n">
-        <v>7029685</v>
+        <v>7029811</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11712,7 +11672,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11722,12 +11682,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11742,7 +11702,7 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
@@ -11754,10 +11714,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124397876</v>
+        <v>124398408</v>
       </c>
       <c r="B92" t="n">
-        <v>91413</v>
+        <v>77743</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11766,41 +11726,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4217</v>
+        <v>228579</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>444498</v>
+        <v>444419</v>
       </c>
       <c r="R92" t="n">
-        <v>7029879</v>
+        <v>7029740</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11829,7 +11789,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11839,12 +11799,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På bark på död grangren på 200-årig gran vid bäck i gammal gransumpskog</t>
+          <t>På liten gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11859,22 +11819,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124399850</v>
+        <v>124399819</v>
       </c>
       <c r="B93" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11883,41 +11843,50 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>444432</v>
+        <v>444478</v>
       </c>
       <c r="R93" t="n">
-        <v>7029779</v>
+        <v>7029836</v>
       </c>
       <c r="S93" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11946,7 +11915,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11956,12 +11925,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11976,22 +11945,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124399157</v>
+        <v>124399571</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12004,37 +11973,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>444448</v>
+        <v>444478</v>
       </c>
       <c r="R94" t="n">
-        <v>7029741</v>
+        <v>7029836</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12063,7 +12037,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12073,12 +12047,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12093,22 +12067,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124398839</v>
+        <v>124398951</v>
       </c>
       <c r="B95" t="n">
-        <v>78998</v>
+        <v>79348</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12117,30 +12091,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>230552</v>
+        <v>1353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -12148,16 +12122,21 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>444409</v>
+        <v>444424</v>
       </c>
       <c r="R95" t="n">
-        <v>7029694</v>
+        <v>7029691</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12189,7 +12168,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12199,12 +12178,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i bäckravin med gammal granskog</t>
+          <t>På död gren på gammal levande gran under grov gammal asp (aspdropp)</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12231,10 +12210,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124399656</v>
+        <v>124398668</v>
       </c>
       <c r="B96" t="n">
-        <v>79851</v>
+        <v>79341</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12243,41 +12222,50 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229497</v>
+        <v>1350</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>444478</v>
+        <v>444415</v>
       </c>
       <c r="R96" t="n">
-        <v>7029836</v>
+        <v>7029660</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12306,7 +12294,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12316,12 +12304,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12348,10 +12336,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124397463</v>
+        <v>124400074</v>
       </c>
       <c r="B97" t="n">
-        <v>91012</v>
+        <v>79348</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12360,46 +12348,55 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>1353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>444279</v>
+        <v>444429</v>
       </c>
       <c r="R97" t="n">
-        <v>7030095</v>
+        <v>7029784</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12428,7 +12425,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12438,12 +12435,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12458,22 +12455,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124400074</v>
+        <v>124396061</v>
       </c>
       <c r="B98" t="n">
-        <v>79348</v>
+        <v>79851</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12482,55 +12479,41 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1353</v>
+        <v>229497</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>444429</v>
+        <v>444402</v>
       </c>
       <c r="R98" t="n">
-        <v>7029784</v>
+        <v>7030044</v>
       </c>
       <c r="S98" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12559,7 +12542,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12569,12 +12552,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På tunna döda kvistar på gammal levande gran i gammal asprik granskog</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12585,26 +12563,41 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124397972</v>
+        <v>124399273</v>
       </c>
       <c r="B99" t="n">
-        <v>79341</v>
+        <v>91030</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12613,41 +12606,50 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1350</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trubbig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramalina obtusata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Arnold) Bitter</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>444487</v>
+        <v>444468</v>
       </c>
       <c r="R99" t="n">
-        <v>7029857</v>
+        <v>7029811</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12676,7 +12678,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12686,12 +12688,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12706,22 +12708,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124399571</v>
+        <v>124399926</v>
       </c>
       <c r="B100" t="n">
-        <v>91030</v>
+        <v>79341</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12730,31 +12732,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>1350</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12769,7 +12775,7 @@
         <v>7029836</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12798,7 +12804,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12808,12 +12814,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På gran, bredvid asp</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12840,10 +12846,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124398408</v>
+        <v>124398748</v>
       </c>
       <c r="B101" t="n">
-        <v>77743</v>
+        <v>79341</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12852,41 +12858,50 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228579</v>
+        <v>1350</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>444419</v>
+        <v>444401</v>
       </c>
       <c r="R101" t="n">
-        <v>7029740</v>
+        <v>7029685</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12915,7 +12930,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12925,12 +12940,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>På liten gran</t>
+          <t>På tunn död kvist på gammal levande gran i gammal granskog i bäckravin</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12945,7 +12960,7 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
@@ -12957,10 +12972,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124396028</v>
+        <v>124396185</v>
       </c>
       <c r="B102" t="n">
-        <v>79857</v>
+        <v>91030</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12969,41 +12984,50 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229748</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Blodbäcken, Blodbäcken, Jmt</t>
+          <t>Åringsån, Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>444402</v>
+        <v>444287</v>
       </c>
       <c r="R102" t="n">
-        <v>7030044</v>
+        <v>7030000</v>
       </c>
       <c r="S102" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13032,7 +13056,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13042,7 +13066,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13053,21 +13077,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13077,17 +13086,17 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124398118</v>
+        <v>124399157</v>
       </c>
       <c r="B103" t="n">
-        <v>91950</v>
+        <v>78810</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13096,25 +13105,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13124,13 +13133,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>444492</v>
+        <v>444448</v>
       </c>
       <c r="R103" t="n">
-        <v>7029851</v>
+        <v>7029741</v>
       </c>
       <c r="S103" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13159,7 +13168,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13169,12 +13178,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På markenni bördig fuktig gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13194,17 +13203,17 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124399819</v>
+        <v>124397972</v>
       </c>
       <c r="B104" t="n">
-        <v>79891</v>
+        <v>79341</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13213,50 +13222,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>1350</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trubbig brosklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramalina obtusata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Arnold) Bitter</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>444478</v>
+        <v>444487</v>
       </c>
       <c r="R104" t="n">
-        <v>7029836</v>
+        <v>7029857</v>
       </c>
       <c r="S104" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13295,12 +13295,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På tunn död kvist på gammal gran vid bäck med gammal granskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13315,22 +13315,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124397664</v>
+        <v>124399091</v>
       </c>
       <c r="B105" t="n">
-        <v>95335</v>
+        <v>79795</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13343,37 +13343,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Åringsån, Åringsån, Jmt</t>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>444403</v>
+        <v>444439</v>
       </c>
       <c r="R105" t="n">
-        <v>7030010</v>
+        <v>7029686</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog</t>
+          <t>På gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13437,17 +13437,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009445</v>
+        <v>125009447</v>
       </c>
       <c r="B106" t="n">
-        <v>79346</v>
+        <v>79795</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,25 +13456,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1352</v>
+        <v>6456</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009447</v>
+        <v>125009443</v>
       </c>
       <c r="B108" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13680,41 +13680,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R108" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009443</v>
+        <v>125009445</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>79346</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13796,37 +13796,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R109" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S109" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13444,10 +13444,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009447</v>
+        <v>125009445</v>
       </c>
       <c r="B106" t="n">
-        <v>79795</v>
+        <v>79346</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,25 +13456,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6456</v>
+        <v>1352</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13556,10 +13556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125009446</v>
+        <v>125009443</v>
       </c>
       <c r="B107" t="n">
-        <v>79348</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13568,41 +13568,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R107" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009443</v>
+        <v>125009447</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13680,41 +13680,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R108" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S108" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009445</v>
+        <v>125009446</v>
       </c>
       <c r="B109" t="n">
-        <v>79346</v>
+        <v>79348</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13792,25 +13792,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13444,10 +13444,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009445</v>
+        <v>125009446</v>
       </c>
       <c r="B106" t="n">
-        <v>79346</v>
+        <v>79348</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,25 +13456,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13556,10 +13556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125009443</v>
+        <v>125009445</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>79346</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13572,37 +13572,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R107" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S107" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009447</v>
+        <v>125009443</v>
       </c>
       <c r="B108" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13680,41 +13680,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R108" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009446</v>
+        <v>125009447</v>
       </c>
       <c r="B109" t="n">
-        <v>79348</v>
+        <v>79795</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13792,25 +13792,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1353</v>
+        <v>6456</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13444,10 +13444,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009446</v>
+        <v>125009447</v>
       </c>
       <c r="B106" t="n">
-        <v>79348</v>
+        <v>79932</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,25 +13456,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1353</v>
+        <v>6456</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13559,7 +13559,7 @@
         <v>125009445</v>
       </c>
       <c r="B107" t="n">
-        <v>79346</v>
+        <v>79483</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009443</v>
+        <v>125009446</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>79485</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13680,41 +13680,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R108" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S108" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009447</v>
+        <v>125009443</v>
       </c>
       <c r="B109" t="n">
-        <v>79795</v>
+        <v>78947</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13792,41 +13792,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R109" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13444,10 +13444,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125009447</v>
+        <v>125009443</v>
       </c>
       <c r="B106" t="n">
-        <v>79932</v>
+        <v>78947</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13456,41 +13456,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>444364</v>
+        <v>444409</v>
       </c>
       <c r="R106" t="n">
-        <v>7029824</v>
+        <v>7029856</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13556,10 +13556,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125009445</v>
+        <v>125009446</v>
       </c>
       <c r="B107" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13568,25 +13568,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -13668,10 +13668,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125009446</v>
+        <v>125009447</v>
       </c>
       <c r="B108" t="n">
-        <v>79485</v>
+        <v>79932</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13680,25 +13680,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1353</v>
+        <v>6456</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13780,10 +13780,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125009443</v>
+        <v>125009445</v>
       </c>
       <c r="B109" t="n">
-        <v>78947</v>
+        <v>79483</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13796,37 +13796,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>MD4:Krokom Municipality, Sweden, Jmt</t>
+          <t>MD0:Krokom Municipality, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>444409</v>
+        <v>444364</v>
       </c>
       <c r="R109" t="n">
-        <v>7029856</v>
+        <v>7029824</v>
       </c>
       <c r="S109" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13870,6 +13870,1448 @@
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>127795738</v>
+      </c>
+      <c r="B110" t="n">
+        <v>92284</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>444456</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7029681</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127795783</v>
+      </c>
+      <c r="B111" t="n">
+        <v>97476</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>444423</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7029735</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>127792860</v>
+      </c>
+      <c r="B112" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>444249</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7029797</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127792888</v>
+      </c>
+      <c r="B113" t="n">
+        <v>88604</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>444268</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7029817</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127790050</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91352</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>444354</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7029940</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Frisk barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>127796085</v>
+      </c>
+      <c r="B115" t="n">
+        <v>90877</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>444409</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7029721</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>127796014</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91385</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>444439</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7029791</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>127793330</v>
+      </c>
+      <c r="B117" t="n">
+        <v>91328</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>444511</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7029881</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>127796634</v>
+      </c>
+      <c r="B118" t="n">
+        <v>86868</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>444581</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7029857</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>127796374</v>
+      </c>
+      <c r="B119" t="n">
+        <v>90105</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>245031</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Borgsjömusseron</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Tricholoma borgsjoeënse</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Jacobsson &amp; Muskos</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>444523</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7029733</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Dagarna går.</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>127794557</v>
+      </c>
+      <c r="B120" t="n">
+        <v>100539</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>444781</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7029795</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>Yngre men naturligt föryngrad och bördig granskog på frisk mark</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>127794015</v>
+      </c>
+      <c r="B121" t="n">
+        <v>92267</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>444580</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7029839</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>127796561</v>
+      </c>
+      <c r="B122" t="n">
+        <v>88604</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>444575</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7029739</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>127795163</v>
+      </c>
+      <c r="B123" t="n">
+        <v>92029</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>444553</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7029700</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13875,7 +13875,7 @@
         <v>127795738</v>
       </c>
       <c r="B110" t="n">
-        <v>92284</v>
+        <v>92290</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>127795783</v>
       </c>
       <c r="B111" t="n">
-        <v>97476</v>
+        <v>97482</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>127792860</v>
       </c>
       <c r="B112" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14178,10 +14178,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127792888</v>
+        <v>127790050</v>
       </c>
       <c r="B113" t="n">
-        <v>88604</v>
+        <v>91358</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14189,34 +14189,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4412</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444268</v>
+        <v>444354</v>
       </c>
       <c r="R113" t="n">
-        <v>7029817</v>
+        <v>7029940</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14257,12 +14260,13 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Bördig och näringsrik naturskog med gran och tall</t>
+          <t>Frisk barrblandskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14280,10 +14284,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127790050</v>
+        <v>127792888</v>
       </c>
       <c r="B114" t="n">
-        <v>91352</v>
+        <v>88610</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14291,37 +14295,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>4412</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444354</v>
+        <v>444268</v>
       </c>
       <c r="R114" t="n">
-        <v>7029940</v>
+        <v>7029817</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14362,13 +14363,12 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Frisk barrblandskog</t>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14389,7 +14389,7 @@
         <v>127796085</v>
       </c>
       <c r="B115" t="n">
-        <v>90877</v>
+        <v>90883</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14488,32 +14488,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127796014</v>
+        <v>127793330</v>
       </c>
       <c r="B116" t="n">
-        <v>91385</v>
+        <v>91334</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5321</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444439</v>
+        <v>444511</v>
       </c>
       <c r="R116" t="n">
-        <v>7029791</v>
+        <v>7029881</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14590,32 +14590,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127793330</v>
+        <v>127796014</v>
       </c>
       <c r="B117" t="n">
-        <v>91328</v>
+        <v>91391</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1108</v>
+        <v>5321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444511</v>
+        <v>444439</v>
       </c>
       <c r="R117" t="n">
-        <v>7029881</v>
+        <v>7029791</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14695,7 +14695,7 @@
         <v>127796634</v>
       </c>
       <c r="B118" t="n">
-        <v>86868</v>
+        <v>86872</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>127796374</v>
       </c>
       <c r="B119" t="n">
-        <v>90105</v>
+        <v>90111</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>127794557</v>
       </c>
       <c r="B120" t="n">
-        <v>100539</v>
+        <v>100545</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>127794015</v>
       </c>
       <c r="B121" t="n">
-        <v>92267</v>
+        <v>92273</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>127796561</v>
       </c>
       <c r="B122" t="n">
-        <v>88604</v>
+        <v>88610</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>127795163</v>
       </c>
       <c r="B123" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13875,7 +13875,7 @@
         <v>127795738</v>
       </c>
       <c r="B110" t="n">
-        <v>92290</v>
+        <v>92293</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13974,10 +13974,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127795783</v>
+        <v>127792860</v>
       </c>
       <c r="B111" t="n">
-        <v>97482</v>
+        <v>92643</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13985,21 +13985,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>222741</v>
+        <v>4366</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444423</v>
+        <v>444249</v>
       </c>
       <c r="R111" t="n">
-        <v>7029735</v>
+        <v>7029797</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14076,10 +14076,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127792860</v>
+        <v>127795783</v>
       </c>
       <c r="B112" t="n">
-        <v>92640</v>
+        <v>97485</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14087,21 +14087,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4366</v>
+        <v>222741</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14111,10 +14111,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444249</v>
+        <v>444423</v>
       </c>
       <c r="R112" t="n">
-        <v>7029797</v>
+        <v>7029735</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14178,10 +14178,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127790050</v>
+        <v>127792888</v>
       </c>
       <c r="B113" t="n">
-        <v>91358</v>
+        <v>88613</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14189,37 +14189,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>4412</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444354</v>
+        <v>444268</v>
       </c>
       <c r="R113" t="n">
-        <v>7029940</v>
+        <v>7029817</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14260,13 +14257,12 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Frisk barrblandskog</t>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14284,10 +14280,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127792888</v>
+        <v>127790050</v>
       </c>
       <c r="B114" t="n">
-        <v>88610</v>
+        <v>91361</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14295,34 +14291,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4412</v>
+        <v>5442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444268</v>
+        <v>444354</v>
       </c>
       <c r="R114" t="n">
-        <v>7029817</v>
+        <v>7029940</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14363,12 +14362,13 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Bördig och näringsrik naturskog med gran och tall</t>
+          <t>Frisk barrblandskog</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14389,7 +14389,7 @@
         <v>127796085</v>
       </c>
       <c r="B115" t="n">
-        <v>90883</v>
+        <v>90886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14488,32 +14488,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127793330</v>
+        <v>127796014</v>
       </c>
       <c r="B116" t="n">
-        <v>91334</v>
+        <v>91394</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>5321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444511</v>
+        <v>444439</v>
       </c>
       <c r="R116" t="n">
-        <v>7029881</v>
+        <v>7029791</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14590,32 +14590,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127796014</v>
+        <v>127793330</v>
       </c>
       <c r="B117" t="n">
-        <v>91391</v>
+        <v>91337</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5321</v>
+        <v>1108</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444439</v>
+        <v>444511</v>
       </c>
       <c r="R117" t="n">
-        <v>7029791</v>
+        <v>7029881</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14695,7 +14695,7 @@
         <v>127796634</v>
       </c>
       <c r="B118" t="n">
-        <v>86872</v>
+        <v>86875</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>127796374</v>
       </c>
       <c r="B119" t="n">
-        <v>90111</v>
+        <v>90114</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>127794557</v>
       </c>
       <c r="B120" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>127794015</v>
       </c>
       <c r="B121" t="n">
-        <v>92273</v>
+        <v>92276</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>127796561</v>
       </c>
       <c r="B122" t="n">
-        <v>88610</v>
+        <v>88613</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>127795163</v>
       </c>
       <c r="B123" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13875,7 +13875,7 @@
         <v>127795738</v>
       </c>
       <c r="B110" t="n">
-        <v>92293</v>
+        <v>92301</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>127792860</v>
       </c>
       <c r="B111" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>127795783</v>
       </c>
       <c r="B112" t="n">
-        <v>97485</v>
+        <v>97493</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>127792888</v>
       </c>
       <c r="B113" t="n">
-        <v>88613</v>
+        <v>88621</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>127790050</v>
       </c>
       <c r="B114" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>127796085</v>
       </c>
       <c r="B115" t="n">
-        <v>90886</v>
+        <v>90894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14488,32 +14488,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127796014</v>
+        <v>127793330</v>
       </c>
       <c r="B116" t="n">
-        <v>91394</v>
+        <v>91345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5321</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444439</v>
+        <v>444511</v>
       </c>
       <c r="R116" t="n">
-        <v>7029791</v>
+        <v>7029881</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14590,32 +14590,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127793330</v>
+        <v>127796014</v>
       </c>
       <c r="B117" t="n">
-        <v>91337</v>
+        <v>91402</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1108</v>
+        <v>5321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444511</v>
+        <v>444439</v>
       </c>
       <c r="R117" t="n">
-        <v>7029881</v>
+        <v>7029791</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14695,7 +14695,7 @@
         <v>127796634</v>
       </c>
       <c r="B118" t="n">
-        <v>86875</v>
+        <v>86882</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>127796374</v>
       </c>
       <c r="B119" t="n">
-        <v>90114</v>
+        <v>90122</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>127794557</v>
       </c>
       <c r="B120" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>127794015</v>
       </c>
       <c r="B121" t="n">
-        <v>92276</v>
+        <v>92284</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>127796561</v>
       </c>
       <c r="B122" t="n">
-        <v>88613</v>
+        <v>88621</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>127795163</v>
       </c>
       <c r="B123" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13875,7 +13875,7 @@
         <v>127795738</v>
       </c>
       <c r="B110" t="n">
-        <v>92301</v>
+        <v>92302</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>127792860</v>
       </c>
       <c r="B111" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>127795783</v>
       </c>
       <c r="B112" t="n">
-        <v>97493</v>
+        <v>97494</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14178,10 +14178,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127792888</v>
+        <v>127790050</v>
       </c>
       <c r="B113" t="n">
-        <v>88621</v>
+        <v>91370</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14189,34 +14189,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4412</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444268</v>
+        <v>444354</v>
       </c>
       <c r="R113" t="n">
-        <v>7029817</v>
+        <v>7029940</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14257,12 +14260,13 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Bördig och näringsrik naturskog med gran och tall</t>
+          <t>Frisk barrblandskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14280,10 +14284,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127790050</v>
+        <v>127792888</v>
       </c>
       <c r="B114" t="n">
-        <v>91369</v>
+        <v>88622</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14291,37 +14295,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>4412</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444354</v>
+        <v>444268</v>
       </c>
       <c r="R114" t="n">
-        <v>7029940</v>
+        <v>7029817</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14362,13 +14363,12 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Frisk barrblandskog</t>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14389,7 +14389,7 @@
         <v>127796085</v>
       </c>
       <c r="B115" t="n">
-        <v>90894</v>
+        <v>90895</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14488,32 +14488,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127793330</v>
+        <v>127796014</v>
       </c>
       <c r="B116" t="n">
-        <v>91345</v>
+        <v>91403</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>5321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444511</v>
+        <v>444439</v>
       </c>
       <c r="R116" t="n">
-        <v>7029881</v>
+        <v>7029791</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14590,32 +14590,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127796014</v>
+        <v>127793330</v>
       </c>
       <c r="B117" t="n">
-        <v>91402</v>
+        <v>91346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5321</v>
+        <v>1108</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444439</v>
+        <v>444511</v>
       </c>
       <c r="R117" t="n">
-        <v>7029791</v>
+        <v>7029881</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14793,7 +14793,7 @@
         <v>127796374</v>
       </c>
       <c r="B119" t="n">
-        <v>90122</v>
+        <v>90123</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>127794557</v>
       </c>
       <c r="B120" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>127794015</v>
       </c>
       <c r="B121" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>127796561</v>
       </c>
       <c r="B122" t="n">
-        <v>88621</v>
+        <v>88622</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>127795163</v>
       </c>
       <c r="B123" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -14488,32 +14488,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127796014</v>
+        <v>127793330</v>
       </c>
       <c r="B116" t="n">
-        <v>91403</v>
+        <v>91346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5321</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444439</v>
+        <v>444511</v>
       </c>
       <c r="R116" t="n">
-        <v>7029791</v>
+        <v>7029881</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14590,32 +14590,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127793330</v>
+        <v>127796014</v>
       </c>
       <c r="B117" t="n">
-        <v>91346</v>
+        <v>91403</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1108</v>
+        <v>5321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444511</v>
+        <v>444439</v>
       </c>
       <c r="R117" t="n">
-        <v>7029881</v>
+        <v>7029791</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13875,7 +13875,7 @@
         <v>127795738</v>
       </c>
       <c r="B110" t="n">
-        <v>92302</v>
+        <v>92303</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>127792860</v>
       </c>
       <c r="B111" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>127795783</v>
       </c>
       <c r="B112" t="n">
-        <v>97494</v>
+        <v>97495</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>127790050</v>
       </c>
       <c r="B113" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>127792888</v>
       </c>
       <c r="B114" t="n">
-        <v>88622</v>
+        <v>88623</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>127796085</v>
       </c>
       <c r="B115" t="n">
-        <v>90895</v>
+        <v>90896</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14488,32 +14488,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127793330</v>
+        <v>127796014</v>
       </c>
       <c r="B116" t="n">
-        <v>91346</v>
+        <v>91404</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>5321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444511</v>
+        <v>444439</v>
       </c>
       <c r="R116" t="n">
-        <v>7029881</v>
+        <v>7029791</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14590,32 +14590,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127796014</v>
+        <v>127793330</v>
       </c>
       <c r="B117" t="n">
-        <v>91403</v>
+        <v>91347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5321</v>
+        <v>1108</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444439</v>
+        <v>444511</v>
       </c>
       <c r="R117" t="n">
-        <v>7029791</v>
+        <v>7029881</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14695,7 +14695,7 @@
         <v>127796634</v>
       </c>
       <c r="B118" t="n">
-        <v>86882</v>
+        <v>86883</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>127796374</v>
       </c>
       <c r="B119" t="n">
-        <v>90123</v>
+        <v>90124</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>127794557</v>
       </c>
       <c r="B120" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>127794015</v>
       </c>
       <c r="B121" t="n">
-        <v>92285</v>
+        <v>92286</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>127796561</v>
       </c>
       <c r="B122" t="n">
-        <v>88622</v>
+        <v>88623</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>127795163</v>
       </c>
       <c r="B123" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13875,7 +13875,7 @@
         <v>127795738</v>
       </c>
       <c r="B110" t="n">
-        <v>92303</v>
+        <v>92304</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>127792860</v>
       </c>
       <c r="B111" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>127795783</v>
       </c>
       <c r="B112" t="n">
-        <v>97495</v>
+        <v>97496</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>127790050</v>
       </c>
       <c r="B113" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>127792888</v>
       </c>
       <c r="B114" t="n">
-        <v>88623</v>
+        <v>88624</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>127796085</v>
       </c>
       <c r="B115" t="n">
-        <v>90896</v>
+        <v>90897</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14488,32 +14488,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127796014</v>
+        <v>127793330</v>
       </c>
       <c r="B116" t="n">
-        <v>91404</v>
+        <v>91348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5321</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>444439</v>
+        <v>444511</v>
       </c>
       <c r="R116" t="n">
-        <v>7029791</v>
+        <v>7029881</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14590,32 +14590,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127793330</v>
+        <v>127796014</v>
       </c>
       <c r="B117" t="n">
-        <v>91347</v>
+        <v>91405</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1108</v>
+        <v>5321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>444511</v>
+        <v>444439</v>
       </c>
       <c r="R117" t="n">
-        <v>7029881</v>
+        <v>7029791</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14695,7 +14695,7 @@
         <v>127796634</v>
       </c>
       <c r="B118" t="n">
-        <v>86883</v>
+        <v>86884</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>127796374</v>
       </c>
       <c r="B119" t="n">
-        <v>90124</v>
+        <v>90125</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>127794557</v>
       </c>
       <c r="B120" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>127794015</v>
       </c>
       <c r="B121" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>127796561</v>
       </c>
       <c r="B122" t="n">
-        <v>88623</v>
+        <v>88624</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>127795163</v>
       </c>
       <c r="B123" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13974,10 +13974,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127792860</v>
+        <v>127795783</v>
       </c>
       <c r="B111" t="n">
-        <v>92654</v>
+        <v>97496</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13985,21 +13985,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4366</v>
+        <v>222741</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444249</v>
+        <v>444423</v>
       </c>
       <c r="R111" t="n">
-        <v>7029797</v>
+        <v>7029735</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14076,10 +14076,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127795783</v>
+        <v>127792860</v>
       </c>
       <c r="B112" t="n">
-        <v>97496</v>
+        <v>92654</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14087,21 +14087,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>222741</v>
+        <v>4366</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14111,10 +14111,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444423</v>
+        <v>444249</v>
       </c>
       <c r="R112" t="n">
-        <v>7029735</v>
+        <v>7029797</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14178,10 +14178,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127790050</v>
+        <v>127792888</v>
       </c>
       <c r="B113" t="n">
-        <v>91372</v>
+        <v>88624</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14189,37 +14189,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>4412</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444354</v>
+        <v>444268</v>
       </c>
       <c r="R113" t="n">
-        <v>7029940</v>
+        <v>7029817</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14260,13 +14257,12 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Frisk barrblandskog</t>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14284,10 +14280,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127792888</v>
+        <v>127790050</v>
       </c>
       <c r="B114" t="n">
-        <v>88624</v>
+        <v>91372</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14295,34 +14291,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4412</v>
+        <v>5442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444268</v>
+        <v>444354</v>
       </c>
       <c r="R114" t="n">
-        <v>7029817</v>
+        <v>7029940</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14363,12 +14362,13 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Bördig och näringsrik naturskog med gran och tall</t>
+          <t>Frisk barrblandskog</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY123"/>
+  <dimension ref="A1:AY141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15312,6 +15312,1950 @@
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128398677</v>
+      </c>
+      <c r="B124" t="n">
+        <v>92682</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>444565</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7029666</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128398684</v>
+      </c>
+      <c r="B125" t="n">
+        <v>92293</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>444577</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7029926</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128398697</v>
+      </c>
+      <c r="B126" t="n">
+        <v>92660</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Åringsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>444423</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7029927</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128398706</v>
+      </c>
+      <c r="B127" t="n">
+        <v>97399</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Åringsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>444276</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7029894</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128398709</v>
+      </c>
+      <c r="B128" t="n">
+        <v>92293</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Åringsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>444312</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7029798</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128398681</v>
+      </c>
+      <c r="B129" t="n">
+        <v>91358</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>444640</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7029746</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128398688</v>
+      </c>
+      <c r="B130" t="n">
+        <v>78015</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>444493</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7029787</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128398710</v>
+      </c>
+      <c r="B131" t="n">
+        <v>92682</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Åringsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>444302</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7029807</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128398685</v>
+      </c>
+      <c r="B132" t="n">
+        <v>92293</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>444539</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7029933</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128398708</v>
+      </c>
+      <c r="B133" t="n">
+        <v>92293</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Åringsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>444330</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7029792</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128398682</v>
+      </c>
+      <c r="B134" t="n">
+        <v>91376</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>444642</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7029814</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128398678</v>
+      </c>
+      <c r="B135" t="n">
+        <v>92293</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>444640</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7029697</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128398676</v>
+      </c>
+      <c r="B136" t="n">
+        <v>91354</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>444526</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7029669</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128398683</v>
+      </c>
+      <c r="B137" t="n">
+        <v>92293</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>444641</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7029890</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128398711</v>
+      </c>
+      <c r="B138" t="n">
+        <v>92682</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Åringsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>444258</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7029800</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128398686</v>
+      </c>
+      <c r="B139" t="n">
+        <v>91354</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>444552</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7029865</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128398671</v>
+      </c>
+      <c r="B140" t="n">
+        <v>75147</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>492</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>444444</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7029685</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128398707</v>
+      </c>
+      <c r="B141" t="n">
+        <v>92293</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Åringsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>444276</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7029894</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY141"/>
+  <dimension ref="A1:AY142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17256,6 +17256,113 @@
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128398674</v>
+      </c>
+      <c r="B142" t="n">
+        <v>92158</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>444444</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7029685</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13875,7 +13875,7 @@
         <v>127795738</v>
       </c>
       <c r="B110" t="n">
-        <v>92304</v>
+        <v>92312</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13974,10 +13974,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127795783</v>
+        <v>127792860</v>
       </c>
       <c r="B111" t="n">
-        <v>97496</v>
+        <v>92662</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13985,21 +13985,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>222741</v>
+        <v>4366</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -14009,10 +14009,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>444423</v>
+        <v>444249</v>
       </c>
       <c r="R111" t="n">
-        <v>7029735</v>
+        <v>7029797</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14076,10 +14076,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127792860</v>
+        <v>127795783</v>
       </c>
       <c r="B112" t="n">
-        <v>92654</v>
+        <v>97504</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14087,21 +14087,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4366</v>
+        <v>222741</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -14111,10 +14111,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>444249</v>
+        <v>444423</v>
       </c>
       <c r="R112" t="n">
-        <v>7029797</v>
+        <v>7029735</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14181,7 +14181,7 @@
         <v>127792888</v>
       </c>
       <c r="B113" t="n">
-        <v>88624</v>
+        <v>88630</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>127790050</v>
       </c>
       <c r="B114" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>127796085</v>
       </c>
       <c r="B115" t="n">
-        <v>90897</v>
+        <v>90903</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>127793330</v>
       </c>
       <c r="B116" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>127796014</v>
       </c>
       <c r="B117" t="n">
-        <v>91405</v>
+        <v>91413</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>127796634</v>
       </c>
       <c r="B118" t="n">
-        <v>86884</v>
+        <v>86888</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>127796374</v>
       </c>
       <c r="B119" t="n">
-        <v>90125</v>
+        <v>90131</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>127794557</v>
       </c>
       <c r="B120" t="n">
-        <v>100559</v>
+        <v>100567</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>127794015</v>
       </c>
       <c r="B121" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>127796561</v>
       </c>
       <c r="B122" t="n">
-        <v>88624</v>
+        <v>88630</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>127795163</v>
       </c>
       <c r="B123" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15314,10 +15314,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128398677</v>
+        <v>128398684</v>
       </c>
       <c r="B124" t="n">
-        <v>92682</v>
+        <v>92295</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15325,21 +15325,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444565</v>
+        <v>444577</v>
       </c>
       <c r="R124" t="n">
-        <v>7029666</v>
+        <v>7029926</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15403,7 +15403,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15422,10 +15421,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128398684</v>
+        <v>128398677</v>
       </c>
       <c r="B125" t="n">
-        <v>92293</v>
+        <v>92684</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15433,21 +15432,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15457,10 +15456,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444577</v>
+        <v>444565</v>
       </c>
       <c r="R125" t="n">
-        <v>7029926</v>
+        <v>7029666</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15492,7 +15491,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15502,7 +15501,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15511,6 +15510,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>128398697</v>
       </c>
       <c r="B126" t="n">
-        <v>92660</v>
+        <v>92662</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>97399</v>
+        <v>92295</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R127" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>92293</v>
+        <v>97401</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R128" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15853,7 +15853,7 @@
         <v>128398681</v>
       </c>
       <c r="B129" t="n">
-        <v>91358</v>
+        <v>91360</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128398710</v>
       </c>
       <c r="B131" t="n">
-        <v>92682</v>
+        <v>92684</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>128398685</v>
       </c>
       <c r="B132" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128398708</v>
       </c>
       <c r="B133" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>128398682</v>
       </c>
       <c r="B134" t="n">
-        <v>91376</v>
+        <v>91378</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>128398678</v>
       </c>
       <c r="B135" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>128398676</v>
       </c>
       <c r="B136" t="n">
-        <v>91354</v>
+        <v>91356</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16707,10 +16707,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398683</v>
+        <v>128398711</v>
       </c>
       <c r="B137" t="n">
-        <v>92293</v>
+        <v>92684</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16718,34 +16718,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444641</v>
+        <v>444258</v>
       </c>
       <c r="R137" t="n">
-        <v>7029890</v>
+        <v>7029800</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16796,6 +16796,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16807,17 +16808,17 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398711</v>
+        <v>128398683</v>
       </c>
       <c r="B138" t="n">
-        <v>92682</v>
+        <v>92295</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16825,34 +16826,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444258</v>
+        <v>444641</v>
       </c>
       <c r="R138" t="n">
-        <v>7029800</v>
+        <v>7029890</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16884,7 +16885,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16894,7 +16895,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16903,7 +16904,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16925,7 +16925,7 @@
         <v>128398686</v>
       </c>
       <c r="B139" t="n">
-        <v>91354</v>
+        <v>91356</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>128398707</v>
       </c>
       <c r="B141" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>128398674</v>
       </c>
       <c r="B142" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -16707,10 +16707,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398711</v>
+        <v>128398683</v>
       </c>
       <c r="B137" t="n">
-        <v>92684</v>
+        <v>92295</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16718,34 +16718,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444258</v>
+        <v>444641</v>
       </c>
       <c r="R137" t="n">
-        <v>7029800</v>
+        <v>7029890</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16796,7 +16796,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16808,17 +16807,17 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398683</v>
+        <v>128398711</v>
       </c>
       <c r="B138" t="n">
-        <v>92295</v>
+        <v>92684</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16826,34 +16825,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444641</v>
+        <v>444258</v>
       </c>
       <c r="R138" t="n">
-        <v>7029890</v>
+        <v>7029800</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16885,7 +16884,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16895,7 +16894,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16904,6 +16903,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -13875,7 +13875,7 @@
         <v>127795738</v>
       </c>
       <c r="B110" t="n">
-        <v>92312</v>
+        <v>92404</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>127792860</v>
       </c>
       <c r="B111" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>127795783</v>
       </c>
       <c r="B112" t="n">
-        <v>97504</v>
+        <v>97597</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14178,10 +14178,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127792888</v>
+        <v>127790050</v>
       </c>
       <c r="B113" t="n">
-        <v>88630</v>
+        <v>91472</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14189,34 +14189,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4412</v>
+        <v>5442</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444268</v>
+        <v>444354</v>
       </c>
       <c r="R113" t="n">
-        <v>7029817</v>
+        <v>7029940</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14257,12 +14260,13 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Bördig och näringsrik naturskog med gran och tall</t>
+          <t>Frisk barrblandskog</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14280,10 +14284,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127790050</v>
+        <v>127792888</v>
       </c>
       <c r="B114" t="n">
-        <v>91380</v>
+        <v>88722</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14291,37 +14295,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5442</v>
+        <v>4412</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444354</v>
+        <v>444268</v>
       </c>
       <c r="R114" t="n">
-        <v>7029940</v>
+        <v>7029817</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14362,13 +14363,12 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Frisk barrblandskog</t>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -14389,7 +14389,7 @@
         <v>127796085</v>
       </c>
       <c r="B115" t="n">
-        <v>90903</v>
+        <v>90995</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>127793330</v>
       </c>
       <c r="B116" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>127796014</v>
       </c>
       <c r="B117" t="n">
-        <v>91413</v>
+        <v>91505</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>127796634</v>
       </c>
       <c r="B118" t="n">
-        <v>86888</v>
+        <v>86980</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>127796374</v>
       </c>
       <c r="B119" t="n">
-        <v>90131</v>
+        <v>90223</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>127794557</v>
       </c>
       <c r="B120" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>127794015</v>
       </c>
       <c r="B121" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>127796561</v>
       </c>
       <c r="B122" t="n">
-        <v>88630</v>
+        <v>88722</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>127795163</v>
       </c>
       <c r="B123" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>128398684</v>
       </c>
       <c r="B124" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>128398677</v>
       </c>
       <c r="B125" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>128398697</v>
       </c>
       <c r="B126" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B127" t="n">
-        <v>92295</v>
+        <v>97494</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R127" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B128" t="n">
-        <v>97401</v>
+        <v>92387</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R128" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15853,7 +15853,7 @@
         <v>128398681</v>
       </c>
       <c r="B129" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>128398688</v>
       </c>
       <c r="B130" t="n">
-        <v>78015</v>
+        <v>78060</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128398710</v>
       </c>
       <c r="B131" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>128398685</v>
       </c>
       <c r="B132" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128398708</v>
       </c>
       <c r="B133" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>128398682</v>
       </c>
       <c r="B134" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>128398678</v>
       </c>
       <c r="B135" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>128398676</v>
       </c>
       <c r="B136" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16707,32 +16707,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398683</v>
+        <v>128398686</v>
       </c>
       <c r="B137" t="n">
-        <v>92295</v>
+        <v>91448</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16742,10 +16742,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444641</v>
+        <v>444552</v>
       </c>
       <c r="R137" t="n">
-        <v>7029890</v>
+        <v>7029865</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16814,10 +16814,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398711</v>
+        <v>128398683</v>
       </c>
       <c r="B138" t="n">
-        <v>92684</v>
+        <v>92387</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16825,34 +16825,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444258</v>
+        <v>444641</v>
       </c>
       <c r="R138" t="n">
-        <v>7029800</v>
+        <v>7029890</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16903,7 +16903,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16915,52 +16914,52 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398686</v>
+        <v>128398711</v>
       </c>
       <c r="B139" t="n">
-        <v>91356</v>
+        <v>92776</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444552</v>
+        <v>444258</v>
       </c>
       <c r="R139" t="n">
-        <v>7029865</v>
+        <v>7029800</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16991,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17001,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17011,6 +17010,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -17032,7 +17032,7 @@
         <v>128398671</v>
       </c>
       <c r="B140" t="n">
-        <v>75147</v>
+        <v>75162</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>128398707</v>
       </c>
       <c r="B141" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>128398674</v>
       </c>
       <c r="B142" t="n">
-        <v>92160</v>
+        <v>92252</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -14178,10 +14178,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127790050</v>
+        <v>127792888</v>
       </c>
       <c r="B113" t="n">
-        <v>91472</v>
+        <v>88722</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14189,37 +14189,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5442</v>
+        <v>4412</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>444354</v>
+        <v>444268</v>
       </c>
       <c r="R113" t="n">
-        <v>7029940</v>
+        <v>7029817</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14260,13 +14257,12 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Frisk barrblandskog</t>
+          <t>Bördig och näringsrik naturskog med gran och tall</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -14284,10 +14280,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127792888</v>
+        <v>127790050</v>
       </c>
       <c r="B114" t="n">
-        <v>88722</v>
+        <v>91472</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14295,34 +14291,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4412</v>
+        <v>5442</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Blodbäcken, Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>444268</v>
+        <v>444354</v>
       </c>
       <c r="R114" t="n">
-        <v>7029817</v>
+        <v>7029940</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14363,12 +14362,13 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Bördig och näringsrik naturskog med gran och tall</t>
+          <t>Frisk barrblandskog</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>97494</v>
+        <v>92387</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R127" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>92387</v>
+        <v>97494</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R128" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD128" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B127" t="n">
-        <v>92387</v>
+        <v>97494</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R127" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B128" t="n">
-        <v>97494</v>
+        <v>92387</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R128" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16707,32 +16707,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398686</v>
+        <v>128398683</v>
       </c>
       <c r="B137" t="n">
-        <v>91448</v>
+        <v>92387</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16742,10 +16742,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444552</v>
+        <v>444641</v>
       </c>
       <c r="R137" t="n">
-        <v>7029865</v>
+        <v>7029890</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16814,10 +16814,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398683</v>
+        <v>128398711</v>
       </c>
       <c r="B138" t="n">
-        <v>92387</v>
+        <v>92776</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16825,34 +16825,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444641</v>
+        <v>444258</v>
       </c>
       <c r="R138" t="n">
-        <v>7029890</v>
+        <v>7029800</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16903,6 +16903,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16914,52 +16915,52 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398711</v>
+        <v>128398686</v>
       </c>
       <c r="B139" t="n">
-        <v>92776</v>
+        <v>91448</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444258</v>
+        <v>444552</v>
       </c>
       <c r="R139" t="n">
-        <v>7029800</v>
+        <v>7029865</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16991,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17001,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17010,7 +17011,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -16707,32 +16707,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398683</v>
+        <v>128398686</v>
       </c>
       <c r="B137" t="n">
-        <v>92387</v>
+        <v>91448</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16742,10 +16742,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444641</v>
+        <v>444552</v>
       </c>
       <c r="R137" t="n">
-        <v>7029890</v>
+        <v>7029865</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16814,10 +16814,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398711</v>
+        <v>128398683</v>
       </c>
       <c r="B138" t="n">
-        <v>92776</v>
+        <v>92387</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16825,34 +16825,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444258</v>
+        <v>444641</v>
       </c>
       <c r="R138" t="n">
-        <v>7029800</v>
+        <v>7029890</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16903,7 +16903,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16915,52 +16914,52 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398686</v>
+        <v>128398711</v>
       </c>
       <c r="B139" t="n">
-        <v>91448</v>
+        <v>92776</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444552</v>
+        <v>444258</v>
       </c>
       <c r="R139" t="n">
-        <v>7029865</v>
+        <v>7029800</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16991,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17001,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17011,6 +17010,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15314,10 +15314,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128398684</v>
+        <v>128398677</v>
       </c>
       <c r="B124" t="n">
-        <v>92387</v>
+        <v>92788</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15325,21 +15325,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444577</v>
+        <v>444565</v>
       </c>
       <c r="R124" t="n">
-        <v>7029926</v>
+        <v>7029666</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15403,6 +15403,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15421,10 +15422,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128398677</v>
+        <v>128398684</v>
       </c>
       <c r="B125" t="n">
-        <v>92776</v>
+        <v>92399</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15432,21 +15433,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15456,10 +15457,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444565</v>
+        <v>444577</v>
       </c>
       <c r="R125" t="n">
-        <v>7029666</v>
+        <v>7029926</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15491,7 +15492,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15501,7 +15502,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15510,7 +15511,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>128398697</v>
       </c>
       <c r="B126" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>97494</v>
+        <v>92399</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R127" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>92387</v>
+        <v>97506</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R128" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15853,7 +15853,7 @@
         <v>128398681</v>
       </c>
       <c r="B129" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>128398688</v>
       </c>
       <c r="B130" t="n">
-        <v>78060</v>
+        <v>78064</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128398710</v>
       </c>
       <c r="B131" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>128398685</v>
       </c>
       <c r="B132" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128398708</v>
       </c>
       <c r="B133" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>128398682</v>
       </c>
       <c r="B134" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>128398678</v>
       </c>
       <c r="B135" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>128398676</v>
       </c>
       <c r="B136" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16707,45 +16707,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398686</v>
+        <v>128398711</v>
       </c>
       <c r="B137" t="n">
-        <v>91448</v>
+        <v>92788</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444552</v>
+        <v>444258</v>
       </c>
       <c r="R137" t="n">
-        <v>7029865</v>
+        <v>7029800</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16796,6 +16796,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16807,39 +16808,39 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398683</v>
+        <v>128398686</v>
       </c>
       <c r="B138" t="n">
-        <v>92387</v>
+        <v>91460</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16849,10 +16850,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444641</v>
+        <v>444552</v>
       </c>
       <c r="R138" t="n">
-        <v>7029890</v>
+        <v>7029865</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16884,7 +16885,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16894,7 +16895,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16921,10 +16922,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398711</v>
+        <v>128398683</v>
       </c>
       <c r="B139" t="n">
-        <v>92776</v>
+        <v>92399</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16932,34 +16933,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444258</v>
+        <v>444641</v>
       </c>
       <c r="R139" t="n">
-        <v>7029800</v>
+        <v>7029890</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16991,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17001,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17010,7 +17011,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -17032,7 +17032,7 @@
         <v>128398671</v>
       </c>
       <c r="B140" t="n">
-        <v>75162</v>
+        <v>75166</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>128398707</v>
       </c>
       <c r="B141" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>128398674</v>
       </c>
       <c r="B142" t="n">
-        <v>92252</v>
+        <v>92264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15314,10 +15314,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128398677</v>
+        <v>128398684</v>
       </c>
       <c r="B124" t="n">
-        <v>92788</v>
+        <v>92401</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15325,21 +15325,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444565</v>
+        <v>444577</v>
       </c>
       <c r="R124" t="n">
-        <v>7029666</v>
+        <v>7029926</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15403,7 +15403,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15422,10 +15421,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128398684</v>
+        <v>128398677</v>
       </c>
       <c r="B125" t="n">
-        <v>92399</v>
+        <v>92790</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15433,21 +15432,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15457,10 +15456,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444577</v>
+        <v>444565</v>
       </c>
       <c r="R125" t="n">
-        <v>7029926</v>
+        <v>7029666</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15492,7 +15491,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15502,7 +15501,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15511,6 +15510,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>128398697</v>
       </c>
       <c r="B126" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15629,17 +15629,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B127" t="n">
-        <v>92399</v>
+        <v>97508</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R127" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15736,17 +15736,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B128" t="n">
-        <v>97506</v>
+        <v>92401</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R128" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -15853,7 +15853,7 @@
         <v>128398681</v>
       </c>
       <c r="B129" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>128398688</v>
       </c>
       <c r="B130" t="n">
-        <v>78064</v>
+        <v>78066</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128398710</v>
       </c>
       <c r="B131" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -16175,7 +16175,7 @@
         <v>128398685</v>
       </c>
       <c r="B132" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128398708</v>
       </c>
       <c r="B133" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -16389,7 +16389,7 @@
         <v>128398682</v>
       </c>
       <c r="B134" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>128398678</v>
       </c>
       <c r="B135" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>128398676</v>
       </c>
       <c r="B136" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>128398711</v>
       </c>
       <c r="B137" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16808,39 +16808,39 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398686</v>
+        <v>128398683</v>
       </c>
       <c r="B138" t="n">
-        <v>91460</v>
+        <v>92401</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444552</v>
+        <v>444641</v>
       </c>
       <c r="R138" t="n">
-        <v>7029865</v>
+        <v>7029890</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398683</v>
+        <v>128398686</v>
       </c>
       <c r="B139" t="n">
-        <v>92399</v>
+        <v>91462</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444641</v>
+        <v>444552</v>
       </c>
       <c r="R139" t="n">
-        <v>7029890</v>
+        <v>7029865</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17032,7 +17032,7 @@
         <v>128398671</v>
       </c>
       <c r="B140" t="n">
-        <v>75166</v>
+        <v>75168</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>128398707</v>
       </c>
       <c r="B141" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Johan Råghall</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -17261,7 +17261,7 @@
         <v>128398674</v>
       </c>
       <c r="B142" t="n">
-        <v>92264</v>
+        <v>92266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15629,17 +15629,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>97508</v>
+        <v>92401</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R127" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15736,17 +15736,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>92401</v>
+        <v>97508</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R128" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -16707,45 +16707,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398711</v>
+        <v>128398686</v>
       </c>
       <c r="B137" t="n">
-        <v>92790</v>
+        <v>91462</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444258</v>
+        <v>444552</v>
       </c>
       <c r="R137" t="n">
-        <v>7029800</v>
+        <v>7029865</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16796,7 +16796,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16808,17 +16807,17 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398683</v>
+        <v>128398711</v>
       </c>
       <c r="B138" t="n">
-        <v>92401</v>
+        <v>92790</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16826,34 +16825,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444641</v>
+        <v>444258</v>
       </c>
       <c r="R138" t="n">
-        <v>7029890</v>
+        <v>7029800</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16885,7 +16884,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16895,7 +16894,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16904,6 +16903,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16915,39 +16915,39 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398686</v>
+        <v>128398683</v>
       </c>
       <c r="B139" t="n">
-        <v>91462</v>
+        <v>92401</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444552</v>
+        <v>444641</v>
       </c>
       <c r="R139" t="n">
-        <v>7029865</v>
+        <v>7029890</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15317,7 +15317,7 @@
         <v>128398684</v>
       </c>
       <c r="B124" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>128398677</v>
       </c>
       <c r="B125" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>128398697</v>
       </c>
       <c r="B126" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B127" t="n">
-        <v>92401</v>
+        <v>97509</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R127" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B128" t="n">
-        <v>97508</v>
+        <v>92402</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R128" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15853,7 +15853,7 @@
         <v>128398681</v>
       </c>
       <c r="B129" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128398710</v>
       </c>
       <c r="B131" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>128398685</v>
       </c>
       <c r="B132" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128398708</v>
       </c>
       <c r="B133" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>128398682</v>
       </c>
       <c r="B134" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>128398678</v>
       </c>
       <c r="B135" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>128398676</v>
       </c>
       <c r="B136" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>128398686</v>
       </c>
       <c r="B137" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>128398711</v>
       </c>
       <c r="B138" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>128398683</v>
       </c>
       <c r="B139" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>128398707</v>
       </c>
       <c r="B141" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>128398674</v>
       </c>
       <c r="B142" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>97509</v>
+        <v>92402</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R127" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>92402</v>
+        <v>97509</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R128" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16814,10 +16814,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398711</v>
+        <v>128398683</v>
       </c>
       <c r="B138" t="n">
-        <v>92791</v>
+        <v>92402</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16825,34 +16825,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444258</v>
+        <v>444641</v>
       </c>
       <c r="R138" t="n">
-        <v>7029800</v>
+        <v>7029890</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16903,7 +16903,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16915,17 +16914,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398683</v>
+        <v>128398711</v>
       </c>
       <c r="B139" t="n">
-        <v>92402</v>
+        <v>92791</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16933,34 +16932,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444641</v>
+        <v>444258</v>
       </c>
       <c r="R139" t="n">
-        <v>7029890</v>
+        <v>7029800</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16991,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17001,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17011,6 +17010,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15314,10 +15314,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128398684</v>
+        <v>128398677</v>
       </c>
       <c r="B124" t="n">
-        <v>92402</v>
+        <v>92818</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15325,21 +15325,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444577</v>
+        <v>444565</v>
       </c>
       <c r="R124" t="n">
-        <v>7029926</v>
+        <v>7029666</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15403,6 +15403,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15421,10 +15422,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128398677</v>
+        <v>128398684</v>
       </c>
       <c r="B125" t="n">
-        <v>92791</v>
+        <v>92429</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15432,21 +15433,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15456,10 +15457,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444565</v>
+        <v>444577</v>
       </c>
       <c r="R125" t="n">
-        <v>7029666</v>
+        <v>7029926</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15491,7 +15492,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15501,7 +15502,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15510,7 +15511,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>128398697</v>
       </c>
       <c r="B126" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>97509</v>
+        <v>97536</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>128398681</v>
       </c>
       <c r="B129" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>128398688</v>
       </c>
       <c r="B130" t="n">
-        <v>78066</v>
+        <v>78093</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128398710</v>
       </c>
       <c r="B131" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>128398685</v>
       </c>
       <c r="B132" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128398708</v>
       </c>
       <c r="B133" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>128398682</v>
       </c>
       <c r="B134" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>128398678</v>
       </c>
       <c r="B135" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>128398676</v>
       </c>
       <c r="B136" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16707,45 +16707,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398686</v>
+        <v>128398711</v>
       </c>
       <c r="B137" t="n">
-        <v>91463</v>
+        <v>92818</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444552</v>
+        <v>444258</v>
       </c>
       <c r="R137" t="n">
-        <v>7029865</v>
+        <v>7029800</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16796,6 +16796,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16807,7 +16808,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16817,7 +16818,7 @@
         <v>128398683</v>
       </c>
       <c r="B138" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16921,45 +16922,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398711</v>
+        <v>128398686</v>
       </c>
       <c r="B139" t="n">
-        <v>92791</v>
+        <v>91490</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444258</v>
+        <v>444552</v>
       </c>
       <c r="R139" t="n">
-        <v>7029800</v>
+        <v>7029865</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16991,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17001,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17010,7 +17011,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -17032,7 +17032,7 @@
         <v>128398671</v>
       </c>
       <c r="B140" t="n">
-        <v>75168</v>
+        <v>75195</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>128398707</v>
       </c>
       <c r="B141" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>128398674</v>
       </c>
       <c r="B142" t="n">
-        <v>92267</v>
+        <v>92294</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15314,10 +15314,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128398677</v>
+        <v>128398684</v>
       </c>
       <c r="B124" t="n">
-        <v>92818</v>
+        <v>92429</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15325,21 +15325,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444565</v>
+        <v>444577</v>
       </c>
       <c r="R124" t="n">
-        <v>7029666</v>
+        <v>7029926</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15403,7 +15403,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15422,10 +15421,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128398684</v>
+        <v>128398677</v>
       </c>
       <c r="B125" t="n">
-        <v>92429</v>
+        <v>92818</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15433,21 +15432,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15457,10 +15456,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444577</v>
+        <v>444565</v>
       </c>
       <c r="R125" t="n">
-        <v>7029926</v>
+        <v>7029666</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15492,7 +15491,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15502,7 +15501,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15511,6 +15510,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -16707,45 +16707,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398711</v>
+        <v>128398686</v>
       </c>
       <c r="B137" t="n">
-        <v>92818</v>
+        <v>91490</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444258</v>
+        <v>444552</v>
       </c>
       <c r="R137" t="n">
-        <v>7029800</v>
+        <v>7029865</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16796,7 +16796,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16808,17 +16807,17 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398683</v>
+        <v>128398711</v>
       </c>
       <c r="B138" t="n">
-        <v>92429</v>
+        <v>92818</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16826,34 +16825,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444641</v>
+        <v>444258</v>
       </c>
       <c r="R138" t="n">
-        <v>7029890</v>
+        <v>7029800</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16885,7 +16884,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16895,7 +16894,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16904,6 +16903,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16915,39 +16915,39 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398686</v>
+        <v>128398683</v>
       </c>
       <c r="B139" t="n">
-        <v>91490</v>
+        <v>92429</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444552</v>
+        <v>444641</v>
       </c>
       <c r="R139" t="n">
-        <v>7029865</v>
+        <v>7029890</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD139" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15314,10 +15314,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128398684</v>
+        <v>128398677</v>
       </c>
       <c r="B124" t="n">
-        <v>92429</v>
+        <v>92830</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15325,21 +15325,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444577</v>
+        <v>444565</v>
       </c>
       <c r="R124" t="n">
-        <v>7029926</v>
+        <v>7029666</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15403,6 +15403,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15421,10 +15422,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128398677</v>
+        <v>128398684</v>
       </c>
       <c r="B125" t="n">
-        <v>92818</v>
+        <v>92439</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15432,21 +15433,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15456,10 +15457,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444565</v>
+        <v>444577</v>
       </c>
       <c r="R125" t="n">
-        <v>7029666</v>
+        <v>7029926</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15491,7 +15492,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15501,7 +15502,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15510,7 +15511,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>128398697</v>
       </c>
       <c r="B126" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B127" t="n">
-        <v>92429</v>
+        <v>97549</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R127" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B128" t="n">
-        <v>97536</v>
+        <v>92439</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R128" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15853,7 +15853,7 @@
         <v>128398681</v>
       </c>
       <c r="B129" t="n">
-        <v>91494</v>
+        <v>91504</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>128398688</v>
       </c>
       <c r="B130" t="n">
-        <v>78093</v>
+        <v>78097</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128398710</v>
       </c>
       <c r="B131" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>128398685</v>
       </c>
       <c r="B132" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128398708</v>
       </c>
       <c r="B133" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>128398682</v>
       </c>
       <c r="B134" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>128398678</v>
       </c>
       <c r="B135" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>128398676</v>
       </c>
       <c r="B136" t="n">
-        <v>91490</v>
+        <v>91500</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16707,45 +16707,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398686</v>
+        <v>128398711</v>
       </c>
       <c r="B137" t="n">
-        <v>91490</v>
+        <v>92830</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444552</v>
+        <v>444258</v>
       </c>
       <c r="R137" t="n">
-        <v>7029865</v>
+        <v>7029800</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16796,6 +16796,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16807,52 +16808,52 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398711</v>
+        <v>128398686</v>
       </c>
       <c r="B138" t="n">
-        <v>92818</v>
+        <v>91500</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444258</v>
+        <v>444552</v>
       </c>
       <c r="R138" t="n">
-        <v>7029800</v>
+        <v>7029865</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16884,7 +16885,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16894,7 +16895,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16903,7 +16904,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -16925,7 +16925,7 @@
         <v>128398683</v>
       </c>
       <c r="B139" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>128398671</v>
       </c>
       <c r="B140" t="n">
-        <v>75195</v>
+        <v>75196</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>128398707</v>
       </c>
       <c r="B141" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>128398674</v>
       </c>
       <c r="B142" t="n">
-        <v>92294</v>
+        <v>92304</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AY144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15314,10 +15314,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128398677</v>
+        <v>128398684</v>
       </c>
       <c r="B124" t="n">
-        <v>92830</v>
+        <v>92439</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15325,21 +15325,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444565</v>
+        <v>444577</v>
       </c>
       <c r="R124" t="n">
-        <v>7029666</v>
+        <v>7029926</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15403,7 +15403,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15422,10 +15421,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128398684</v>
+        <v>128398677</v>
       </c>
       <c r="B125" t="n">
-        <v>92439</v>
+        <v>92830</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15433,21 +15432,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15457,10 +15456,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444577</v>
+        <v>444565</v>
       </c>
       <c r="R125" t="n">
-        <v>7029926</v>
+        <v>7029666</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15492,7 +15491,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15502,7 +15501,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15511,6 +15510,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>97549</v>
+        <v>92439</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R127" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>92439</v>
+        <v>97549</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R128" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16815,32 +16815,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398686</v>
+        <v>128398683</v>
       </c>
       <c r="B138" t="n">
-        <v>91500</v>
+        <v>92439</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16850,10 +16850,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444552</v>
+        <v>444641</v>
       </c>
       <c r="R138" t="n">
-        <v>7029865</v>
+        <v>7029890</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398683</v>
+        <v>128398686</v>
       </c>
       <c r="B139" t="n">
-        <v>92439</v>
+        <v>91500</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444641</v>
+        <v>444552</v>
       </c>
       <c r="R139" t="n">
-        <v>7029890</v>
+        <v>7029865</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17363,6 +17363,251 @@
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128398687</v>
+      </c>
+      <c r="B143" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6006</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Oljeporing</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Sistotrema alboluteum</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>444491</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7029786</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>I mossa intill granlåga</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128398694</v>
+      </c>
+      <c r="B144" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6006</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Oljeporing</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Sistotrema alboluteum</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>444433</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7029787</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Asprikt parti i grandominerad kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Grov aspbark nedfallen till marken från låga.</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B127" t="n">
-        <v>92439</v>
+        <v>97549</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R127" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B128" t="n">
-        <v>97549</v>
+        <v>92439</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R128" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16707,45 +16707,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398711</v>
+        <v>128398686</v>
       </c>
       <c r="B137" t="n">
-        <v>92830</v>
+        <v>91500</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5964</v>
+        <v>1108</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Åringsån, Jmt</t>
+          <t>Blodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444258</v>
+        <v>444552</v>
       </c>
       <c r="R137" t="n">
-        <v>7029800</v>
+        <v>7029865</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16796,7 +16796,6 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
@@ -16808,17 +16807,17 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128398683</v>
+        <v>128398711</v>
       </c>
       <c r="B138" t="n">
-        <v>92439</v>
+        <v>92830</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16826,34 +16825,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Blodbäcken, Jmt</t>
+          <t>Åringsån, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>444641</v>
+        <v>444258</v>
       </c>
       <c r="R138" t="n">
-        <v>7029890</v>
+        <v>7029800</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16885,7 +16884,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16895,7 +16894,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16904,6 +16903,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -16915,39 +16915,39 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398686</v>
+        <v>128398683</v>
       </c>
       <c r="B139" t="n">
-        <v>91500</v>
+        <v>92439</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444552</v>
+        <v>444641</v>
       </c>
       <c r="R139" t="n">
-        <v>7029865</v>
+        <v>7029890</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD139" t="b">

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15636,10 +15636,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128398706</v>
+        <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>97549</v>
+        <v>92439</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15647,21 +15647,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221063</v>
+        <v>4769</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>444276</v>
+        <v>444312</v>
       </c>
       <c r="R127" t="n">
-        <v>7029894</v>
+        <v>7029798</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15743,10 +15743,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128398709</v>
+        <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>92439</v>
+        <v>97549</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,21 +15754,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>444312</v>
+        <v>444276</v>
       </c>
       <c r="R128" t="n">
-        <v>7029798</v>
+        <v>7029894</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16707,32 +16707,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398686</v>
+        <v>128398683</v>
       </c>
       <c r="B137" t="n">
-        <v>91500</v>
+        <v>92439</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16742,10 +16742,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444552</v>
+        <v>444641</v>
       </c>
       <c r="R137" t="n">
-        <v>7029865</v>
+        <v>7029890</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16922,32 +16922,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398683</v>
+        <v>128398686</v>
       </c>
       <c r="B139" t="n">
-        <v>92439</v>
+        <v>91500</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444641</v>
+        <v>444552</v>
       </c>
       <c r="R139" t="n">
-        <v>7029890</v>
+        <v>7029865</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91314</v>
+        <v>91318</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91314</v>
+        <v>91318</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15314,10 +15314,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128398684</v>
+        <v>128398677</v>
       </c>
       <c r="B124" t="n">
-        <v>92439</v>
+        <v>92834</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15325,21 +15325,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444577</v>
+        <v>444565</v>
       </c>
       <c r="R124" t="n">
-        <v>7029926</v>
+        <v>7029666</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15403,6 +15403,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15421,10 +15422,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128398677</v>
+        <v>128398684</v>
       </c>
       <c r="B125" t="n">
-        <v>92830</v>
+        <v>92443</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15432,21 +15433,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15456,10 +15457,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444565</v>
+        <v>444577</v>
       </c>
       <c r="R125" t="n">
-        <v>7029666</v>
+        <v>7029926</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15491,7 +15492,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15501,7 +15502,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15510,7 +15511,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>128398697</v>
       </c>
       <c r="B126" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>97549</v>
+        <v>97553</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>128398681</v>
       </c>
       <c r="B129" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>128398688</v>
       </c>
       <c r="B130" t="n">
-        <v>78097</v>
+        <v>78101</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128398710</v>
       </c>
       <c r="B131" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>128398685</v>
       </c>
       <c r="B132" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128398708</v>
       </c>
       <c r="B133" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>128398682</v>
       </c>
       <c r="B134" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>128398678</v>
       </c>
       <c r="B135" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>128398676</v>
       </c>
       <c r="B136" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16707,32 +16707,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128398683</v>
+        <v>128398686</v>
       </c>
       <c r="B137" t="n">
-        <v>92439</v>
+        <v>91504</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16742,10 +16742,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>444641</v>
+        <v>444552</v>
       </c>
       <c r="R137" t="n">
-        <v>7029890</v>
+        <v>7029865</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16817,7 +16817,7 @@
         <v>128398711</v>
       </c>
       <c r="B138" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16922,32 +16922,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128398686</v>
+        <v>128398683</v>
       </c>
       <c r="B139" t="n">
-        <v>91500</v>
+        <v>92443</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>444552</v>
+        <v>444641</v>
       </c>
       <c r="R139" t="n">
-        <v>7029865</v>
+        <v>7029890</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17032,7 +17032,7 @@
         <v>128398671</v>
       </c>
       <c r="B140" t="n">
-        <v>75196</v>
+        <v>75200</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>128398707</v>
       </c>
       <c r="B141" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>128398674</v>
       </c>
       <c r="B142" t="n">
-        <v>92304</v>
+        <v>92308</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -15314,10 +15314,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128398677</v>
+        <v>128398684</v>
       </c>
       <c r="B124" t="n">
-        <v>92834</v>
+        <v>92448</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15325,21 +15325,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>444565</v>
+        <v>444577</v>
       </c>
       <c r="R124" t="n">
-        <v>7029666</v>
+        <v>7029926</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15403,7 +15403,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15422,10 +15421,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128398684</v>
+        <v>128398677</v>
       </c>
       <c r="B125" t="n">
-        <v>92443</v>
+        <v>92839</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15433,21 +15432,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15457,10 +15456,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>444577</v>
+        <v>444565</v>
       </c>
       <c r="R125" t="n">
-        <v>7029926</v>
+        <v>7029666</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15492,7 +15491,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15502,7 +15501,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15511,6 +15510,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>128398697</v>
       </c>
       <c r="B126" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>128398709</v>
       </c>
       <c r="B127" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>128398706</v>
       </c>
       <c r="B128" t="n">
-        <v>97553</v>
+        <v>97560</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>128398681</v>
       </c>
       <c r="B129" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>128398688</v>
       </c>
       <c r="B130" t="n">
-        <v>78101</v>
+        <v>78042</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128398710</v>
       </c>
       <c r="B131" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>128398685</v>
       </c>
       <c r="B132" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128398708</v>
       </c>
       <c r="B133" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>128398682</v>
       </c>
       <c r="B134" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>128398678</v>
       </c>
       <c r="B135" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>128398676</v>
       </c>
       <c r="B136" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>128398686</v>
       </c>
       <c r="B137" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>128398711</v>
       </c>
       <c r="B138" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>128398683</v>
       </c>
       <c r="B139" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>128398671</v>
       </c>
       <c r="B140" t="n">
-        <v>75200</v>
+        <v>82996</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>128398707</v>
       </c>
       <c r="B141" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>128398674</v>
       </c>
       <c r="B142" t="n">
-        <v>92308</v>
+        <v>92313</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91318</v>
+        <v>91323</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91318</v>
+        <v>91323</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91330</v>
+        <v>91333</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91330</v>
+        <v>91333</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91333</v>
+        <v>91336</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91333</v>
+        <v>91336</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91336</v>
+        <v>91342</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91336</v>
+        <v>91342</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91342</v>
+        <v>91349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91342</v>
+        <v>91349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91349</v>
+        <v>91351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91349</v>
+        <v>91351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91351</v>
+        <v>91350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91351</v>
+        <v>91350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91350</v>
+        <v>91353</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91350</v>
+        <v>91353</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY144"/>
+  <dimension ref="A1:AY145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91353</v>
+        <v>91355</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91353</v>
+        <v>91355</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17608,6 +17608,129 @@
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128398696</v>
+      </c>
+      <c r="B145" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Blodbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>444433</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7029787</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17368,7 +17368,7 @@
         <v>128398687</v>
       </c>
       <c r="B143" t="n">
-        <v>91355</v>
+        <v>91359</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>128398694</v>
       </c>
       <c r="B144" t="n">
-        <v>91355</v>
+        <v>91359</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>128398696</v>
       </c>
       <c r="B145" t="n">
-        <v>91602</v>
+        <v>91606</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17613,7 +17613,7 @@
         <v>128398696</v>
       </c>
       <c r="B145" t="n">
-        <v>91606</v>
+        <v>91607</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17613,7 +17613,7 @@
         <v>128398696</v>
       </c>
       <c r="B145" t="n">
-        <v>91607</v>
+        <v>91610</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17613,7 +17613,7 @@
         <v>128398696</v>
       </c>
       <c r="B145" t="n">
-        <v>91610</v>
+        <v>91638</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17613,7 +17613,7 @@
         <v>128398696</v>
       </c>
       <c r="B145" t="n">
-        <v>91638</v>
+        <v>91644</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17613,7 +17613,7 @@
         <v>128398696</v>
       </c>
       <c r="B145" t="n">
-        <v>91644</v>
+        <v>91645</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 59126-2024 artfynd.xlsx
+++ b/artfynd/A 59126-2024 artfynd.xlsx
@@ -17613,7 +17613,7 @@
         <v>128398696</v>
       </c>
       <c r="B145" t="n">
-        <v>91645</v>
+        <v>91650</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
